--- a/beaching_data_all.xlsx
+++ b/beaching_data_all.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <si>
     <t xml:space="preserve">beach</t>
   </si>
@@ -70,12 +70,18 @@
     <t xml:space="preserve">Bald Point State Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Barefoot Beach Preserve</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beach Club Drive (North)</t>
   </si>
   <si>
     <t xml:space="preserve">Beach Club Drive (South)</t>
   </si>
   <si>
+    <t xml:space="preserve">Big Hickory Island</t>
+  </si>
+  <si>
     <t xml:space="preserve">Big Pine Key</t>
   </si>
   <si>
@@ -91,9 +97,15 @@
     <t xml:space="preserve">Boca Raton Beaches</t>
   </si>
   <si>
+    <t xml:space="preserve">Bonita Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Breakers</t>
   </si>
   <si>
+    <t xml:space="preserve">Bunche Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabbage/Shell Key</t>
   </si>
   <si>
@@ -145,6 +157,9 @@
     <t xml:space="preserve">Clam Pass Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Clarence Higgs Beach (Key West)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cocoa Beach</t>
   </si>
   <si>
@@ -169,6 +184,9 @@
     <t xml:space="preserve">Don Pedro State Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Dry Tortugas - Bush Key</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dry Tortugas - East Key</t>
   </si>
   <si>
@@ -178,9 +196,15 @@
     <t xml:space="preserve">Dry Tortugas - Loggerhead Key</t>
   </si>
   <si>
+    <t xml:space="preserve">Dry Tortugas - Long Key</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dry Tortugas - Middle Key</t>
   </si>
   <si>
+    <t xml:space="preserve">ENP - Cape Sable (North)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENP - Cape Sable (South)</t>
   </si>
   <si>
@@ -199,6 +223,9 @@
     <t xml:space="preserve">Eglin Air Force Base (Santa Rosa County)</t>
   </si>
   <si>
+    <t xml:space="preserve">Egmont Key</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estero Island</t>
   </si>
   <si>
@@ -355,9 +382,15 @@
     <t xml:space="preserve">Little Crawl Key</t>
   </si>
   <si>
+    <t xml:space="preserve">Little Gasparilla Island</t>
+  </si>
+  <si>
     <t xml:space="preserve">Little Talbot Island State Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Long Key (West End)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Long Key State Park</t>
   </si>
   <si>
@@ -367,6 +400,9 @@
     <t xml:space="preserve">Longboat Key (South)</t>
   </si>
   <si>
+    <t xml:space="preserve">Lovers Key State Park</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lower Matecumbe Sea Oats Bch</t>
   </si>
   <si>
@@ -415,6 +451,9 @@
     <t xml:space="preserve">Naples Beach</t>
   </si>
   <si>
+    <t xml:space="preserve">Nature Preserve Beach (Key West)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Navarre Beach</t>
   </si>
   <si>
@@ -445,6 +484,9 @@
     <t xml:space="preserve">Ocean Inlet Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Ocean Reef Park</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ocean Ridge (Boynton)</t>
   </si>
   <si>
@@ -469,6 +511,9 @@
     <t xml:space="preserve">Parkshore Beach</t>
   </si>
   <si>
+    <t xml:space="preserve">Patio Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Patrick Air Force Base</t>
   </si>
   <si>
@@ -481,6 +526,9 @@
     <t xml:space="preserve">Perdido Key State Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Phipps Preserve Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pompano/Lauderdale by-the-sea</t>
   </si>
   <si>
@@ -514,6 +562,9 @@
     <t xml:space="preserve">Sanibel Island (West)</t>
   </si>
   <si>
+    <t xml:space="preserve">Sea Oat Island</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sebastian Inlet State Park (Brevard County)</t>
   </si>
   <si>
@@ -580,6 +631,9 @@
     <t xml:space="preserve">Stump Pass State Park</t>
   </si>
   <si>
+    <t xml:space="preserve">Ten Thousand Islands National Wildlife Refuge</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tequesta Beaches</t>
   </si>
   <si>
@@ -595,6 +649,9 @@
     <t xml:space="preserve">Upper Matecumbe Key</t>
   </si>
   <si>
+    <t xml:space="preserve">Vanderbilt Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Venice Beaches</t>
   </si>
   <si>
@@ -626,6 +683,9 @@
   </si>
   <si>
     <t xml:space="preserve">West (Walton) County Beaches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiggins Pass</t>
   </si>
   <si>
     <t xml:space="preserve">Woman Key</t>
@@ -710,34 +770,34 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>30.03297</v>
+        <v>29.893457</v>
       </c>
       <c r="C2">
-        <v>-85.481563</v>
+        <v>-84.424007</v>
       </c>
       <c r="D2">
-        <v>29.902953</v>
+        <v>29.904019</v>
       </c>
       <c r="E2">
-        <v>-84.371677</v>
+        <v>-84.343628</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="G2">
-        <v>0.9833</v>
+        <v>53.4804</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="I2">
-        <v>2.0087</v>
+        <v>45.4168</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="K2">
-        <v>2.1881</v>
+        <v>57.2174</v>
       </c>
     </row>
     <row r="3">
@@ -745,34 +805,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>29.665239</v>
+        <v>30.526339</v>
       </c>
       <c r="C3">
-        <v>-80.789886</v>
+        <v>-81.443195</v>
       </c>
       <c r="D3">
-        <v>30.611641</v>
+        <v>30.690828</v>
       </c>
       <c r="E3">
-        <v>-81.429535</v>
+        <v>-81.428452</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="G3">
-        <v>13.0832</v>
+        <v>119.4948</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="I3">
-        <v>12.4017</v>
+        <v>117.6794</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="K3">
-        <v>12.7818</v>
+        <v>71.0684</v>
       </c>
     </row>
     <row r="4">
@@ -780,34 +840,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>30.77931</v>
+        <v>30.514971</v>
       </c>
       <c r="C4">
-        <v>-81.30472</v>
+        <v>-81.445112</v>
       </c>
       <c r="D4">
-        <v>30.52185</v>
+        <v>30.526354</v>
       </c>
       <c r="E4">
-        <v>-81.41898</v>
+        <v>-81.435707</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>0.176</v>
+        <v>19.1903</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>1.1539</v>
+        <v>11.3192</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K4">
-        <v>1.1561</v>
+        <v>19.3516</v>
       </c>
     </row>
     <row r="5">
@@ -815,34 +875,34 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>22.501987</v>
+        <v>29.859566</v>
       </c>
       <c r="C5">
-        <v>-74.378533</v>
+        <v>-81.284006</v>
       </c>
       <c r="D5">
-        <v>29.902429</v>
+        <v>29.908523</v>
       </c>
       <c r="E5">
-        <v>-81.275192</v>
+        <v>-81.266143</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="G5">
-        <v>11.0676</v>
+        <v>148.1206</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="I5">
-        <v>1.982</v>
+        <v>92.3574</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="K5">
-        <v>4.3418</v>
+        <v>102.2136</v>
       </c>
     </row>
     <row r="6">
@@ -850,34 +910,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>28.872722</v>
+        <v>28.156548</v>
       </c>
       <c r="C6">
-        <v>-83.42492</v>
+        <v>-82.852129</v>
       </c>
       <c r="D6">
-        <v>28.190556</v>
+        <v>28.234185</v>
       </c>
       <c r="E6">
-        <v>-82.844606</v>
+        <v>-82.837764</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>4.0415</v>
+        <v>76.0792</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>1.9321</v>
+        <v>11.7463</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="K6">
-        <v>33.0484</v>
+        <v>156.1777</v>
       </c>
     </row>
     <row r="7">
@@ -885,34 +945,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>28.250294</v>
+        <v>27.444272</v>
       </c>
       <c r="C7">
-        <v>-83.138167</v>
+        <v>-82.746586</v>
       </c>
       <c r="D7">
-        <v>27.496179</v>
+        <v>27.538994</v>
       </c>
       <c r="E7">
-        <v>-82.711583</v>
+        <v>-82.690959</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>207</v>
       </c>
       <c r="G7">
-        <v>2.9647</v>
+        <v>159.7115</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="I7">
-        <v>3.3235</v>
+        <v>109.1482</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>232</v>
       </c>
       <c r="K7">
-        <v>4.3741</v>
+        <v>179.4603</v>
       </c>
     </row>
     <row r="8">
@@ -920,34 +980,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>21.37964</v>
+        <v>27.532591</v>
       </c>
       <c r="C8">
-        <v>-74.797398</v>
+        <v>-80.321571</v>
       </c>
       <c r="D8">
-        <v>27.549495</v>
+        <v>27.557286</v>
       </c>
       <c r="E8">
-        <v>-80.320752</v>
+        <v>-80.313919</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>5.8015</v>
+        <v>53.2001</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>9.0524</v>
+        <v>45.7024</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="K8">
-        <v>7.2453</v>
+        <v>69.4307</v>
       </c>
     </row>
     <row r="9">
@@ -955,34 +1015,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>27.325265</v>
+        <v>24.654141</v>
       </c>
       <c r="C9">
-        <v>-82.76019</v>
+        <v>-81.281122</v>
       </c>
       <c r="D9">
-        <v>24.665685</v>
+        <v>24.6686</v>
       </c>
       <c r="E9">
-        <v>-81.253215</v>
+        <v>-81.249709</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>0.0</v>
+        <v>1.5113</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>0.9845</v>
+        <v>15.5252</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K9">
-        <v>0.9846</v>
+        <v>22.6609</v>
       </c>
     </row>
     <row r="10">
@@ -990,34 +1050,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>29.95609</v>
+        <v>29.899879</v>
       </c>
       <c r="C10">
-        <v>-84.27226</v>
+        <v>-84.343628</v>
       </c>
       <c r="D10">
-        <v>29.95568</v>
+        <v>29.947917</v>
       </c>
       <c r="E10">
-        <v>-84.35091</v>
+        <v>-84.333444</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G10">
-        <v>0.3932</v>
+        <v>45.4868</v>
       </c>
       <c r="H10">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="I10">
-        <v>9.023</v>
+        <v>81.2438</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K10">
-        <v>0.0</v>
+        <v>22.9123</v>
       </c>
     </row>
     <row r="11">
@@ -1025,34 +1085,34 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>30.34312</v>
+        <v>26.289549</v>
       </c>
       <c r="C11">
-        <v>-81.25398</v>
+        <v>-81.845765</v>
       </c>
       <c r="D11">
-        <v>30.20062</v>
+        <v>26.330222</v>
       </c>
       <c r="E11">
-        <v>-81.36847</v>
+        <v>-81.830931</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>0.0</v>
+        <v>7.4594</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>1.1666</v>
+        <v>3.872</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K11">
-        <v>2.5332</v>
+        <v>9.4313</v>
       </c>
     </row>
     <row r="12">
@@ -1060,34 +1120,34 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>29.757218</v>
+        <v>30.193545</v>
       </c>
       <c r="C12">
-        <v>-81.097078</v>
+        <v>-81.370734</v>
       </c>
       <c r="D12">
-        <v>30.169861</v>
+        <v>30.21709</v>
       </c>
       <c r="E12">
-        <v>-81.355607</v>
+        <v>-81.363965</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G12">
-        <v>8.3741</v>
+        <v>23.7144</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I12">
-        <v>6.4315</v>
+        <v>15.8382</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="K12">
-        <v>9.1403</v>
+        <v>49.4158</v>
       </c>
     </row>
     <row r="13">
@@ -1095,34 +1155,34 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>20.586284</v>
+        <v>30.141105</v>
       </c>
       <c r="C13">
-        <v>-75.650135</v>
+        <v>-81.363965</v>
       </c>
       <c r="D13">
-        <v>24.642932</v>
+        <v>30.193545</v>
       </c>
       <c r="E13">
-        <v>-81.345093</v>
+        <v>-81.350425</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="G13">
-        <v>0.0</v>
+        <v>119.7171</v>
       </c>
       <c r="H13">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="I13">
-        <v>14.0117</v>
+        <v>82.7508</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="K13">
-        <v>2.056</v>
+        <v>109.6151</v>
       </c>
     </row>
     <row r="14">
@@ -1130,34 +1190,34 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>19.199505</v>
+        <v>26.366616</v>
       </c>
       <c r="C14">
-        <v>-74.819065</v>
+        <v>-81.867867</v>
       </c>
       <c r="D14">
-        <v>25.41045</v>
+        <v>26.378581</v>
       </c>
       <c r="E14">
-        <v>-80.19336</v>
+        <v>-81.861569</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>3.7305</v>
+        <v>1.6771</v>
       </c>
       <c r="H14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>20.1675</v>
+        <v>3.1424</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>2.0101</v>
+        <v>2.0359</v>
       </c>
     </row>
     <row r="15">
@@ -1165,34 +1225,34 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>18.66151</v>
+        <v>24.633941</v>
       </c>
       <c r="C15">
-        <v>-74.62033</v>
+        <v>-81.357291</v>
       </c>
       <c r="D15">
-        <v>24.567611</v>
+        <v>24.639979</v>
       </c>
       <c r="E15">
-        <v>-81.676202</v>
+        <v>-81.338951</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>0.0</v>
+        <v>2.9153</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="I15">
-        <v>13.3484</v>
+        <v>140.6065</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K15">
-        <v>0.8918</v>
+        <v>45.2351</v>
       </c>
     </row>
     <row r="16">
@@ -1200,34 +1260,34 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>25.130897</v>
+        <v>25.415142</v>
       </c>
       <c r="C16">
-        <v>-79.668083</v>
+        <v>-80.203522</v>
       </c>
       <c r="D16">
-        <v>24.529427</v>
+        <v>25.492535</v>
       </c>
       <c r="E16">
-        <v>-82.000293</v>
+        <v>-80.177473</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G16">
-        <v>0.0</v>
+        <v>16.6103</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>225</v>
       </c>
       <c r="I16">
-        <v>2.204</v>
+        <v>244.9883</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K16">
-        <v>0.0</v>
+        <v>25.5812</v>
       </c>
     </row>
     <row r="17">
@@ -1235,34 +1295,34 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>17.805917</v>
+        <v>24.56327</v>
       </c>
       <c r="C17">
-        <v>-73.257837</v>
+        <v>-81.676851</v>
       </c>
       <c r="D17">
-        <v>26.368581</v>
+        <v>24.567751</v>
       </c>
       <c r="E17">
-        <v>-80.070083</v>
+        <v>-81.670865</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>5.414</v>
+        <v>6.5423</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="I17">
-        <v>3.5628</v>
+        <v>153.2862</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K17">
-        <v>3.9293</v>
+        <v>24.5334</v>
       </c>
     </row>
     <row r="18">
@@ -1270,16 +1330,16 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>26.03735</v>
+        <v>24.527564</v>
       </c>
       <c r="C18">
-        <v>-80.01018</v>
+        <v>-82.009891</v>
       </c>
       <c r="D18">
-        <v>26.716805</v>
+        <v>24.537774</v>
       </c>
       <c r="E18">
-        <v>-80.01838</v>
+        <v>-82.005886</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1288,16 +1348,16 @@
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I18">
-        <v>0.0</v>
+        <v>25.3788</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>1.0714</v>
+        <v>7.9549</v>
       </c>
     </row>
     <row r="19">
@@ -1305,34 +1365,34 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>28.233297</v>
+        <v>26.321003</v>
       </c>
       <c r="C19">
-        <v>-83.269797</v>
+        <v>-80.074627</v>
       </c>
       <c r="D19">
-        <v>27.66298</v>
+        <v>26.39088</v>
       </c>
       <c r="E19">
-        <v>-82.727407</v>
+        <v>-80.066179</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="G19">
-        <v>1.4069</v>
+        <v>207.0144</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="I19">
-        <v>2.4639</v>
+        <v>177.9717</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="K19">
-        <v>2.3883</v>
+        <v>132.0588</v>
       </c>
     </row>
     <row r="20">
@@ -1340,34 +1400,34 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>28.27706</v>
+        <v>26.330222</v>
       </c>
       <c r="C20">
-        <v>-82.943302</v>
+        <v>-81.86315</v>
       </c>
       <c r="D20">
-        <v>28.033918</v>
+        <v>26.364345</v>
       </c>
       <c r="E20">
-        <v>-82.810622</v>
+        <v>-81.845765</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G20">
-        <v>2.0745</v>
+        <v>8.7542</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I20">
-        <v>1.5717</v>
+        <v>7.9651</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K20">
-        <v>2.1583</v>
+        <v>11.9191</v>
       </c>
     </row>
     <row r="21">
@@ -1375,34 +1435,34 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>29.139366</v>
+        <v>26.71072</v>
       </c>
       <c r="C21">
-        <v>-84.928166</v>
+        <v>-80.033861</v>
       </c>
       <c r="D21">
-        <v>30.276314</v>
+        <v>26.71904</v>
       </c>
       <c r="E21">
-        <v>-85.992166</v>
+        <v>-80.032891</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2.5038</v>
+        <v>0.0</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I21">
-        <v>1.6612</v>
+        <v>15.3794</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K21">
-        <v>0.3442</v>
+        <v>15.758</v>
       </c>
     </row>
     <row r="22">
@@ -1410,34 +1470,34 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>21.153327</v>
+        <v>26.470909</v>
       </c>
       <c r="C22">
-        <v>-74.651171</v>
+        <v>-81.971643</v>
       </c>
       <c r="D22">
-        <v>28.496181</v>
+        <v>26.478743</v>
       </c>
       <c r="E22">
-        <v>-80.564079</v>
+        <v>-81.959963</v>
       </c>
       <c r="F22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>16.9031</v>
+        <v>0.9345</v>
       </c>
       <c r="H22">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>47.2314</v>
+        <v>0.3474</v>
       </c>
       <c r="J22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>23.5604</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1445,34 +1505,34 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>22.430238</v>
+        <v>27.649767</v>
       </c>
       <c r="C23">
-        <v>-75.617324</v>
+        <v>-82.746263</v>
       </c>
       <c r="D23">
-        <v>28.66761</v>
+        <v>27.676238</v>
       </c>
       <c r="E23">
-        <v>-80.65024</v>
+        <v>-82.732224</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="G23">
-        <v>15.3531</v>
+        <v>78.9616</v>
       </c>
       <c r="H23">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I23">
-        <v>37.0078</v>
+        <v>57.1863</v>
       </c>
       <c r="J23">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K23">
-        <v>12.2513</v>
+        <v>55.9811</v>
       </c>
     </row>
     <row r="24">
@@ -1480,34 +1540,34 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>24.904214</v>
+        <v>28.019435</v>
       </c>
       <c r="C24">
-        <v>-78.203393</v>
+        <v>-82.827134</v>
       </c>
       <c r="D24">
-        <v>28.864046</v>
+        <v>28.051693</v>
       </c>
       <c r="E24">
-        <v>-80.789131</v>
+        <v>-82.815935</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G24">
-        <v>0.0</v>
+        <v>44.4111</v>
       </c>
       <c r="H24">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I24">
-        <v>37.7471</v>
+        <v>42.1512</v>
       </c>
       <c r="J24">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="K24">
-        <v>23.7196</v>
+        <v>49.4795</v>
       </c>
     </row>
     <row r="25">
@@ -1515,34 +1575,34 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>15.80402</v>
+        <v>30.267052</v>
       </c>
       <c r="C25">
-        <v>-68.33587</v>
+        <v>-85.995907</v>
       </c>
       <c r="D25">
-        <v>25.67113</v>
+        <v>30.269383</v>
       </c>
       <c r="E25">
-        <v>-80.162477</v>
+        <v>-85.990854</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="G25">
-        <v>3.52</v>
+        <v>24.3405</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="I25">
-        <v>11.8485</v>
+        <v>46.8874</v>
       </c>
       <c r="J25">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K25">
-        <v>20.264</v>
+        <v>23.9364</v>
       </c>
     </row>
     <row r="26">
@@ -1550,34 +1610,34 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>26.317605</v>
+        <v>28.411555</v>
       </c>
       <c r="C26">
-        <v>-82.0115</v>
+        <v>-80.584163</v>
       </c>
       <c r="D26">
-        <v>25.882665</v>
+        <v>28.568617</v>
       </c>
       <c r="E26">
-        <v>-81.722365</v>
+        <v>-80.525407</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="G26">
-        <v>1.1099</v>
+        <v>235.5956</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>589.0474</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="K26">
-        <v>0.0</v>
+        <v>320.2714</v>
       </c>
     </row>
     <row r="27">
@@ -1585,34 +1645,34 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>15.855037</v>
+        <v>28.644196</v>
       </c>
       <c r="C27">
-        <v>-68.072537</v>
+        <v>-80.73297</v>
       </c>
       <c r="D27">
-        <v>29.67849</v>
+        <v>28.791195</v>
       </c>
       <c r="E27">
-        <v>-85.298017</v>
+        <v>-80.624025</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="G27">
-        <v>5.0205</v>
+        <v>101.2997</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>378</v>
       </c>
       <c r="I27">
-        <v>5.4194</v>
+        <v>276.1857</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="K27">
-        <v>1.3624</v>
+        <v>132.8141</v>
       </c>
     </row>
     <row r="28">
@@ -1620,34 +1680,34 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>17.2466</v>
+        <v>28.791195</v>
       </c>
       <c r="C28">
-        <v>-71.954653</v>
+        <v>-80.830148</v>
       </c>
       <c r="D28">
-        <v>29.674657</v>
+        <v>28.938634</v>
       </c>
       <c r="E28">
-        <v>-85.349137</v>
+        <v>-80.73297</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G28">
-        <v>0.0</v>
+        <v>39.8081</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="I28">
-        <v>1.7311</v>
+        <v>243.9995</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="K28">
-        <v>0.0</v>
+        <v>132.2207</v>
       </c>
     </row>
     <row r="29">
@@ -1655,34 +1715,34 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>27.95704</v>
+        <v>25.666725</v>
       </c>
       <c r="C29">
-        <v>-82.92941</v>
+        <v>-80.155833</v>
       </c>
       <c r="D29">
-        <v>29.60646</v>
+        <v>25.683025</v>
       </c>
       <c r="E29">
-        <v>-85.05523</v>
+        <v>-80.152772</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G29">
-        <v>0.4684</v>
+        <v>55.5617</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="I29">
-        <v>0.1427</v>
+        <v>159.8586</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K29">
-        <v>0.0</v>
+        <v>179.3835</v>
       </c>
     </row>
     <row r="30">
@@ -1690,34 +1750,34 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>26.299567</v>
+        <v>25.843995</v>
       </c>
       <c r="C30">
-        <v>-82.030513</v>
+        <v>-81.716203</v>
       </c>
       <c r="D30">
-        <v>26.53422</v>
+        <v>25.902069</v>
       </c>
       <c r="E30">
-        <v>-82.193627</v>
+        <v>-81.672481</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G30">
-        <v>1.6774</v>
+        <v>4.5906</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>1.856</v>
+        <v>3.0144</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K30">
-        <v>0.9154</v>
+        <v>9.5547</v>
       </c>
     </row>
     <row r="31">
@@ -1725,34 +1785,34 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>29.942492</v>
+        <v>29.676105</v>
       </c>
       <c r="C31">
-        <v>-84.243705</v>
+        <v>-85.333904</v>
       </c>
       <c r="D31">
-        <v>29.81414</v>
+        <v>29.684196</v>
       </c>
       <c r="E31">
-        <v>-84.688382</v>
+        <v>-85.222301</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="G31">
-        <v>2.3772</v>
+        <v>90.7418</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>120.1969</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K31">
-        <v>0.0</v>
+        <v>76.2295</v>
       </c>
     </row>
     <row r="32">
@@ -1760,34 +1820,34 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>26.72549</v>
+        <v>29.666531</v>
       </c>
       <c r="C32">
-        <v>-82.40897</v>
+        <v>-85.363114</v>
       </c>
       <c r="D32">
-        <v>27.21529</v>
+        <v>29.676535</v>
       </c>
       <c r="E32">
-        <v>-82.50047</v>
+        <v>-85.333904</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>0.0</v>
+        <v>3.1456</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>21.7995</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K32">
-        <v>0.2096</v>
+        <v>16.3423</v>
       </c>
     </row>
     <row r="33">
@@ -1795,34 +1855,34 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>27.221341</v>
+        <v>29.587158</v>
       </c>
       <c r="C33">
-        <v>-82.526626</v>
+        <v>-85.098511</v>
       </c>
       <c r="D33">
-        <v>26.648944</v>
+        <v>29.625764</v>
       </c>
       <c r="E33">
-        <v>-82.240621</v>
+        <v>-84.959254</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G33">
-        <v>7.7507</v>
+        <v>8.092</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I33">
-        <v>3.4967</v>
+        <v>25.091</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K33">
-        <v>5.5149</v>
+        <v>19.1613</v>
       </c>
     </row>
     <row r="34">
@@ -1830,34 +1890,34 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>21.162833</v>
+        <v>26.482725</v>
       </c>
       <c r="C34">
-        <v>-75.120217</v>
+        <v>-82.201578</v>
       </c>
       <c r="D34">
-        <v>28.129732</v>
+        <v>26.551299</v>
       </c>
       <c r="E34">
-        <v>-80.574882</v>
+        <v>-82.183753</v>
       </c>
       <c r="F34">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G34">
-        <v>50.4129</v>
+        <v>7.9357</v>
       </c>
       <c r="H34">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="I34">
-        <v>132.3769</v>
+        <v>18.0006</v>
       </c>
       <c r="J34">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K34">
-        <v>79.2363</v>
+        <v>25.9166</v>
       </c>
     </row>
     <row r="35">
@@ -1865,34 +1925,34 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>26.51117</v>
+        <v>29.787415</v>
       </c>
       <c r="C35">
-        <v>-82.24692</v>
+        <v>-84.761978</v>
       </c>
       <c r="D35">
-        <v>26.21797</v>
+        <v>29.832691</v>
       </c>
       <c r="E35">
-        <v>-81.81007</v>
+        <v>-84.674634</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="G35">
-        <v>0.9164</v>
+        <v>106.3677</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>96.2528</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K35">
-        <v>0.0</v>
+        <v>50.244</v>
       </c>
     </row>
     <row r="36">
@@ -1900,34 +1960,34 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>20.387687</v>
+        <v>27.11329</v>
       </c>
       <c r="C36">
-        <v>-73.935798</v>
+        <v>-82.512127</v>
       </c>
       <c r="D36">
-        <v>28.325972</v>
+        <v>27.208416</v>
       </c>
       <c r="E36">
-        <v>-80.614779</v>
+        <v>-82.468664</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="G36">
-        <v>18.7994</v>
+        <v>83.3225</v>
       </c>
       <c r="H36">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="I36">
-        <v>61.9956</v>
+        <v>60.1082</v>
       </c>
       <c r="J36">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="K36">
-        <v>32.0304</v>
+        <v>91.0269</v>
       </c>
     </row>
     <row r="37">
@@ -1935,34 +1995,34 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>10.74994</v>
+        <v>26.613118</v>
       </c>
       <c r="C37">
-        <v>-66.88937</v>
+        <v>-82.26364</v>
       </c>
       <c r="D37">
-        <v>26.96371</v>
+        <v>26.707637</v>
       </c>
       <c r="E37">
-        <v>-80.07993</v>
+        <v>-82.222295</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="G37">
-        <v>5.4957</v>
+        <v>89.406</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="I37">
-        <v>5.9421</v>
+        <v>61.6055</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="K37">
-        <v>7.439</v>
+        <v>69.9492</v>
       </c>
     </row>
     <row r="38">
@@ -1970,34 +2030,34 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>20.37938</v>
+        <v>28.043353</v>
       </c>
       <c r="C38">
-        <v>-73.833715</v>
+        <v>-80.596748</v>
       </c>
       <c r="D38">
-        <v>30.313243</v>
+        <v>28.21268</v>
       </c>
       <c r="E38">
-        <v>-86.077405</v>
+        <v>-80.545315</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>559</v>
       </c>
       <c r="G38">
-        <v>6.0386</v>
+        <v>535.0504</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>869</v>
       </c>
       <c r="I38">
-        <v>0.0</v>
+        <v>841.4415</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>579</v>
       </c>
       <c r="K38">
-        <v>0.3544</v>
+        <v>566.9348</v>
       </c>
     </row>
     <row r="39">
@@ -2005,34 +2065,34 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>17.074757</v>
+        <v>26.210934</v>
       </c>
       <c r="C39">
-        <v>-68.531987</v>
+        <v>-81.817808</v>
       </c>
       <c r="D39">
-        <v>26.30241</v>
+        <v>26.219578</v>
       </c>
       <c r="E39">
-        <v>-80.08567</v>
+        <v>-81.817001</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39">
-        <v>6.4742</v>
+        <v>1.656</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>1.1881</v>
+        <v>1.4874</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39">
-        <v>2.9324</v>
+        <v>2.0584</v>
       </c>
     </row>
     <row r="40">
@@ -2040,34 +2100,34 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>15.10038</v>
+        <v>24.546885</v>
       </c>
       <c r="C40">
-        <v>-67.85629</v>
+        <v>-81.788547</v>
       </c>
       <c r="D40">
-        <v>26.44514</v>
+        <v>24.547045</v>
       </c>
       <c r="E40">
-        <v>-80.071445</v>
+        <v>-81.787027</v>
       </c>
       <c r="F40">
         <v>2</v>
       </c>
       <c r="G40">
-        <v>2.2288</v>
+        <v>0.4075</v>
       </c>
       <c r="H40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I40">
-        <v>11.0631</v>
+        <v>12.9563</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K40">
-        <v>5.1487</v>
+        <v>2.7243</v>
       </c>
     </row>
     <row r="41">
@@ -2075,34 +2135,34 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>29.705036</v>
+        <v>28.301428</v>
       </c>
       <c r="C41">
-        <v>-84.078274</v>
+        <v>-80.607513</v>
       </c>
       <c r="D41">
-        <v>29.810769</v>
+        <v>28.365526</v>
       </c>
       <c r="E41">
-        <v>-84.60428</v>
+        <v>-80.602357</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="G41">
-        <v>4.1724</v>
+        <v>87.1895</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>413</v>
       </c>
       <c r="I41">
-        <v>0.7874</v>
+        <v>388.5411</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>205</v>
       </c>
       <c r="K41">
-        <v>3.3858</v>
+        <v>192.9147</v>
       </c>
     </row>
     <row r="42">
@@ -2110,34 +2170,34 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>27.392737</v>
+        <v>26.962096</v>
       </c>
       <c r="C42">
-        <v>-82.819417</v>
+        <v>-80.078734</v>
       </c>
       <c r="D42">
-        <v>26.88107</v>
+        <v>26.964525</v>
       </c>
       <c r="E42">
-        <v>-82.334693</v>
+        <v>-80.077626</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G42">
-        <v>1.1507</v>
+        <v>22.279</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I42">
-        <v>0.5221</v>
+        <v>43.0823</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K42">
-        <v>0.5226</v>
+        <v>28.1132</v>
       </c>
     </row>
     <row r="43">
@@ -2145,34 +2205,34 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>27.28603</v>
+        <v>30.299113</v>
       </c>
       <c r="C43">
-        <v>-82.71253</v>
+        <v>-86.084851</v>
       </c>
       <c r="D43">
-        <v>26.83603</v>
+        <v>30.302005</v>
       </c>
       <c r="E43">
-        <v>-82.3091</v>
+        <v>-86.077351</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G43">
-        <v>0.0</v>
+        <v>27.7897</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>0.0</v>
+        <v>1.4875</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>0.5228</v>
+        <v>4.3097</v>
       </c>
     </row>
     <row r="44">
@@ -2180,34 +2240,34 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>18.71833</v>
+        <v>26.258606</v>
       </c>
       <c r="C44">
-        <v>-74.597565</v>
+        <v>-80.080187</v>
       </c>
       <c r="D44">
-        <v>24.655745</v>
+        <v>26.321003</v>
       </c>
       <c r="E44">
-        <v>-82.804445</v>
+        <v>-80.074627</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G44">
-        <v>0.0</v>
+        <v>84.9929</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="I44">
-        <v>3.176</v>
+        <v>86.4979</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="K44">
-        <v>3.176</v>
+        <v>76.7853</v>
       </c>
     </row>
     <row r="45">
@@ -2215,34 +2275,34 @@
         <v>54</v>
       </c>
       <c r="B45">
-        <v>19.55528</v>
+        <v>26.432125</v>
       </c>
       <c r="C45">
-        <v>-73.39391</v>
+        <v>-80.061683</v>
       </c>
       <c r="D45">
-        <v>24.60955</v>
+        <v>26.475839</v>
       </c>
       <c r="E45">
-        <v>-82.87373</v>
+        <v>-80.05518</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G45">
-        <v>0.0</v>
+        <v>30.8862</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="I45">
-        <v>0.2756</v>
+        <v>161.0864</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K45">
-        <v>0.0</v>
+        <v>57.0164</v>
       </c>
     </row>
     <row r="46">
@@ -2250,34 +2310,34 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>19.119672</v>
+        <v>29.777878</v>
       </c>
       <c r="C46">
-        <v>-72.039134</v>
+        <v>-84.674579</v>
       </c>
       <c r="D46">
-        <v>24.62653</v>
+        <v>29.831459</v>
       </c>
       <c r="E46">
-        <v>-82.922776</v>
+        <v>-84.571322</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G46">
-        <v>0.0</v>
+        <v>44.9398</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="I46">
-        <v>8.3585</v>
+        <v>96.8382</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="K46">
-        <v>1.1714</v>
+        <v>43.7284</v>
       </c>
     </row>
     <row r="47">
@@ -2285,34 +2345,34 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>28.02263</v>
+        <v>26.854315</v>
       </c>
       <c r="C47">
-        <v>-82.98172</v>
+        <v>-82.34023</v>
       </c>
       <c r="D47">
-        <v>24.63602</v>
+        <v>26.898362</v>
       </c>
       <c r="E47">
-        <v>-82.82891</v>
+        <v>-82.309733</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G47">
-        <v>0.0</v>
+        <v>47.5544</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I47">
-        <v>0.5508</v>
+        <v>40.1408</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K47">
-        <v>0.0</v>
+        <v>48.0336</v>
       </c>
     </row>
     <row r="48">
@@ -2320,34 +2380,34 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>13.385927</v>
+        <v>26.839618</v>
       </c>
       <c r="C48">
-        <v>-66.633697</v>
+        <v>-82.309733</v>
       </c>
       <c r="D48">
-        <v>25.120997</v>
+        <v>26.854315</v>
       </c>
       <c r="E48">
-        <v>-81.085397</v>
+        <v>-82.29909</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G48">
-        <v>0.0</v>
+        <v>22.0996</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I48">
-        <v>3.3897</v>
+        <v>26.6432</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="K48">
-        <v>0.7779</v>
+        <v>26.0917</v>
       </c>
     </row>
     <row r="49">
@@ -2355,34 +2415,34 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>30.293325</v>
+        <v>24.627182</v>
       </c>
       <c r="C49">
-        <v>-86.887795</v>
+        <v>-82.870286</v>
       </c>
       <c r="D49">
-        <v>30.381395</v>
+        <v>24.628981</v>
       </c>
       <c r="E49">
-        <v>-86.41287</v>
+        <v>-82.862864</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>1.2714</v>
+        <v>0.0</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I49">
-        <v>1.8206</v>
+        <v>23.3912</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K49">
-        <v>0.3974</v>
+        <v>7.6746</v>
       </c>
     </row>
     <row r="50">
@@ -2390,34 +2450,34 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>25.002069</v>
+        <v>24.650283</v>
       </c>
       <c r="C50">
-        <v>-80.173728</v>
+        <v>-82.805685</v>
       </c>
       <c r="D50">
-        <v>30.285022</v>
+        <v>24.652238</v>
       </c>
       <c r="E50">
-        <v>-86.033114</v>
+        <v>-82.80378</v>
       </c>
       <c r="F50">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>18.4038</v>
+        <v>0.0</v>
       </c>
       <c r="H50">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="I50">
-        <v>53.5275</v>
+        <v>82.3827</v>
       </c>
       <c r="J50">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K50">
-        <v>20.567</v>
+        <v>28.3724</v>
       </c>
     </row>
     <row r="51">
@@ -2425,34 +2485,34 @@
         <v>60</v>
       </c>
       <c r="B51">
-        <v>28.918497</v>
+        <v>24.626465</v>
       </c>
       <c r="C51">
-        <v>-85.834832</v>
+        <v>-82.873769</v>
       </c>
       <c r="D51">
-        <v>30.395954</v>
+        <v>24.629947</v>
       </c>
       <c r="E51">
-        <v>-86.537741</v>
+        <v>-82.871633</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>3.8263</v>
+        <v>0.0</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I51">
-        <v>2.224</v>
+        <v>30.8365</v>
       </c>
       <c r="J51">
         <v>12</v>
       </c>
       <c r="K51">
-        <v>5.3392</v>
+        <v>11.8318</v>
       </c>
     </row>
     <row r="52">
@@ -2460,34 +2520,34 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>29.487073</v>
+        <v>24.627791</v>
       </c>
       <c r="C52">
-        <v>-86.010691</v>
+        <v>-82.926027</v>
       </c>
       <c r="D52">
-        <v>30.388822</v>
+        <v>24.637168</v>
       </c>
       <c r="E52">
-        <v>-86.745675</v>
+        <v>-82.91566</v>
       </c>
       <c r="F52">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>8.1597</v>
+        <v>0.0</v>
       </c>
       <c r="H52">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="I52">
-        <v>12.7353</v>
+        <v>76.9241</v>
       </c>
       <c r="J52">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K52">
-        <v>6.5623</v>
+        <v>23.1941</v>
       </c>
     </row>
     <row r="53">
@@ -2495,34 +2555,34 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>30.259566</v>
+        <v>24.624792</v>
       </c>
       <c r="C53">
-        <v>-86.991942</v>
+        <v>-82.863685</v>
       </c>
       <c r="D53">
-        <v>30.387388</v>
+        <v>24.627998</v>
       </c>
       <c r="E53">
-        <v>-86.82572</v>
+        <v>-82.862971</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>2.3232</v>
+        <v>0.0</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I53">
-        <v>2.2811</v>
+        <v>29.358</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K53">
-        <v>1.7117</v>
+        <v>5.4137</v>
       </c>
     </row>
     <row r="54">
@@ -2530,34 +2590,34 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>19.608585</v>
+        <v>24.649752</v>
       </c>
       <c r="C54">
-        <v>-71.54038</v>
+        <v>-82.828681</v>
       </c>
       <c r="D54">
-        <v>26.44804</v>
+        <v>24.650164</v>
       </c>
       <c r="E54">
-        <v>-81.94812</v>
+        <v>-82.827897</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>0.7118</v>
+        <v>0.0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I54">
-        <v>0.0</v>
+        <v>55.1838</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K54">
-        <v>0.5609</v>
+        <v>7.2963</v>
       </c>
     </row>
     <row r="55">
@@ -2565,34 +2625,34 @@
         <v>64</v>
       </c>
       <c r="B55">
-        <v>14.320845</v>
+        <v>25.183351</v>
       </c>
       <c r="C55">
-        <v>-70.455685</v>
+        <v>-81.172075</v>
       </c>
       <c r="D55">
-        <v>24.73304</v>
+        <v>25.24074</v>
       </c>
       <c r="E55">
-        <v>-81.008475</v>
+        <v>-81.141249</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G55">
-        <v>0.0</v>
+        <v>15.6539</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I55">
-        <v>1.3439</v>
+        <v>7.0932</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K55">
-        <v>0.0</v>
+        <v>16.3827</v>
       </c>
     </row>
     <row r="56">
@@ -2600,34 +2660,34 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>26.820345</v>
+        <v>25.116377</v>
       </c>
       <c r="C56">
-        <v>-81.545615</v>
+        <v>-81.141676</v>
       </c>
       <c r="D56">
-        <v>25.76614</v>
+        <v>25.182885</v>
       </c>
       <c r="E56">
-        <v>-80.140655</v>
+        <v>-81.085871</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G56">
-        <v>0.0</v>
+        <v>25.5928</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I56">
-        <v>2.4413</v>
+        <v>27.7897</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K56">
-        <v>1.8908</v>
+        <v>40.4537</v>
       </c>
     </row>
     <row r="57">
@@ -2635,34 +2695,34 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>28.68616</v>
+        <v>30.378838</v>
       </c>
       <c r="C57">
-        <v>-80.687397</v>
+        <v>-86.432605</v>
       </c>
       <c r="D57">
-        <v>29.473343</v>
+        <v>30.382275</v>
       </c>
       <c r="E57">
-        <v>-81.13504</v>
+        <v>-86.397366</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G57">
-        <v>1.9543</v>
+        <v>35.4843</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I57">
-        <v>2.9347</v>
+        <v>48.0136</v>
       </c>
       <c r="J57">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K57">
-        <v>4.9165</v>
+        <v>22.8846</v>
       </c>
     </row>
     <row r="58">
@@ -2670,34 +2730,34 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>29.281253</v>
+        <v>30.269283</v>
       </c>
       <c r="C58">
-        <v>-80.863033</v>
+        <v>-86.077351</v>
       </c>
       <c r="D58">
-        <v>29.43339</v>
+        <v>30.299113</v>
       </c>
       <c r="E58">
-        <v>-81.11238</v>
+        <v>-85.996029</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>391</v>
       </c>
       <c r="G58">
-        <v>1.1561</v>
+        <v>290.4931</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>651</v>
       </c>
       <c r="I58">
-        <v>2.6114</v>
+        <v>496.9559</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>305</v>
       </c>
       <c r="K58">
-        <v>0.3241</v>
+        <v>209.4328</v>
       </c>
     </row>
     <row r="59">
@@ -2705,34 +2765,34 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>30.498952</v>
+        <v>30.385698</v>
       </c>
       <c r="C59">
-        <v>-81.21583</v>
+        <v>-86.582795</v>
       </c>
       <c r="D59">
-        <v>30.706767</v>
+        <v>30.392791</v>
       </c>
       <c r="E59">
-        <v>-81.44644</v>
+        <v>-86.514689</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="G59">
-        <v>1.1373</v>
+        <v>142.2359</v>
       </c>
       <c r="H59">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="I59">
-        <v>7.3169</v>
+        <v>112.2923</v>
       </c>
       <c r="J59">
-        <v>9</v>
+        <v>177</v>
       </c>
       <c r="K59">
-        <v>6.0259</v>
+        <v>137.4729</v>
       </c>
     </row>
     <row r="60">
@@ -2740,34 +2800,34 @@
         <v>69</v>
       </c>
       <c r="B60">
-        <v>28.518651</v>
+        <v>30.386845</v>
       </c>
       <c r="C60">
-        <v>-83.386861</v>
+        <v>-86.799505</v>
       </c>
       <c r="D60">
-        <v>27.61893</v>
+        <v>30.396816</v>
       </c>
       <c r="E60">
-        <v>-82.722491</v>
+        <v>-86.633172</v>
       </c>
       <c r="F60">
-        <v>8</v>
+        <v>344</v>
       </c>
       <c r="G60">
-        <v>5.4166</v>
+        <v>282.6157</v>
       </c>
       <c r="H60">
-        <v>8</v>
+        <v>606</v>
       </c>
       <c r="I60">
-        <v>5.3487</v>
+        <v>478.8735</v>
       </c>
       <c r="J60">
-        <v>8</v>
+        <v>411</v>
       </c>
       <c r="K60">
-        <v>5.1112</v>
+        <v>330.2051</v>
       </c>
     </row>
     <row r="61">
@@ -2775,34 +2835,34 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>22.138435</v>
+        <v>30.381299</v>
       </c>
       <c r="C61">
-        <v>-76.134221</v>
+        <v>-86.849415</v>
       </c>
       <c r="D61">
-        <v>26.134382</v>
+        <v>30.386845</v>
       </c>
       <c r="E61">
-        <v>-80.108122</v>
+        <v>-86.799508</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G61">
-        <v>0.0</v>
+        <v>67.0331</v>
       </c>
       <c r="H61">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I61">
-        <v>17.3898</v>
+        <v>66.299</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="K61">
-        <v>2.5381</v>
+        <v>54.705</v>
       </c>
     </row>
     <row r="62">
@@ -2810,34 +2870,34 @@
         <v>71</v>
       </c>
       <c r="B62">
-        <v>29.087182</v>
+        <v>27.576136</v>
       </c>
       <c r="C62">
-        <v>-80.848585</v>
+        <v>-82.764606</v>
       </c>
       <c r="D62">
-        <v>29.728978</v>
+        <v>27.602885</v>
       </c>
       <c r="E62">
-        <v>-81.238223</v>
+        <v>-82.756223</v>
       </c>
       <c r="F62">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G62">
-        <v>3.4815</v>
+        <v>11.8981</v>
       </c>
       <c r="H62">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I62">
-        <v>11.9885</v>
+        <v>5.4771</v>
       </c>
       <c r="J62">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K62">
-        <v>10.1489</v>
+        <v>10.0271</v>
       </c>
     </row>
     <row r="63">
@@ -2845,34 +2905,34 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>30.31849</v>
+        <v>26.401618</v>
       </c>
       <c r="C63">
-        <v>-81.31372</v>
+        <v>-81.967961</v>
       </c>
       <c r="D63">
-        <v>29.70269</v>
+        <v>26.465528</v>
       </c>
       <c r="E63">
-        <v>-81.23237</v>
+        <v>-81.883451</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G63">
-        <v>1.1653</v>
+        <v>38.0949</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="I63">
-        <v>0.397</v>
+        <v>35.6601</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="K63">
-        <v>0.1634</v>
+        <v>42.969</v>
       </c>
     </row>
     <row r="64">
@@ -2880,34 +2940,34 @@
         <v>73</v>
       </c>
       <c r="B64">
-        <v>15.329615</v>
+        <v>24.723109</v>
       </c>
       <c r="C64">
-        <v>-68.91121</v>
+        <v>-81.011148</v>
       </c>
       <c r="D64">
-        <v>27.47694</v>
+        <v>24.730296</v>
       </c>
       <c r="E64">
-        <v>-80.288975</v>
+        <v>-80.99986</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>2.285</v>
+        <v>0.0</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I64">
-        <v>0.0</v>
+        <v>13.6433</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>0.0</v>
+        <v>6.653</v>
       </c>
     </row>
     <row r="65">
@@ -2915,34 +2975,34 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>17.6671</v>
+        <v>25.755519</v>
       </c>
       <c r="C65">
-        <v>-77.65913</v>
+        <v>-80.139926</v>
       </c>
       <c r="D65">
-        <v>24.55212</v>
+        <v>25.761675</v>
       </c>
       <c r="E65">
-        <v>-81.81744</v>
+        <v>-80.134743</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>0.0</v>
+        <v>2.8542</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I65">
-        <v>0.0</v>
+        <v>49.1277</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K65">
-        <v>0.14</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="66">
@@ -2950,34 +3010,34 @@
         <v>75</v>
       </c>
       <c r="B66">
-        <v>27.272723</v>
+        <v>29.441727</v>
       </c>
       <c r="C66">
-        <v>-82.706923</v>
+        <v>-81.140733</v>
       </c>
       <c r="D66">
-        <v>26.799113</v>
+        <v>29.50915</v>
       </c>
       <c r="E66">
-        <v>-82.273573</v>
+        <v>-81.108693</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="G66">
-        <v>1.5676</v>
+        <v>64.5135</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="I66">
-        <v>0.5217</v>
+        <v>112.2591</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="K66">
-        <v>2.1574</v>
+        <v>90.0582</v>
       </c>
     </row>
     <row r="67">
@@ -2985,34 +3045,34 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>27.28138</v>
+        <v>29.427175</v>
       </c>
       <c r="C67">
-        <v>-82.729337</v>
+        <v>-81.108693</v>
       </c>
       <c r="D67">
-        <v>26.760687</v>
+        <v>29.441727</v>
       </c>
       <c r="E67">
-        <v>-82.255147</v>
+        <v>-81.102132</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G67">
-        <v>1.5642</v>
+        <v>28.3528</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I67">
-        <v>2.5644</v>
+        <v>20.0607</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K67">
-        <v>2.7224</v>
+        <v>17.0458</v>
       </c>
     </row>
     <row r="68">
@@ -3020,34 +3080,34 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>27.89397</v>
+        <v>30.690828</v>
       </c>
       <c r="C68">
-        <v>-82.739285</v>
+        <v>-81.452923</v>
       </c>
       <c r="D68">
-        <v>26.729725</v>
+        <v>30.705343</v>
       </c>
       <c r="E68">
-        <v>-82.253085</v>
+        <v>-81.426224</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="G68">
-        <v>0.6295</v>
+        <v>18.9179</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I68">
-        <v>0.0</v>
+        <v>76.7579</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="K68">
-        <v>0.5597</v>
+        <v>32.5666</v>
       </c>
     </row>
     <row r="69">
@@ -3055,34 +3115,34 @@
         <v>78</v>
       </c>
       <c r="B69">
-        <v>23.967777</v>
+        <v>27.611546</v>
       </c>
       <c r="C69">
-        <v>-78.838113</v>
+        <v>-82.743684</v>
       </c>
       <c r="D69">
-        <v>25.965053</v>
+        <v>27.649488</v>
       </c>
       <c r="E69">
-        <v>-80.120707</v>
+        <v>-82.698404</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G69">
-        <v>0.0</v>
+        <v>83.6209</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="I69">
-        <v>4.1293</v>
+        <v>57.2827</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="K69">
-        <v>0.0</v>
+        <v>80.415</v>
       </c>
     </row>
     <row r="70">
@@ -3090,34 +3150,34 @@
         <v>79</v>
       </c>
       <c r="B70">
-        <v>24.765434</v>
+        <v>26.095216</v>
       </c>
       <c r="C70">
-        <v>-79.99366</v>
+        <v>-80.104917</v>
       </c>
       <c r="D70">
-        <v>30.318578</v>
+        <v>26.189484</v>
       </c>
       <c r="E70">
-        <v>-86.17008</v>
+        <v>-80.094827</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G70">
-        <v>3.948</v>
+        <v>12.8059</v>
       </c>
       <c r="H70">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="I70">
-        <v>10.1988</v>
+        <v>324.3045</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="K70">
-        <v>3.3169</v>
+        <v>92.1166</v>
       </c>
     </row>
     <row r="71">
@@ -3125,34 +3185,34 @@
         <v>80</v>
       </c>
       <c r="B71">
-        <v>28.20842</v>
+        <v>29.706026</v>
       </c>
       <c r="C71">
-        <v>-80.502195</v>
+        <v>-81.251455</v>
       </c>
       <c r="D71">
-        <v>30.060255</v>
+        <v>29.769412</v>
       </c>
       <c r="E71">
-        <v>-81.338105</v>
+        <v>-81.227273</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="G71">
-        <v>0.635</v>
+        <v>33.8225</v>
       </c>
       <c r="H71">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="I71">
-        <v>8.3292</v>
+        <v>130.9647</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="K71">
-        <v>3.7331</v>
+        <v>80.8811</v>
       </c>
     </row>
     <row r="72">
@@ -3160,34 +3220,34 @@
         <v>81</v>
       </c>
       <c r="B72">
-        <v>27.531132</v>
+        <v>29.670856</v>
       </c>
       <c r="C72">
-        <v>-80.300959</v>
+        <v>-81.227516</v>
       </c>
       <c r="D72">
-        <v>30.095355</v>
+        <v>29.704203</v>
       </c>
       <c r="E72">
-        <v>-81.346714</v>
+        <v>-81.213123</v>
       </c>
       <c r="F72">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G72">
-        <v>6.7288</v>
+        <v>19.028</v>
       </c>
       <c r="H72">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="I72">
-        <v>4.9044</v>
+        <v>25.7909</v>
       </c>
       <c r="J72">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K72">
-        <v>3.6998</v>
+        <v>15.5731</v>
       </c>
     </row>
     <row r="73">
@@ -3195,34 +3255,34 @@
         <v>82</v>
       </c>
       <c r="B73">
-        <v>26.248169</v>
+        <v>27.473341</v>
       </c>
       <c r="C73">
-        <v>-82.418974</v>
+        <v>-80.29316</v>
       </c>
       <c r="D73">
-        <v>30.322644</v>
+        <v>27.479237</v>
       </c>
       <c r="E73">
-        <v>-87.234908</v>
+        <v>-80.289727</v>
       </c>
       <c r="F73">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G73">
-        <v>12.142</v>
+        <v>10.5337</v>
       </c>
       <c r="H73">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>7.8212</v>
+        <v>1.7225</v>
       </c>
       <c r="J73">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>8.3952</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -3230,34 +3290,34 @@
         <v>83</v>
       </c>
       <c r="B74">
-        <v>27.626522</v>
+        <v>24.545158</v>
       </c>
       <c r="C74">
-        <v>-83.376777</v>
+        <v>-81.81241</v>
       </c>
       <c r="D74">
-        <v>30.305155</v>
+        <v>24.545715</v>
       </c>
       <c r="E74">
-        <v>-87.360523</v>
+        <v>-81.80826</v>
       </c>
       <c r="F74">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>8.136</v>
+        <v>1.0928</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>1.1939</v>
+        <v>0.0</v>
       </c>
       <c r="J74">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K74">
-        <v>7.2949</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="75">
@@ -3265,34 +3325,34 @@
         <v>84</v>
       </c>
       <c r="B75">
-        <v>26.252148</v>
+        <v>26.789695</v>
       </c>
       <c r="C75">
-        <v>-82.554796</v>
+        <v>-82.284726</v>
       </c>
       <c r="D75">
-        <v>30.359138</v>
+        <v>26.811035</v>
       </c>
       <c r="E75">
-        <v>-86.998106</v>
+        <v>-82.272083</v>
       </c>
       <c r="F75">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G75">
-        <v>7.3633</v>
+        <v>37.8111</v>
       </c>
       <c r="H75">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I75">
-        <v>2.6326</v>
+        <v>11.6028</v>
       </c>
       <c r="J75">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="K75">
-        <v>8.9392</v>
+        <v>62.6296</v>
       </c>
     </row>
     <row r="76">
@@ -3300,34 +3360,34 @@
         <v>85</v>
       </c>
       <c r="B76">
-        <v>18.382107</v>
+        <v>26.727356</v>
       </c>
       <c r="C76">
-        <v>-75.508907</v>
+        <v>-82.272327</v>
       </c>
       <c r="D76">
-        <v>26.488937</v>
+        <v>26.789801</v>
       </c>
       <c r="E76">
-        <v>-80.054003</v>
+        <v>-82.263341</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="G76">
-        <v>2.5085</v>
+        <v>47.0998</v>
       </c>
       <c r="H76">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="I76">
-        <v>14.3193</v>
+        <v>36.0403</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="K76">
-        <v>3.4112</v>
+        <v>41.4316</v>
       </c>
     </row>
     <row r="77">
@@ -3335,34 +3395,34 @@
         <v>86</v>
       </c>
       <c r="B77">
-        <v>22.07218</v>
+        <v>26.716952</v>
       </c>
       <c r="C77">
-        <v>-77.255775</v>
+        <v>-82.264179</v>
       </c>
       <c r="D77">
-        <v>26.50628</v>
+        <v>26.743514</v>
       </c>
       <c r="E77">
-        <v>-80.05522</v>
+        <v>-82.259204</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G77">
-        <v>0.0</v>
+        <v>10.0045</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0.8942</v>
+        <v>1.4112</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K77">
-        <v>0.6897</v>
+        <v>3.2535</v>
       </c>
     </row>
     <row r="78">
@@ -3370,34 +3430,34 @@
         <v>87</v>
       </c>
       <c r="B78">
-        <v>25.746573</v>
+        <v>25.957123</v>
       </c>
       <c r="C78">
-        <v>-79.64398</v>
+        <v>-80.118665</v>
       </c>
       <c r="D78">
-        <v>30.37078</v>
+        <v>25.975188</v>
       </c>
       <c r="E78">
-        <v>-81.40559</v>
+        <v>-80.118184</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78">
-        <v>0.0</v>
+        <v>1.381</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I78">
-        <v>5.0045</v>
+        <v>29.9588</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K78">
-        <v>4.8421</v>
+        <v>40.1768</v>
       </c>
     </row>
     <row r="79">
@@ -3405,34 +3465,34 @@
         <v>88</v>
       </c>
       <c r="B79">
-        <v>29.224907</v>
+        <v>30.321217</v>
       </c>
       <c r="C79">
-        <v>-86.122753</v>
+        <v>-86.179915</v>
       </c>
       <c r="D79">
-        <v>30.381997</v>
+        <v>30.331686</v>
       </c>
       <c r="E79">
-        <v>-86.447417</v>
+        <v>-86.146185</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="G79">
-        <v>1.2207</v>
+        <v>87.0382</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>238</v>
       </c>
       <c r="I79">
-        <v>5.0282</v>
+        <v>214.7108</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="K79">
-        <v>1.0027</v>
+        <v>86.3653</v>
       </c>
     </row>
     <row r="80">
@@ -3440,34 +3500,34 @@
         <v>89</v>
       </c>
       <c r="B80">
-        <v>22.799713</v>
+        <v>30.02263</v>
       </c>
       <c r="C80">
-        <v>-76.354445</v>
+        <v>-81.333119</v>
       </c>
       <c r="D80">
-        <v>26.402917</v>
+        <v>30.068365</v>
       </c>
       <c r="E80">
-        <v>-80.070788</v>
+        <v>-81.322754</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G80">
-        <v>8.2774</v>
+        <v>48.4978</v>
       </c>
       <c r="H80">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="I80">
-        <v>11.6736</v>
+        <v>108.0059</v>
       </c>
       <c r="J80">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="K80">
-        <v>6.6405</v>
+        <v>40.5279</v>
       </c>
     </row>
     <row r="81">
@@ -3475,34 +3535,34 @@
         <v>90</v>
       </c>
       <c r="B81">
-        <v>17.878658</v>
+        <v>30.068365</v>
       </c>
       <c r="C81">
-        <v>-70.985446</v>
+        <v>-81.34714</v>
       </c>
       <c r="D81">
-        <v>27.111165</v>
+        <v>30.127155</v>
       </c>
       <c r="E81">
-        <v>-80.143261</v>
+        <v>-81.333119</v>
       </c>
       <c r="F81">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G81">
-        <v>21.3985</v>
+        <v>87.9114</v>
       </c>
       <c r="H81">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="I81">
-        <v>37.9592</v>
+        <v>97.9774</v>
       </c>
       <c r="J81">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="K81">
-        <v>16.8753</v>
+        <v>71.9294</v>
       </c>
     </row>
     <row r="82">
@@ -3510,34 +3570,34 @@
         <v>91</v>
       </c>
       <c r="B82">
-        <v>20.163883</v>
+        <v>30.316263</v>
       </c>
       <c r="C82">
-        <v>-75.257109</v>
+        <v>-87.303221</v>
       </c>
       <c r="D82">
-        <v>26.022062</v>
+        <v>30.330977</v>
       </c>
       <c r="E82">
-        <v>-80.11724</v>
+        <v>-87.181147</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="G82">
-        <v>0.0</v>
+        <v>288.2442</v>
       </c>
       <c r="H82">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="I82">
-        <v>27.4294</v>
+        <v>238.9767</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="K82">
-        <v>1.8898</v>
+        <v>232.1469</v>
       </c>
     </row>
     <row r="83">
@@ -3545,34 +3605,34 @@
         <v>92</v>
       </c>
       <c r="B83">
-        <v>28.007927</v>
+        <v>30.297552</v>
       </c>
       <c r="C83">
-        <v>-82.931538</v>
+        <v>-87.419571</v>
       </c>
       <c r="D83">
-        <v>28.081362</v>
+        <v>30.326033</v>
       </c>
       <c r="E83">
-        <v>-82.827018</v>
+        <v>-87.311957</v>
       </c>
       <c r="F83">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="G83">
-        <v>4.7833</v>
+        <v>311.2411</v>
       </c>
       <c r="H83">
-        <v>3</v>
+        <v>370</v>
       </c>
       <c r="I83">
-        <v>1.6723</v>
+        <v>288.1684</v>
       </c>
       <c r="J83">
-        <v>9</v>
+        <v>371</v>
       </c>
       <c r="K83">
-        <v>6.2359</v>
+        <v>279.3695</v>
       </c>
     </row>
     <row r="84">
@@ -3580,34 +3640,34 @@
         <v>93</v>
       </c>
       <c r="B84">
-        <v>30.08469</v>
+        <v>30.347202</v>
       </c>
       <c r="C84">
-        <v>-81.18819</v>
+        <v>-87.053055</v>
       </c>
       <c r="D84">
-        <v>30.39972</v>
+        <v>30.371015</v>
       </c>
       <c r="E84">
-        <v>-81.41105</v>
+        <v>-86.918748</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="G84">
-        <v>0.4432</v>
+        <v>144.8703</v>
       </c>
       <c r="H84">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="I84">
-        <v>2.9652</v>
+        <v>85.4534</v>
       </c>
       <c r="J84">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="K84">
-        <v>2.6863</v>
+        <v>108.6688</v>
       </c>
     </row>
     <row r="85">
@@ -3615,34 +3675,34 @@
         <v>94</v>
       </c>
       <c r="B85">
-        <v>22.082546</v>
+        <v>26.475839</v>
       </c>
       <c r="C85">
-        <v>-76.058949</v>
+        <v>-80.05518</v>
       </c>
       <c r="D85">
-        <v>27.205478</v>
+        <v>26.499028</v>
       </c>
       <c r="E85">
-        <v>-80.176595</v>
+        <v>-80.051971</v>
       </c>
       <c r="F85">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G85">
-        <v>22.5561</v>
+        <v>8.7308</v>
       </c>
       <c r="H85">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="I85">
-        <v>22.5351</v>
+        <v>76.2851</v>
       </c>
       <c r="J85">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K85">
-        <v>49.6239</v>
+        <v>36.7055</v>
       </c>
     </row>
     <row r="86">
@@ -3650,34 +3710,34 @@
         <v>95</v>
       </c>
       <c r="B86">
-        <v>19.6453</v>
+        <v>26.504213</v>
       </c>
       <c r="C86">
-        <v>-72.565709</v>
+        <v>-80.051392</v>
       </c>
       <c r="D86">
-        <v>27.352113</v>
+        <v>26.507469</v>
       </c>
       <c r="E86">
-        <v>-80.248279</v>
+        <v>-80.050739</v>
       </c>
       <c r="F86">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>46.1029</v>
+        <v>0.0</v>
       </c>
       <c r="H86">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I86">
-        <v>78.9661</v>
+        <v>15.6785</v>
       </c>
       <c r="J86">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="K86">
-        <v>94.2636</v>
+        <v>3.7004</v>
       </c>
     </row>
     <row r="87">
@@ -3685,34 +3745,34 @@
         <v>96</v>
       </c>
       <c r="B87">
-        <v>19.932356</v>
+        <v>30.36041</v>
       </c>
       <c r="C87">
-        <v>-73.774037</v>
+        <v>-81.397517</v>
       </c>
       <c r="D87">
-        <v>27.721909</v>
+        <v>30.381827</v>
       </c>
       <c r="E87">
-        <v>-80.370017</v>
+        <v>-81.396394</v>
       </c>
       <c r="F87">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G87">
-        <v>11.4935</v>
+        <v>14.2268</v>
       </c>
       <c r="H87">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I87">
-        <v>6.3422</v>
+        <v>17.0324</v>
       </c>
       <c r="J87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K87">
-        <v>5.2613</v>
+        <v>12.1286</v>
       </c>
     </row>
     <row r="88">
@@ -3720,34 +3780,34 @@
         <v>97</v>
       </c>
       <c r="B88">
-        <v>27.97866</v>
+        <v>30.382275</v>
       </c>
       <c r="C88">
-        <v>-82.97986</v>
+        <v>-86.453631</v>
       </c>
       <c r="D88">
-        <v>27.74798</v>
+        <v>30.383355</v>
       </c>
       <c r="E88">
-        <v>-80.4003</v>
+        <v>-86.432605</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G88">
-        <v>0.0</v>
+        <v>27.3017</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I88">
-        <v>0.0</v>
+        <v>43.0755</v>
       </c>
       <c r="J88">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K88">
-        <v>0.4558</v>
+        <v>16.7556</v>
       </c>
     </row>
     <row r="89">
@@ -3755,34 +3815,34 @@
         <v>98</v>
       </c>
       <c r="B89">
-        <v>21.552317</v>
+        <v>26.39088</v>
       </c>
       <c r="C89">
-        <v>-74.748739</v>
+        <v>-80.066179</v>
       </c>
       <c r="D89">
-        <v>28.389107</v>
+        <v>26.432125</v>
       </c>
       <c r="E89">
-        <v>-80.595613</v>
+        <v>-80.061683</v>
       </c>
       <c r="F89">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="G89">
-        <v>10.2786</v>
+        <v>125.3211</v>
       </c>
       <c r="H89">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="I89">
-        <v>29.3732</v>
+        <v>183.1151</v>
       </c>
       <c r="J89">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="K89">
-        <v>22.5304</v>
+        <v>112.5033</v>
       </c>
     </row>
     <row r="90">
@@ -3790,34 +3850,34 @@
         <v>99</v>
       </c>
       <c r="B90">
-        <v>26.124925</v>
+        <v>27.086369</v>
       </c>
       <c r="C90">
-        <v>-79.997825</v>
+        <v>-80.145245</v>
       </c>
       <c r="D90">
-        <v>26.82763</v>
+        <v>27.130719</v>
       </c>
       <c r="E90">
-        <v>-80.051965</v>
+        <v>-80.124855</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="G90">
-        <v>0.0</v>
+        <v>341.4172</v>
       </c>
       <c r="H90">
-        <v>2</v>
+        <v>483</v>
       </c>
       <c r="I90">
-        <v>1.8106</v>
+        <v>504.7825</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="K90">
-        <v>1.4148</v>
+        <v>367.1235</v>
       </c>
     </row>
     <row r="91">
@@ -3825,34 +3885,34 @@
         <v>100</v>
       </c>
       <c r="B91">
-        <v>22.721638</v>
+        <v>25.975183</v>
       </c>
       <c r="C91">
-        <v>-77.156348</v>
+        <v>-80.118268</v>
       </c>
       <c r="D91">
-        <v>26.077926</v>
+        <v>26.060435</v>
       </c>
       <c r="E91">
-        <v>-80.113752</v>
+        <v>-80.111383</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G91">
-        <v>0.0</v>
+        <v>16.4031</v>
       </c>
       <c r="H91">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="I91">
-        <v>9.6274</v>
+        <v>250.8959</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="K91">
-        <v>0.0723</v>
+        <v>63.3383</v>
       </c>
     </row>
     <row r="92">
@@ -3860,34 +3920,34 @@
         <v>101</v>
       </c>
       <c r="B92">
-        <v>18.219414</v>
+        <v>28.053887</v>
       </c>
       <c r="C92">
-        <v>-72.340588</v>
+        <v>-82.837153</v>
       </c>
       <c r="D92">
-        <v>26.927728</v>
+        <v>28.097694</v>
       </c>
       <c r="E92">
-        <v>-80.080676</v>
+        <v>-82.815445</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G92">
-        <v>2.931</v>
+        <v>62.5353</v>
       </c>
       <c r="H92">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="I92">
-        <v>5.8899</v>
+        <v>24.2896</v>
       </c>
       <c r="J92">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="K92">
-        <v>1.2289</v>
+        <v>84.4069</v>
       </c>
     </row>
     <row r="93">
@@ -3895,34 +3955,34 @@
         <v>102</v>
       </c>
       <c r="B93">
-        <v>20.647836</v>
+        <v>30.403573</v>
       </c>
       <c r="C93">
-        <v>-73.23331</v>
+        <v>-81.41191</v>
       </c>
       <c r="D93">
-        <v>26.947858</v>
+        <v>30.420145</v>
       </c>
       <c r="E93">
-        <v>-80.073232</v>
+        <v>-81.402772</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G93">
-        <v>3.8158</v>
+        <v>26.3069</v>
       </c>
       <c r="H93">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I93">
-        <v>3.6008</v>
+        <v>57.0934</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="K93">
-        <v>3.0006</v>
+        <v>25.1764</v>
       </c>
     </row>
     <row r="94">
@@ -3930,34 +3990,34 @@
         <v>103</v>
       </c>
       <c r="B94">
-        <v>19.95367</v>
+        <v>27.168196</v>
       </c>
       <c r="C94">
-        <v>-73.682104</v>
+        <v>-80.199813</v>
       </c>
       <c r="D94">
-        <v>27.023941</v>
+        <v>27.262886</v>
       </c>
       <c r="E94">
-        <v>-80.099236</v>
+        <v>-80.153176</v>
       </c>
       <c r="F94">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="G94">
-        <v>49.359</v>
+        <v>205.1433</v>
       </c>
       <c r="H94">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="I94">
-        <v>73.4668</v>
+        <v>196.8946</v>
       </c>
       <c r="J94">
-        <v>51</v>
+        <v>300</v>
       </c>
       <c r="K94">
-        <v>49.4105</v>
+        <v>322.2482</v>
       </c>
     </row>
     <row r="95">
@@ -3965,34 +4025,34 @@
         <v>104</v>
       </c>
       <c r="B95">
-        <v>14.001112</v>
+        <v>27.262886</v>
       </c>
       <c r="C95">
-        <v>-66.894578</v>
+        <v>-80.290417</v>
       </c>
       <c r="D95">
-        <v>26.900974</v>
+        <v>27.470656</v>
       </c>
       <c r="E95">
-        <v>-80.075268</v>
+        <v>-80.199813</v>
       </c>
       <c r="F95">
-        <v>5</v>
+        <v>440</v>
       </c>
       <c r="G95">
-        <v>9.494</v>
+        <v>458.7624</v>
       </c>
       <c r="H95">
-        <v>9</v>
+        <v>778</v>
       </c>
       <c r="I95">
-        <v>7.7194</v>
+        <v>732.3845</v>
       </c>
       <c r="J95">
-        <v>3</v>
+        <v>719</v>
       </c>
       <c r="K95">
-        <v>8.1574</v>
+        <v>718.437</v>
       </c>
     </row>
     <row r="96">
@@ -4000,34 +4060,34 @@
         <v>105</v>
       </c>
       <c r="B96">
-        <v>26.69277</v>
+        <v>27.674945</v>
       </c>
       <c r="C96">
-        <v>-82.41451</v>
+        <v>-80.389043</v>
       </c>
       <c r="D96">
-        <v>26.06122</v>
+        <v>27.750635</v>
       </c>
       <c r="E96">
-        <v>-81.78471</v>
+        <v>-80.361754</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="G96">
-        <v>0.2098</v>
+        <v>77.4281</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="I96">
-        <v>0.2096</v>
+        <v>56.7363</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="K96">
-        <v>0.21</v>
+        <v>49.2771</v>
       </c>
     </row>
     <row r="97">
@@ -4035,34 +4095,34 @@
         <v>106</v>
       </c>
       <c r="B97">
-        <v>26.31733</v>
+        <v>27.750635</v>
       </c>
       <c r="C97">
-        <v>-81.99976</v>
+        <v>-80.392673</v>
       </c>
       <c r="D97">
-        <v>25.99796</v>
+        <v>27.756911</v>
       </c>
       <c r="E97">
-        <v>-81.76356</v>
+        <v>-80.389043</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G97">
-        <v>0.5569</v>
+        <v>6.3395</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I97">
-        <v>0.5528</v>
+        <v>12.5653</v>
       </c>
       <c r="J97">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K97">
-        <v>0.5558</v>
+        <v>11.2659</v>
       </c>
     </row>
     <row r="98">
@@ -4070,34 +4130,34 @@
         <v>107</v>
       </c>
       <c r="B98">
-        <v>10.77536</v>
+        <v>28.365526</v>
       </c>
       <c r="C98">
-        <v>-63.77929</v>
+        <v>-80.602357</v>
       </c>
       <c r="D98">
-        <v>25.71216</v>
+        <v>28.407953</v>
       </c>
       <c r="E98">
-        <v>-80.15526</v>
+        <v>-80.588541</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="G98">
-        <v>2.422</v>
+        <v>140.8981</v>
       </c>
       <c r="H98">
-        <v>17</v>
+        <v>546</v>
       </c>
       <c r="I98">
-        <v>25.8257</v>
+        <v>488.3967</v>
       </c>
       <c r="J98">
-        <v>4</v>
+        <v>330</v>
       </c>
       <c r="K98">
-        <v>10.8613</v>
+        <v>283.009</v>
       </c>
     </row>
     <row r="99">
@@ -4105,34 +4165,34 @@
         <v>108</v>
       </c>
       <c r="B99">
-        <v>24.74991</v>
+        <v>26.812955</v>
       </c>
       <c r="C99">
-        <v>-81.06472</v>
+        <v>-80.041275</v>
       </c>
       <c r="D99">
-        <v>24.70279</v>
+        <v>26.8362</v>
       </c>
       <c r="E99">
-        <v>-81.020685</v>
+        <v>-80.035049</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99">
-        <v>0.0</v>
+        <v>3.9701</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I99">
-        <v>0.0</v>
+        <v>53.6138</v>
       </c>
       <c r="J99">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K99">
-        <v>0.1347</v>
+        <v>17.5628</v>
       </c>
     </row>
     <row r="100">
@@ -4140,34 +4200,34 @@
         <v>109</v>
       </c>
       <c r="B100">
-        <v>26.06869</v>
+        <v>26.060435</v>
       </c>
       <c r="C100">
-        <v>-79.97971</v>
+        <v>-80.111383</v>
       </c>
       <c r="D100">
-        <v>26.61652</v>
+        <v>26.092243</v>
       </c>
       <c r="E100">
-        <v>-80.02753</v>
+        <v>-80.108148</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G100">
-        <v>0.0</v>
+        <v>4.5315</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I100">
-        <v>0.0</v>
+        <v>77.7555</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K100">
-        <v>0.3979</v>
+        <v>11.1618</v>
       </c>
     </row>
     <row r="101">
@@ -4175,34 +4235,34 @@
         <v>110</v>
       </c>
       <c r="B101">
-        <v>19.31965</v>
+        <v>26.920498</v>
       </c>
       <c r="C101">
-        <v>-74.799667</v>
+        <v>-80.071844</v>
       </c>
       <c r="D101">
-        <v>26.774033</v>
+        <v>26.943588</v>
       </c>
       <c r="E101">
-        <v>-80.047887</v>
+        <v>-80.06538</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G101">
-        <v>0.0</v>
+        <v>153.4766</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="I101">
-        <v>1.1105</v>
+        <v>85.5474</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K101">
-        <v>0.0</v>
+        <v>73.3593</v>
       </c>
     </row>
     <row r="102">
@@ -4210,34 +4270,34 @@
         <v>111</v>
       </c>
       <c r="B102">
-        <v>18.22584</v>
+        <v>26.944725</v>
       </c>
       <c r="C102">
-        <v>-68.92576</v>
+        <v>-80.076245</v>
       </c>
       <c r="D102">
-        <v>26.61443</v>
+        <v>26.956523</v>
       </c>
       <c r="E102">
-        <v>-80.04101</v>
+        <v>-80.071129</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="G102">
-        <v>0.9893</v>
+        <v>80.9969</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I102">
-        <v>0.0</v>
+        <v>95.1126</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="K102">
-        <v>0.0</v>
+        <v>117.1253</v>
       </c>
     </row>
     <row r="103">
@@ -4245,34 +4305,34 @@
         <v>112</v>
       </c>
       <c r="B103">
-        <v>10.43846</v>
+        <v>26.970431</v>
       </c>
       <c r="C103">
-        <v>-61.56311</v>
+        <v>-80.124855</v>
       </c>
       <c r="D103">
-        <v>26.58463</v>
+        <v>27.086369</v>
       </c>
       <c r="E103">
-        <v>-80.03719</v>
+        <v>-80.080544</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="G103">
-        <v>0.8609</v>
+        <v>457.454</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>762</v>
       </c>
       <c r="I103">
-        <v>1.4576</v>
+        <v>757.9071</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="K103">
-        <v>0.0</v>
+        <v>644.1255</v>
       </c>
     </row>
     <row r="104">
@@ -4280,34 +4340,34 @@
         <v>113</v>
       </c>
       <c r="B104">
-        <v>26.92838</v>
+        <v>26.8362</v>
       </c>
       <c r="C104">
-        <v>-82.54836</v>
+        <v>-80.065425</v>
       </c>
       <c r="D104">
-        <v>27.313695</v>
+        <v>26.920498</v>
       </c>
       <c r="E104">
-        <v>-82.58234</v>
+        <v>-80.041275</v>
       </c>
       <c r="F104">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="G104">
-        <v>0.383</v>
+        <v>82.9461</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="I104">
-        <v>0.0</v>
+        <v>217.1604</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="K104">
-        <v>0.0</v>
+        <v>151.6636</v>
       </c>
     </row>
     <row r="105">
@@ -4315,34 +4375,34 @@
         <v>114</v>
       </c>
       <c r="B105">
-        <v>19.99364</v>
+        <v>26.046951</v>
       </c>
       <c r="C105">
-        <v>-78.289394</v>
+        <v>-81.801747</v>
       </c>
       <c r="D105">
-        <v>24.74146</v>
+        <v>26.091797</v>
       </c>
       <c r="E105">
-        <v>-80.981738</v>
+        <v>-81.780744</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G105">
-        <v>0.0</v>
+        <v>6.192</v>
       </c>
       <c r="H105">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I105">
-        <v>9.8887</v>
+        <v>5.5853</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K105">
-        <v>0.0</v>
+        <v>11.8925</v>
       </c>
     </row>
     <row r="106">
@@ -4350,34 +4410,34 @@
         <v>115</v>
       </c>
       <c r="B106">
-        <v>26.57807</v>
+        <v>25.991501</v>
       </c>
       <c r="C106">
-        <v>-80.028196</v>
+        <v>-81.780744</v>
       </c>
       <c r="D106">
-        <v>30.44874</v>
+        <v>26.046951</v>
       </c>
       <c r="E106">
-        <v>-81.414926</v>
+        <v>-81.750811</v>
       </c>
       <c r="F106">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G106">
-        <v>9.9652</v>
+        <v>5.3143</v>
       </c>
       <c r="H106">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I106">
-        <v>5.6444</v>
+        <v>2.0042</v>
       </c>
       <c r="J106">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K106">
-        <v>4.3071</v>
+        <v>2.9696</v>
       </c>
     </row>
     <row r="107">
@@ -4385,34 +4445,34 @@
         <v>116</v>
       </c>
       <c r="B107">
-        <v>17.73373</v>
+        <v>25.683025</v>
       </c>
       <c r="C107">
-        <v>-76.66655</v>
+        <v>-80.156615</v>
       </c>
       <c r="D107">
-        <v>24.80034</v>
+        <v>25.726385</v>
       </c>
       <c r="E107">
-        <v>-80.82759</v>
+        <v>-80.147569</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G107">
-        <v>0.0</v>
+        <v>42.0455</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="I107">
-        <v>0.529</v>
+        <v>414.3674</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="K107">
-        <v>0.4182</v>
+        <v>109.2393</v>
       </c>
     </row>
     <row r="108">
@@ -4420,34 +4480,34 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>26.88963</v>
+        <v>24.716408</v>
       </c>
       <c r="C108">
-        <v>-82.46188</v>
+        <v>-81.023781</v>
       </c>
       <c r="D108">
-        <v>27.39088</v>
+        <v>24.721795</v>
       </c>
       <c r="E108">
-        <v>-82.64538</v>
+        <v>-81.01195</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>1.0156</v>
+        <v>0.0</v>
       </c>
       <c r="H108">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I108">
-        <v>1.9694</v>
+        <v>14.8763</v>
       </c>
       <c r="J108">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K108">
-        <v>3.5116</v>
+        <v>3.4258</v>
       </c>
     </row>
     <row r="109">
@@ -4455,34 +4515,34 @@
         <v>118</v>
       </c>
       <c r="B109">
-        <v>26.84659</v>
+        <v>26.615228</v>
       </c>
       <c r="C109">
-        <v>-82.47634</v>
+        <v>-80.036623</v>
       </c>
       <c r="D109">
-        <v>27.33839</v>
+        <v>26.616837</v>
       </c>
       <c r="E109">
-        <v>-82.60776</v>
+        <v>-80.036566</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109">
-        <v>1.0156</v>
+        <v>0.3533</v>
       </c>
       <c r="H109">
         <v>5</v>
       </c>
       <c r="I109">
-        <v>3.7794</v>
+        <v>5.1097</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K109">
-        <v>1.016</v>
+        <v>1.7445</v>
       </c>
     </row>
     <row r="110">
@@ -4490,34 +4550,34 @@
         <v>119</v>
       </c>
       <c r="B110">
-        <v>19.085225</v>
+        <v>26.761576</v>
       </c>
       <c r="C110">
-        <v>-73.29479</v>
+        <v>-80.036975</v>
       </c>
       <c r="D110">
-        <v>24.88245</v>
+        <v>26.771253</v>
       </c>
       <c r="E110">
-        <v>-80.70136</v>
+        <v>-80.035226</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>2.2509</v>
+        <v>0.3753</v>
       </c>
       <c r="H110">
+        <v>56</v>
+      </c>
+      <c r="I110">
+        <v>51.0617</v>
+      </c>
+      <c r="J110">
         <v>9</v>
       </c>
-      <c r="I110">
-        <v>10.5344</v>
-      </c>
-      <c r="J110">
-        <v>3</v>
-      </c>
       <c r="K110">
-        <v>0.9077</v>
+        <v>13.7598</v>
       </c>
     </row>
     <row r="111">
@@ -4525,34 +4585,34 @@
         <v>120</v>
       </c>
       <c r="B111">
-        <v>10.92409</v>
+        <v>26.611645</v>
       </c>
       <c r="C111">
-        <v>-64.44888</v>
+        <v>-80.036578</v>
       </c>
       <c r="D111">
-        <v>26.54556</v>
+        <v>26.615371</v>
       </c>
       <c r="E111">
-        <v>-80.03527</v>
+        <v>-80.036476</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111">
-        <v>0.0949</v>
+        <v>0.9893</v>
       </c>
       <c r="H111">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I111">
-        <v>9.6579</v>
+        <v>13.1912</v>
       </c>
       <c r="J111">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K111">
-        <v>3.5344</v>
+        <v>9.4445</v>
       </c>
     </row>
     <row r="112">
@@ -4560,34 +4620,34 @@
         <v>121</v>
       </c>
       <c r="B112">
-        <v>27.28293</v>
+        <v>26.583951</v>
       </c>
       <c r="C112">
-        <v>-82.68399</v>
+        <v>-80.037684</v>
       </c>
       <c r="D112">
-        <v>26.93616</v>
+        <v>26.585991</v>
       </c>
       <c r="E112">
-        <v>-82.3506</v>
+        <v>-80.037489</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112">
-        <v>0.5224</v>
+        <v>0.8609</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I112">
-        <v>0.6726</v>
+        <v>22.9411</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K112">
-        <v>0.5223</v>
+        <v>8.9136</v>
       </c>
     </row>
     <row r="113">
@@ -4595,34 +4655,34 @@
         <v>122</v>
       </c>
       <c r="B113">
-        <v>27.162435</v>
+        <v>27.297346</v>
       </c>
       <c r="C113">
-        <v>-82.655845</v>
+        <v>-82.588734</v>
       </c>
       <c r="D113">
-        <v>26.991765</v>
+        <v>27.326704</v>
       </c>
       <c r="E113">
-        <v>-82.410485</v>
+        <v>-82.564267</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G113">
-        <v>0.6077</v>
+        <v>46.6121</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="I113">
-        <v>1.0223</v>
+        <v>41.2399</v>
       </c>
       <c r="J113">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="K113">
-        <v>1.2666</v>
+        <v>40.9011</v>
       </c>
     </row>
     <row r="114">
@@ -4630,34 +4690,34 @@
         <v>123</v>
       </c>
       <c r="B114">
-        <v>26.330787</v>
+        <v>24.739786</v>
       </c>
       <c r="C114">
-        <v>-82.001883</v>
+        <v>-80.983473</v>
       </c>
       <c r="D114">
-        <v>25.92131</v>
+        <v>24.741487</v>
       </c>
       <c r="E114">
-        <v>-81.745853</v>
+        <v>-80.979912</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114">
-        <v>0.0</v>
+        <v>0.7182</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I114">
-        <v>0.0</v>
+        <v>38.0552</v>
       </c>
       <c r="J114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K114">
-        <v>1.6677</v>
+        <v>5.4109</v>
       </c>
     </row>
     <row r="115">
@@ -4665,34 +4725,34 @@
         <v>124</v>
       </c>
       <c r="B115">
-        <v>30.33047</v>
+        <v>26.815736</v>
       </c>
       <c r="C115">
-        <v>-81.190247</v>
+        <v>-82.299089</v>
       </c>
       <c r="D115">
-        <v>29.645618</v>
+        <v>26.839618</v>
       </c>
       <c r="E115">
-        <v>-81.210487</v>
+        <v>-82.281293</v>
       </c>
       <c r="F115">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G115">
-        <v>2.6818</v>
+        <v>23.9008</v>
       </c>
       <c r="H115">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I115">
-        <v>4.2347</v>
+        <v>10.0216</v>
       </c>
       <c r="J115">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K115">
-        <v>4.1647</v>
+        <v>16.8452</v>
       </c>
     </row>
     <row r="116">
@@ -4700,34 +4760,34 @@
         <v>125</v>
       </c>
       <c r="B116">
-        <v>24.455757</v>
+        <v>30.426483</v>
       </c>
       <c r="C116">
-        <v>-80.235618</v>
+        <v>-81.426045</v>
       </c>
       <c r="D116">
-        <v>24.579786</v>
+        <v>30.490337</v>
       </c>
       <c r="E116">
-        <v>-82.136937</v>
+        <v>-81.406</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G116">
-        <v>0.0</v>
+        <v>114.6118</v>
       </c>
       <c r="H116">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="I116">
-        <v>28.4194</v>
+        <v>81.8554</v>
       </c>
       <c r="J116">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="K116">
-        <v>8.3292</v>
+        <v>77.7402</v>
       </c>
     </row>
     <row r="117">
@@ -4735,16 +4795,16 @@
         <v>126</v>
       </c>
       <c r="B117">
-        <v>29.43924</v>
+        <v>24.802982</v>
       </c>
       <c r="C117">
-        <v>-80.93117</v>
+        <v>-80.848836</v>
       </c>
       <c r="D117">
-        <v>30.40435</v>
+        <v>24.805643</v>
       </c>
       <c r="E117">
-        <v>-81.39331</v>
+        <v>-80.841914</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4762,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="K117">
-        <v>0.161</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="118">
@@ -4770,34 +4830,34 @@
         <v>127</v>
       </c>
       <c r="B118">
-        <v>23.02593</v>
+        <v>24.805643</v>
       </c>
       <c r="C118">
-        <v>-78.581445</v>
+        <v>-80.841914</v>
       </c>
       <c r="D118">
-        <v>28.625415</v>
+        <v>24.812604</v>
       </c>
       <c r="E118">
-        <v>-80.626015</v>
+        <v>-80.817548</v>
       </c>
       <c r="F118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>1.2911</v>
+        <v>2.8939</v>
       </c>
       <c r="H118">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I118">
-        <v>14.2262</v>
+        <v>36.7842</v>
       </c>
       <c r="J118">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K118">
-        <v>7.648</v>
+        <v>7.9608</v>
       </c>
     </row>
     <row r="119">
@@ -4805,34 +4865,34 @@
         <v>128</v>
       </c>
       <c r="B119">
-        <v>20.826588</v>
+        <v>27.389664</v>
       </c>
       <c r="C119">
-        <v>-74.318448</v>
+        <v>-82.689737</v>
       </c>
       <c r="D119">
-        <v>29.948348</v>
+        <v>27.436377</v>
       </c>
       <c r="E119">
-        <v>-85.435962</v>
+        <v>-82.642835</v>
       </c>
       <c r="F119">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="G119">
-        <v>3.2649</v>
+        <v>45.8189</v>
       </c>
       <c r="H119">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="I119">
-        <v>13.6838</v>
+        <v>45.722</v>
       </c>
       <c r="J119">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="K119">
-        <v>5.7895</v>
+        <v>60.7196</v>
       </c>
     </row>
     <row r="120">
@@ -4840,34 +4900,34 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>25.63213</v>
+        <v>27.328355</v>
       </c>
       <c r="C120">
-        <v>-80.12335</v>
+        <v>-82.642835</v>
       </c>
       <c r="D120">
-        <v>25.84395</v>
+        <v>27.389664</v>
       </c>
       <c r="E120">
-        <v>-80.11173</v>
+        <v>-82.586297</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="G120">
-        <v>1.8888</v>
+        <v>58.985</v>
       </c>
       <c r="H120">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="I120">
-        <v>61.0308</v>
+        <v>79.2855</v>
       </c>
       <c r="J120">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="K120">
-        <v>39.3727</v>
+        <v>95.6455</v>
       </c>
     </row>
     <row r="121">
@@ -4875,34 +4935,34 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>27.70609</v>
+        <v>26.379177</v>
       </c>
       <c r="C121">
-        <v>-82.796296</v>
+        <v>-81.885982</v>
       </c>
       <c r="D121">
-        <v>30.384842</v>
+        <v>26.403509</v>
       </c>
       <c r="E121">
-        <v>-86.484332</v>
+        <v>-81.868653</v>
       </c>
       <c r="F121">
+        <v>26</v>
+      </c>
+      <c r="G121">
+        <v>15.0015</v>
+      </c>
+      <c r="H121">
         <v>16</v>
       </c>
-      <c r="G121">
-        <v>6.5217</v>
-      </c>
-      <c r="H121">
-        <v>14</v>
-      </c>
       <c r="I121">
-        <v>8.4905</v>
+        <v>6.5157</v>
       </c>
       <c r="J121">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K121">
-        <v>2.6704</v>
+        <v>4.9825</v>
       </c>
     </row>
     <row r="122">
@@ -4910,34 +4970,34 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>27.846045</v>
+        <v>24.86043</v>
       </c>
       <c r="C122">
-        <v>-82.999661</v>
+        <v>-80.720231</v>
       </c>
       <c r="D122">
-        <v>27.78958</v>
+        <v>24.874204</v>
       </c>
       <c r="E122">
-        <v>-82.793678</v>
+        <v>-80.698582</v>
       </c>
       <c r="F122">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G122">
-        <v>5.078</v>
+        <v>36.3485</v>
       </c>
       <c r="H122">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="I122">
-        <v>6.2872</v>
+        <v>167.751</v>
       </c>
       <c r="J122">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="K122">
-        <v>6.4485</v>
+        <v>67.3809</v>
       </c>
     </row>
     <row r="123">
@@ -4945,34 +5005,34 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>26.932522</v>
+        <v>26.545617</v>
       </c>
       <c r="C123">
-        <v>-82.178554</v>
+        <v>-80.041922</v>
       </c>
       <c r="D123">
-        <v>30.315905</v>
+        <v>26.583951</v>
       </c>
       <c r="E123">
-        <v>-86.110579</v>
+        <v>-80.037517</v>
       </c>
       <c r="F123">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G123">
-        <v>11.5208</v>
+        <v>3.8674</v>
       </c>
       <c r="H123">
-        <v>16</v>
+        <v>199</v>
       </c>
       <c r="I123">
-        <v>9.3069</v>
+        <v>187.5907</v>
       </c>
       <c r="J123">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="K123">
-        <v>5.5828</v>
+        <v>65.7052</v>
       </c>
     </row>
     <row r="124">
@@ -4980,34 +5040,34 @@
         <v>133</v>
       </c>
       <c r="B124">
-        <v>30.065165</v>
+        <v>26.910938</v>
       </c>
       <c r="C124">
-        <v>-86.158605</v>
+        <v>-82.374293</v>
       </c>
       <c r="D124">
-        <v>30.371061</v>
+        <v>26.945969</v>
       </c>
       <c r="E124">
-        <v>-86.361638</v>
+        <v>-82.353414</v>
       </c>
       <c r="F124">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G124">
-        <v>2.6034</v>
+        <v>17.1822</v>
       </c>
       <c r="H124">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I124">
-        <v>1.9859</v>
+        <v>13.5705</v>
       </c>
       <c r="J124">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K124">
-        <v>2.185</v>
+        <v>16.3232</v>
       </c>
     </row>
     <row r="125">
@@ -5015,34 +5075,34 @@
         <v>134</v>
       </c>
       <c r="B125">
-        <v>26.42748</v>
+        <v>26.946027</v>
       </c>
       <c r="C125">
-        <v>-82.10844</v>
+        <v>-82.441893</v>
       </c>
       <c r="D125">
-        <v>26.106835</v>
+        <v>27.054913</v>
       </c>
       <c r="E125">
-        <v>-81.78985</v>
+        <v>-82.374304</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="G125">
-        <v>1.4724</v>
+        <v>52.7182</v>
       </c>
       <c r="H125">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="I125">
-        <v>1.4755</v>
+        <v>62.1702</v>
       </c>
       <c r="J125">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="K125">
-        <v>2.3904</v>
+        <v>75.4421</v>
       </c>
     </row>
     <row r="126">
@@ -5050,34 +5110,34 @@
         <v>135</v>
       </c>
       <c r="B126">
-        <v>27.301253</v>
+        <v>25.909409</v>
       </c>
       <c r="C126">
-        <v>-82.746173</v>
+        <v>-81.753797</v>
       </c>
       <c r="D126">
-        <v>30.38695</v>
+        <v>25.964159</v>
       </c>
       <c r="E126">
-        <v>-86.89143</v>
+        <v>-81.729024</v>
       </c>
       <c r="F126">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G126">
-        <v>1.6078</v>
+        <v>6.4143</v>
       </c>
       <c r="H126">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I126">
-        <v>1.3553</v>
+        <v>3.4633</v>
       </c>
       <c r="J126">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K126">
-        <v>2.2792</v>
+        <v>17.055</v>
       </c>
     </row>
     <row r="127">
@@ -5085,34 +5145,34 @@
         <v>136</v>
       </c>
       <c r="B127">
-        <v>21.417961</v>
+        <v>29.643187</v>
       </c>
       <c r="C127">
-        <v>-72.878278</v>
+        <v>-81.213123</v>
       </c>
       <c r="D127">
-        <v>29.020598</v>
+        <v>29.670856</v>
       </c>
       <c r="E127">
-        <v>-80.894615</v>
+        <v>-81.201497</v>
       </c>
       <c r="F127">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G127">
-        <v>13.0533</v>
+        <v>18.4395</v>
       </c>
       <c r="H127">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I127">
-        <v>25.844</v>
+        <v>51.3386</v>
       </c>
       <c r="J127">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K127">
-        <v>18.3592</v>
+        <v>34.4175</v>
       </c>
     </row>
     <row r="128">
@@ -5120,34 +5180,34 @@
         <v>137</v>
       </c>
       <c r="B128">
-        <v>26.192755</v>
+        <v>24.548072</v>
       </c>
       <c r="C128">
-        <v>-81.96828</v>
+        <v>-82.165823</v>
       </c>
       <c r="D128">
-        <v>26.605605</v>
+        <v>24.597612</v>
       </c>
       <c r="E128">
-        <v>-82.220955</v>
+        <v>-82.118175</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128">
-        <v>0.7233</v>
+        <v>0.4506</v>
       </c>
       <c r="H128">
-        <v>3</v>
+        <v>247</v>
       </c>
       <c r="I128">
-        <v>1.6715</v>
+        <v>293.2667</v>
       </c>
       <c r="J128">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="K128">
-        <v>2.4137</v>
+        <v>78.6406</v>
       </c>
     </row>
     <row r="129">
@@ -5155,34 +5215,34 @@
         <v>138</v>
       </c>
       <c r="B129">
-        <v>26.13954</v>
+        <v>30.381827</v>
       </c>
       <c r="C129">
-        <v>-81.94511</v>
+        <v>-81.396396</v>
       </c>
       <c r="D129">
-        <v>26.55365</v>
+        <v>30.397038</v>
       </c>
       <c r="E129">
-        <v>-82.19176</v>
+        <v>-81.39196</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G129">
-        <v>0.3742</v>
+        <v>7.9598</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I129">
-        <v>0.0</v>
+        <v>14.6709</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K129">
-        <v>0.0</v>
+        <v>9.3149</v>
       </c>
     </row>
     <row r="130">
@@ -5190,34 +5250,34 @@
         <v>139</v>
       </c>
       <c r="B130">
-        <v>26.254372</v>
+        <v>28.568617</v>
       </c>
       <c r="C130">
-        <v>-81.975952</v>
+        <v>-80.624025</v>
       </c>
       <c r="D130">
-        <v>26.577536</v>
+        <v>28.644196</v>
       </c>
       <c r="E130">
-        <v>-82.198198</v>
+        <v>-80.5691</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G130">
-        <v>2.4191</v>
+        <v>45.6851</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I130">
-        <v>0.0</v>
+        <v>129.1011</v>
       </c>
       <c r="J130">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="K130">
-        <v>2.2402</v>
+        <v>68.1133</v>
       </c>
     </row>
     <row r="131">
@@ -5225,34 +5285,34 @@
         <v>140</v>
       </c>
       <c r="B131">
-        <v>27.813518</v>
+        <v>29.924896</v>
       </c>
       <c r="C131">
-        <v>-82.92384</v>
+        <v>-85.448952</v>
       </c>
       <c r="D131">
-        <v>27.95277</v>
+        <v>29.955533</v>
       </c>
       <c r="E131">
-        <v>-82.826977</v>
+        <v>-85.389284</v>
       </c>
       <c r="F131">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="G131">
-        <v>2.1198</v>
+        <v>67.4399</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="I131">
-        <v>7.0252</v>
+        <v>64.368</v>
       </c>
       <c r="J131">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="K131">
-        <v>9.0506</v>
+        <v>64.0648</v>
       </c>
     </row>
     <row r="132">
@@ -5260,34 +5320,34 @@
         <v>141</v>
       </c>
       <c r="B132">
-        <v>26.429238</v>
+        <v>25.764279</v>
       </c>
       <c r="C132">
-        <v>-78.759929</v>
+        <v>-80.130901</v>
       </c>
       <c r="D132">
-        <v>29.609999</v>
+        <v>25.957123</v>
       </c>
       <c r="E132">
-        <v>-81.197158</v>
+        <v>-80.118496</v>
       </c>
       <c r="F132">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G132">
-        <v>9.9754</v>
+        <v>35.2119</v>
       </c>
       <c r="H132">
-        <v>14</v>
+        <v>680</v>
       </c>
       <c r="I132">
-        <v>9.8691</v>
+        <v>880.2058</v>
       </c>
       <c r="J132">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="K132">
-        <v>8.1919</v>
+        <v>345.5369</v>
       </c>
     </row>
     <row r="133">
@@ -5295,34 +5355,34 @@
         <v>142</v>
       </c>
       <c r="B133">
-        <v>26.973145</v>
+        <v>30.3817</v>
       </c>
       <c r="C133">
-        <v>-78.243383</v>
+        <v>-86.507082</v>
       </c>
       <c r="D133">
-        <v>29.400417</v>
+        <v>30.383856</v>
       </c>
       <c r="E133">
-        <v>-81.10254</v>
+        <v>-86.453631</v>
       </c>
       <c r="F133">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="G133">
-        <v>3.051</v>
+        <v>86.056</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="I133">
-        <v>13.5846</v>
+        <v>132.2565</v>
       </c>
       <c r="J133">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="K133">
-        <v>4.3966</v>
+        <v>67.4769</v>
       </c>
     </row>
     <row r="134">
@@ -5330,34 +5390,34 @@
         <v>143</v>
       </c>
       <c r="B134">
-        <v>18.917292</v>
+        <v>27.73906</v>
       </c>
       <c r="C134">
-        <v>-73.27988</v>
+        <v>-82.837897</v>
       </c>
       <c r="D134">
-        <v>27.503697</v>
+        <v>27.836408</v>
       </c>
       <c r="E134">
-        <v>-80.304363</v>
+        <v>-82.75671</v>
       </c>
       <c r="F134">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="G134">
-        <v>35.8497</v>
+        <v>78.0742</v>
       </c>
       <c r="H134">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="I134">
-        <v>27.6418</v>
+        <v>111.9152</v>
       </c>
       <c r="J134">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="K134">
-        <v>30.2428</v>
+        <v>95.7763</v>
       </c>
     </row>
     <row r="135">
@@ -5365,34 +5425,34 @@
         <v>144</v>
       </c>
       <c r="B135">
-        <v>26.09515</v>
+        <v>30.302005</v>
       </c>
       <c r="C135">
-        <v>-80.02686</v>
+        <v>-86.146185</v>
       </c>
       <c r="D135">
-        <v>26.54915</v>
+        <v>30.321217</v>
       </c>
       <c r="E135">
-        <v>-80.05752</v>
+        <v>-86.084851</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="G135">
-        <v>0.0</v>
+        <v>195.4866</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="I135">
-        <v>0.3974</v>
+        <v>170.268</v>
       </c>
       <c r="J135">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="K135">
-        <v>0.0</v>
+        <v>162.3888</v>
       </c>
     </row>
     <row r="136">
@@ -5400,34 +5460,34 @@
         <v>145</v>
       </c>
       <c r="B136">
-        <v>21.066145</v>
+        <v>30.366741</v>
       </c>
       <c r="C136">
-        <v>-71.90051</v>
+        <v>-86.397365</v>
       </c>
       <c r="D136">
-        <v>26.526745</v>
+        <v>30.378838</v>
       </c>
       <c r="E136">
-        <v>-80.052505</v>
+        <v>-86.317194</v>
       </c>
       <c r="F136">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="G136">
-        <v>1.483</v>
+        <v>61.1477</v>
       </c>
       <c r="H136">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I136">
-        <v>22.4216</v>
+        <v>51.9863</v>
       </c>
       <c r="J136">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="K136">
-        <v>5.7025</v>
+        <v>34.1309</v>
       </c>
     </row>
     <row r="137">
@@ -5435,34 +5495,34 @@
         <v>146</v>
       </c>
       <c r="B137">
-        <v>25.093797</v>
+        <v>26.093532</v>
       </c>
       <c r="C137">
-        <v>-79.397457</v>
+        <v>-81.814252</v>
       </c>
       <c r="D137">
-        <v>30.13281</v>
+        <v>26.173682</v>
       </c>
       <c r="E137">
-        <v>-81.352147</v>
+        <v>-81.800888</v>
       </c>
       <c r="F137">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G137">
-        <v>1.3585</v>
+        <v>11.872</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I137">
-        <v>0.1965</v>
+        <v>24.1895</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K137">
-        <v>0.7276</v>
+        <v>21.5106</v>
       </c>
     </row>
     <row r="138">
@@ -5470,34 +5530,34 @@
         <v>147</v>
       </c>
       <c r="B138">
-        <v>24.239666</v>
+        <v>24.549706</v>
       </c>
       <c r="C138">
-        <v>-79.265992</v>
+        <v>-81.779691</v>
       </c>
       <c r="D138">
-        <v>26.74649</v>
+        <v>24.550395</v>
       </c>
       <c r="E138">
-        <v>-80.043004</v>
+        <v>-81.776584</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G138">
-        <v>0.0</v>
+        <v>7.4526</v>
       </c>
       <c r="H138">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I138">
-        <v>2.7941</v>
+        <v>9.1769</v>
       </c>
       <c r="J138">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K138">
-        <v>6.6653</v>
+        <v>2.957</v>
       </c>
     </row>
     <row r="139">
@@ -5505,34 +5565,34 @@
         <v>148</v>
       </c>
       <c r="B139">
-        <v>22.892551</v>
+        <v>30.371015</v>
       </c>
       <c r="C139">
-        <v>-77.594775</v>
+        <v>-86.918748</v>
       </c>
       <c r="D139">
-        <v>26.669464</v>
+        <v>30.381299</v>
       </c>
       <c r="E139">
-        <v>-80.042772</v>
+        <v>-86.849415</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="G139">
-        <v>0.0</v>
+        <v>127.4304</v>
       </c>
       <c r="H139">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="I139">
-        <v>22.1507</v>
+        <v>48.9932</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="K139">
-        <v>0.7957</v>
+        <v>84.5626</v>
       </c>
     </row>
     <row r="140">
@@ -5540,34 +5600,34 @@
         <v>149</v>
       </c>
       <c r="B140">
-        <v>27.81671</v>
+        <v>28.938634</v>
       </c>
       <c r="C140">
-        <v>-82.98071</v>
+        <v>-80.917763</v>
       </c>
       <c r="D140">
-        <v>26.77016</v>
+        <v>29.074484</v>
       </c>
       <c r="E140">
-        <v>-80.02655</v>
+        <v>-80.830148</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G140">
-        <v>0.0</v>
+        <v>146.5659</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>442</v>
       </c>
       <c r="I140">
-        <v>0.8132</v>
+        <v>376.3478</v>
       </c>
       <c r="J140">
-        <v>3</v>
+        <v>338</v>
       </c>
       <c r="K140">
-        <v>1.546</v>
+        <v>280.802</v>
       </c>
     </row>
     <row r="141">
@@ -5575,34 +5635,34 @@
         <v>150</v>
       </c>
       <c r="B141">
-        <v>25.454839</v>
+        <v>26.59325</v>
       </c>
       <c r="C141">
-        <v>-80.710688</v>
+        <v>-82.224497</v>
       </c>
       <c r="D141">
-        <v>30.219798</v>
+        <v>26.6072</v>
       </c>
       <c r="E141">
-        <v>-85.903287</v>
+        <v>-82.219788</v>
       </c>
       <c r="F141">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="G141">
-        <v>66.1235</v>
+        <v>10.7728</v>
       </c>
       <c r="H141">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I141">
-        <v>52.5188</v>
+        <v>6.339</v>
       </c>
       <c r="J141">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="K141">
-        <v>42.4546</v>
+        <v>16.9013</v>
       </c>
     </row>
     <row r="142">
@@ -5610,34 +5670,34 @@
         <v>151</v>
       </c>
       <c r="B142">
-        <v>25.13085</v>
+        <v>26.555677</v>
       </c>
       <c r="C142">
-        <v>-80.23206</v>
+        <v>-82.20206</v>
       </c>
       <c r="D142">
-        <v>26.62483</v>
+        <v>26.56011</v>
       </c>
       <c r="E142">
-        <v>-80.04926</v>
+        <v>-82.20022</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>0.0</v>
+        <v>0.3742</v>
       </c>
       <c r="H142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I142">
-        <v>0.1601</v>
+        <v>0.7217</v>
       </c>
       <c r="J142">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K142">
-        <v>4.6427</v>
+        <v>4.2564</v>
       </c>
     </row>
     <row r="143">
@@ -5645,34 +5705,34 @@
         <v>152</v>
       </c>
       <c r="B143">
-        <v>26.51117</v>
+        <v>26.56011</v>
       </c>
       <c r="C143">
-        <v>-82.24692</v>
+        <v>-82.224123</v>
       </c>
       <c r="D143">
-        <v>26.20866</v>
+        <v>26.59325</v>
       </c>
       <c r="E143">
-        <v>-81.80737</v>
+        <v>-82.20206</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G143">
-        <v>0.0</v>
+        <v>15.2266</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I143">
-        <v>0.9174</v>
+        <v>1.3654</v>
       </c>
       <c r="J143">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K143">
-        <v>0.9175</v>
+        <v>12.1493</v>
       </c>
     </row>
     <row r="144">
@@ -5680,34 +5740,34 @@
         <v>153</v>
       </c>
       <c r="B144">
-        <v>22.044399</v>
+        <v>27.836408</v>
       </c>
       <c r="C144">
-        <v>-76.651911</v>
+        <v>-82.851854</v>
       </c>
       <c r="D144">
-        <v>28.236735</v>
+        <v>28.019435</v>
       </c>
       <c r="E144">
-        <v>-80.611874</v>
+        <v>-82.827116</v>
       </c>
       <c r="F144">
-        <v>11</v>
+        <v>172</v>
       </c>
       <c r="G144">
-        <v>14.1181</v>
+        <v>125.3935</v>
       </c>
       <c r="H144">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="I144">
-        <v>15.9576</v>
+        <v>169.0045</v>
       </c>
       <c r="J144">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="K144">
-        <v>13.3776</v>
+        <v>195.9506</v>
       </c>
     </row>
     <row r="145">
@@ -5715,34 +5775,34 @@
         <v>154</v>
       </c>
       <c r="B145">
-        <v>28.470477</v>
+        <v>29.584532</v>
       </c>
       <c r="C145">
-        <v>-85.998307</v>
+        <v>-81.197575</v>
       </c>
       <c r="D145">
-        <v>30.344069</v>
+        <v>29.63368</v>
       </c>
       <c r="E145">
-        <v>-87.120151</v>
+        <v>-81.176465</v>
       </c>
       <c r="F145">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="G145">
-        <v>3.728</v>
+        <v>98.4018</v>
       </c>
       <c r="H145">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="I145">
-        <v>8.1</v>
+        <v>135.2264</v>
       </c>
       <c r="J145">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="K145">
-        <v>8.8832</v>
+        <v>96.3381</v>
       </c>
     </row>
     <row r="146">
@@ -5750,34 +5810,34 @@
         <v>155</v>
       </c>
       <c r="B146">
-        <v>23.111895</v>
+        <v>29.387243</v>
       </c>
       <c r="C146">
-        <v>-76.709065</v>
+        <v>-81.102132</v>
       </c>
       <c r="D146">
-        <v>30.297897</v>
+        <v>29.427175</v>
       </c>
       <c r="E146">
-        <v>-87.45547</v>
+        <v>-81.083844</v>
       </c>
       <c r="F146">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="G146">
-        <v>2.2378</v>
+        <v>58.1222</v>
       </c>
       <c r="H146">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="I146">
-        <v>2.8027</v>
+        <v>141.0102</v>
       </c>
       <c r="J146">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K146">
-        <v>0.2195</v>
+        <v>74.9521</v>
       </c>
     </row>
     <row r="147">
@@ -5785,34 +5845,34 @@
         <v>156</v>
       </c>
       <c r="B147">
-        <v>24.019975</v>
+        <v>27.479237</v>
       </c>
       <c r="C147">
-        <v>-78.064525</v>
+        <v>-80.313919</v>
       </c>
       <c r="D147">
-        <v>30.275935</v>
+        <v>27.532591</v>
       </c>
       <c r="E147">
-        <v>-87.45644</v>
+        <v>-80.29316</v>
       </c>
       <c r="F147">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="G147">
-        <v>2.5463</v>
+        <v>230.93</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="I147">
-        <v>0.0</v>
+        <v>307.0758</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="K147">
-        <v>0.365</v>
+        <v>208.2893</v>
       </c>
     </row>
     <row r="148">
@@ -5820,34 +5880,34 @@
         <v>157</v>
       </c>
       <c r="B148">
-        <v>16.36475</v>
+        <v>26.542925</v>
       </c>
       <c r="C148">
-        <v>-68.524766</v>
+        <v>-80.043478</v>
       </c>
       <c r="D148">
-        <v>26.232461</v>
+        <v>26.545178</v>
       </c>
       <c r="E148">
-        <v>-80.095046</v>
+        <v>-80.042758</v>
       </c>
       <c r="F148">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G148">
-        <v>11.729</v>
+        <v>0.0</v>
       </c>
       <c r="H148">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="I148">
-        <v>67.9009</v>
+        <v>8.0561</v>
       </c>
       <c r="J148">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="K148">
-        <v>41.6671</v>
+        <v>1.9617</v>
       </c>
     </row>
     <row r="149">
@@ -5855,16 +5915,16 @@
         <v>158</v>
       </c>
       <c r="B149">
-        <v>29.69422</v>
+        <v>26.792729</v>
       </c>
       <c r="C149">
-        <v>-81.0568</v>
+        <v>-80.032084</v>
       </c>
       <c r="D149">
-        <v>30.231825</v>
+        <v>26.794747</v>
       </c>
       <c r="E149">
-        <v>-81.392415</v>
+        <v>-80.031972</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -5873,16 +5933,16 @@
         <v>0.0</v>
       </c>
       <c r="H149">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I149">
-        <v>2.3225</v>
+        <v>7.1157</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K149">
-        <v>0.0</v>
+        <v>3.5043</v>
       </c>
     </row>
     <row r="150">
@@ -5890,34 +5950,34 @@
         <v>159</v>
       </c>
       <c r="B150">
-        <v>28.081057</v>
+        <v>26.499028</v>
       </c>
       <c r="C150">
-        <v>-80.38475</v>
+        <v>-80.052016</v>
       </c>
       <c r="D150">
-        <v>29.98398</v>
+        <v>26.542925</v>
       </c>
       <c r="E150">
-        <v>-81.32644</v>
+        <v>-80.043478</v>
       </c>
       <c r="F150">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G150">
-        <v>2.4091</v>
+        <v>13.3785</v>
       </c>
       <c r="H150">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="I150">
-        <v>5.9668</v>
+        <v>191.9693</v>
       </c>
       <c r="J150">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="K150">
-        <v>6.1787</v>
+        <v>64.2098</v>
       </c>
     </row>
     <row r="151">
@@ -5925,34 +5985,34 @@
         <v>160</v>
       </c>
       <c r="B151">
-        <v>10.92834</v>
+        <v>30.127155</v>
       </c>
       <c r="C151">
-        <v>-61.38693</v>
+        <v>-81.350425</v>
       </c>
       <c r="D151">
-        <v>24.5554</v>
+        <v>30.141105</v>
       </c>
       <c r="E151">
-        <v>-81.79554</v>
+        <v>-81.34714</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G151">
-        <v>0.0</v>
+        <v>26.622</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I151">
-        <v>0.2044</v>
+        <v>17.9612</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K151">
-        <v>0.3856</v>
+        <v>13.5936</v>
       </c>
     </row>
     <row r="152">
@@ -5960,16 +6020,16 @@
         <v>161</v>
       </c>
       <c r="B152">
-        <v>23.257865</v>
+        <v>26.72723</v>
       </c>
       <c r="C152">
-        <v>-77.78854</v>
+        <v>-80.036759</v>
       </c>
       <c r="D152">
-        <v>24.55241</v>
+        <v>26.761576</v>
       </c>
       <c r="E152">
-        <v>-81.784885</v>
+        <v>-80.034794</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -5978,16 +6038,16 @@
         <v>0.0</v>
       </c>
       <c r="H152">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="I152">
-        <v>1.2189</v>
+        <v>86.2364</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K152">
-        <v>0.0</v>
+        <v>46.9672</v>
       </c>
     </row>
     <row r="153">
@@ -5995,34 +6055,34 @@
         <v>162</v>
       </c>
       <c r="B153">
-        <v>29.88228</v>
+        <v>26.646752</v>
       </c>
       <c r="C153">
-        <v>-81.060325</v>
+        <v>-80.037082</v>
       </c>
       <c r="D153">
-        <v>30.31945</v>
+        <v>26.692502</v>
       </c>
       <c r="E153">
-        <v>-81.4051</v>
+        <v>-80.033545</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G153">
-        <v>1.4039</v>
+        <v>0.2813</v>
       </c>
       <c r="H153">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="I153">
-        <v>6.6246</v>
+        <v>226.531</v>
       </c>
       <c r="J153">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="K153">
-        <v>5.5864</v>
+        <v>80.9086</v>
       </c>
     </row>
     <row r="154">
@@ -6030,34 +6090,34 @@
         <v>163</v>
       </c>
       <c r="B154">
-        <v>22.477261</v>
+        <v>26.773715</v>
       </c>
       <c r="C154">
-        <v>-76.905499</v>
+        <v>-80.031757</v>
       </c>
       <c r="D154">
-        <v>30.102811</v>
+        <v>26.781464</v>
       </c>
       <c r="E154">
-        <v>-85.71779</v>
+        <v>-80.031305</v>
       </c>
       <c r="F154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>7.9428</v>
+        <v>0.0</v>
       </c>
       <c r="H154">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I154">
-        <v>6.2031</v>
+        <v>30.5024</v>
       </c>
       <c r="J154">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K154">
-        <v>4.3663</v>
+        <v>14.3231</v>
       </c>
     </row>
     <row r="155">
@@ -6065,34 +6125,34 @@
         <v>164</v>
       </c>
       <c r="B155">
-        <v>27.704498</v>
+        <v>30.133211</v>
       </c>
       <c r="C155">
-        <v>-80.23032</v>
+        <v>-85.990854</v>
       </c>
       <c r="D155">
-        <v>29.816909</v>
+        <v>30.267052</v>
       </c>
       <c r="E155">
-        <v>-81.264559</v>
+        <v>-85.745474</v>
       </c>
       <c r="F155">
-        <v>27</v>
+        <v>1151</v>
       </c>
       <c r="G155">
-        <v>15.1897</v>
+        <v>925.3003</v>
       </c>
       <c r="H155">
-        <v>20</v>
+        <v>1412</v>
       </c>
       <c r="I155">
-        <v>11.3902</v>
+        <v>1176.5396</v>
       </c>
       <c r="J155">
-        <v>25</v>
+        <v>1035</v>
       </c>
       <c r="K155">
-        <v>11.6343</v>
+        <v>747.6857</v>
       </c>
     </row>
     <row r="156">
@@ -6100,34 +6160,34 @@
         <v>165</v>
       </c>
       <c r="B156">
-        <v>27.953862</v>
+        <v>26.616837</v>
       </c>
       <c r="C156">
-        <v>-83.042387</v>
+        <v>-80.036958</v>
       </c>
       <c r="D156">
-        <v>27.721605</v>
+        <v>26.629405</v>
       </c>
       <c r="E156">
-        <v>-82.731044</v>
+        <v>-80.036623</v>
       </c>
       <c r="F156">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>7.9615</v>
+        <v>0.3968</v>
       </c>
       <c r="H156">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="I156">
-        <v>4.1771</v>
+        <v>33.8011</v>
       </c>
       <c r="J156">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K156">
-        <v>2.4536</v>
+        <v>29.2912</v>
       </c>
     </row>
     <row r="157">
@@ -6135,34 +6195,34 @@
         <v>166</v>
       </c>
       <c r="B157">
-        <v>26.154702</v>
+        <v>26.174472</v>
       </c>
       <c r="C157">
-        <v>-81.907995</v>
+        <v>-81.817</v>
       </c>
       <c r="D157">
-        <v>26.45042</v>
+        <v>26.210934</v>
       </c>
       <c r="E157">
-        <v>-82.01805</v>
+        <v>-81.81468</v>
       </c>
       <c r="F157">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G157">
-        <v>1.2844</v>
+        <v>5.0827</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="I157">
-        <v>1.1578</v>
+        <v>18.6624</v>
       </c>
       <c r="J157">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K157">
-        <v>2.2199</v>
+        <v>9.9941</v>
       </c>
     </row>
     <row r="158">
@@ -6170,34 +6230,34 @@
         <v>167</v>
       </c>
       <c r="B158">
-        <v>26.14152</v>
+        <v>24.545014</v>
       </c>
       <c r="C158">
-        <v>-81.92762</v>
+        <v>-81.80826</v>
       </c>
       <c r="D158">
-        <v>26.44072</v>
+        <v>24.545365</v>
       </c>
       <c r="E158">
-        <v>-82.130965</v>
+        <v>-81.805491</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>0.7498</v>
+        <v>0.0</v>
       </c>
       <c r="H158">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I158">
-        <v>6.1677</v>
+        <v>6.8802</v>
       </c>
       <c r="J158">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K158">
-        <v>3.5445</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="159">
@@ -6205,34 +6265,34 @@
         <v>168</v>
       </c>
       <c r="B159">
-        <v>21.241083</v>
+        <v>28.21268</v>
       </c>
       <c r="C159">
-        <v>-77.231323</v>
+        <v>-80.605359</v>
       </c>
       <c r="D159">
-        <v>27.866983</v>
+        <v>28.271967</v>
       </c>
       <c r="E159">
-        <v>-80.4624</v>
+        <v>-80.596748</v>
       </c>
       <c r="F159">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G159">
-        <v>4.1805</v>
+        <v>51.0424</v>
       </c>
       <c r="H159">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="I159">
-        <v>7.7542</v>
+        <v>81.5714</v>
       </c>
       <c r="J159">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="K159">
-        <v>2.9701</v>
+        <v>66.6064</v>
       </c>
     </row>
     <row r="160">
@@ -6240,34 +6300,34 @@
         <v>169</v>
       </c>
       <c r="B160">
-        <v>21.005401</v>
+        <v>30.324524</v>
       </c>
       <c r="C160">
-        <v>-73.265796</v>
+        <v>-87.181147</v>
       </c>
       <c r="D160">
-        <v>27.850483</v>
+        <v>30.34722</v>
       </c>
       <c r="E160">
-        <v>-80.446145</v>
+        <v>-87.053055</v>
       </c>
       <c r="F160">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="G160">
-        <v>7.0108</v>
+        <v>94.1414</v>
       </c>
       <c r="H160">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="I160">
-        <v>24.7385</v>
+        <v>151.9196</v>
       </c>
       <c r="J160">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="K160">
-        <v>35.9608</v>
+        <v>121.6448</v>
       </c>
     </row>
     <row r="161">
@@ -6275,34 +6335,34 @@
         <v>170</v>
       </c>
       <c r="B161">
-        <v>26.75926</v>
+        <v>30.279934</v>
       </c>
       <c r="C161">
-        <v>-82.39913</v>
+        <v>-87.51847</v>
       </c>
       <c r="D161">
-        <v>27.25255</v>
+        <v>30.297552</v>
       </c>
       <c r="E161">
-        <v>-82.53816</v>
+        <v>-87.419571</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="G161">
-        <v>0.2096</v>
+        <v>97.3666</v>
       </c>
       <c r="H161">
-        <v>2</v>
+        <v>325</v>
       </c>
       <c r="I161">
-        <v>0.9771</v>
+        <v>267.1171</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="K161">
-        <v>0.1505</v>
+        <v>137.3532</v>
       </c>
     </row>
     <row r="162">
@@ -6310,34 +6370,34 @@
         <v>171</v>
       </c>
       <c r="B162">
-        <v>27.55016</v>
+        <v>30.287606</v>
       </c>
       <c r="C162">
-        <v>-82.85925</v>
+        <v>-87.479867</v>
       </c>
       <c r="D162">
-        <v>27.23635</v>
+        <v>30.292613</v>
       </c>
       <c r="E162">
-        <v>-82.53069</v>
+        <v>-87.453063</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G162">
-        <v>0.1503</v>
+        <v>29.2436</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I162">
-        <v>0.0</v>
+        <v>46.1265</v>
       </c>
       <c r="J162">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K162">
-        <v>0.0</v>
+        <v>35.5067</v>
       </c>
     </row>
     <row r="163">
@@ -6345,34 +6405,34 @@
         <v>172</v>
       </c>
       <c r="B163">
-        <v>22.828495</v>
+        <v>29.904019</v>
       </c>
       <c r="C163">
-        <v>-77.443755</v>
+        <v>-84.441384</v>
       </c>
       <c r="D163">
-        <v>26.796335</v>
+        <v>29.917606</v>
       </c>
       <c r="E163">
-        <v>-80.03011</v>
+        <v>-84.424007</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G163">
-        <v>0.0</v>
+        <v>9.3598</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I163">
-        <v>1.412</v>
+        <v>2.7724</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K163">
-        <v>0.0</v>
+        <v>8.1982</v>
       </c>
     </row>
     <row r="164">
@@ -6380,34 +6440,34 @@
         <v>173</v>
       </c>
       <c r="B164">
-        <v>21.935253</v>
+        <v>26.189484</v>
       </c>
       <c r="C164">
-        <v>-75.505113</v>
+        <v>-80.094831</v>
       </c>
       <c r="D164">
-        <v>26.784818</v>
+        <v>26.257906</v>
       </c>
       <c r="E164">
-        <v>-80.035193</v>
+        <v>-80.081885</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="G164">
-        <v>0.0</v>
+        <v>199.9314</v>
       </c>
       <c r="H164">
-        <v>4</v>
+        <v>790</v>
       </c>
       <c r="I164">
-        <v>2.1231</v>
+        <v>929.2045</v>
       </c>
       <c r="J164">
-        <v>2</v>
+        <v>574</v>
       </c>
       <c r="K164">
-        <v>1.7587</v>
+        <v>615.6565</v>
       </c>
     </row>
     <row r="165">
@@ -6415,34 +6475,34 @@
         <v>174</v>
       </c>
       <c r="B165">
-        <v>21.291334</v>
+        <v>30.21709</v>
       </c>
       <c r="C165">
-        <v>-75.072298</v>
+        <v>-81.380386</v>
       </c>
       <c r="D165">
-        <v>26.637692</v>
+        <v>30.252993</v>
       </c>
       <c r="E165">
-        <v>-80.044872</v>
+        <v>-81.370734</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G165">
-        <v>0.0</v>
+        <v>51.2918</v>
       </c>
       <c r="H165">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="I165">
-        <v>2.6257</v>
+        <v>66.2592</v>
       </c>
       <c r="J165">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="K165">
-        <v>2.1794</v>
+        <v>46.8158</v>
       </c>
     </row>
     <row r="166">
@@ -6450,34 +6510,34 @@
         <v>175</v>
       </c>
       <c r="B166">
-        <v>15.544383</v>
+        <v>29.952538</v>
       </c>
       <c r="C166">
-        <v>-70.346419</v>
+        <v>-81.322754</v>
       </c>
       <c r="D166">
-        <v>24.560614</v>
+        <v>30.02263</v>
       </c>
       <c r="E166">
-        <v>-81.758848</v>
+        <v>-81.30392</v>
       </c>
       <c r="F166">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="G166">
-        <v>14.8022</v>
+        <v>136.9174</v>
       </c>
       <c r="H166">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="I166">
-        <v>10.0672</v>
+        <v>121.7816</v>
       </c>
       <c r="J166">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="K166">
-        <v>14.9208</v>
+        <v>98.8623</v>
       </c>
     </row>
     <row r="167">
@@ -6485,34 +6545,34 @@
         <v>176</v>
       </c>
       <c r="B167">
-        <v>26.35823</v>
+        <v>24.545801</v>
       </c>
       <c r="C167">
-        <v>-81.97315</v>
+        <v>-81.801991</v>
       </c>
       <c r="D167">
-        <v>24.68623</v>
+        <v>24.546519</v>
       </c>
       <c r="E167">
-        <v>-81.0746</v>
+        <v>-81.799137</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G167">
-        <v>0.5478</v>
+        <v>0.9674</v>
       </c>
       <c r="H167">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I167">
-        <v>0.5328</v>
+        <v>18.7849</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K167">
-        <v>0.0</v>
+        <v>12.0577</v>
       </c>
     </row>
     <row r="168">
@@ -6520,34 +6580,34 @@
         <v>177</v>
       </c>
       <c r="B168">
-        <v>21.085713</v>
+        <v>24.547644</v>
       </c>
       <c r="C168">
-        <v>-74.535509</v>
+        <v>-81.784693</v>
       </c>
       <c r="D168">
-        <v>27.976427</v>
+        <v>24.548696</v>
       </c>
       <c r="E168">
-        <v>-80.51509</v>
+        <v>-81.783023</v>
       </c>
       <c r="F168">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G168">
-        <v>46.9609</v>
+        <v>1.3456</v>
       </c>
       <c r="H168">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="I168">
-        <v>62.0342</v>
+        <v>8.5821</v>
       </c>
       <c r="J168">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>24.3469</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="169">
@@ -6555,34 +6615,34 @@
         <v>178</v>
       </c>
       <c r="B169">
-        <v>22.214613</v>
+        <v>30.252993</v>
       </c>
       <c r="C169">
-        <v>-77.837627</v>
+        <v>-81.397438</v>
       </c>
       <c r="D169">
-        <v>28.286599</v>
+        <v>30.36041</v>
       </c>
       <c r="E169">
-        <v>-80.61509</v>
+        <v>-81.380386</v>
       </c>
       <c r="F169">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="G169">
-        <v>5.769</v>
+        <v>59.2126</v>
       </c>
       <c r="H169">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="I169">
-        <v>6.4532</v>
+        <v>189.6992</v>
       </c>
       <c r="J169">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="K169">
-        <v>6.82</v>
+        <v>87.4245</v>
       </c>
     </row>
     <row r="170">
@@ -6590,34 +6650,34 @@
         <v>179</v>
       </c>
       <c r="B170">
-        <v>29.252195</v>
+        <v>30.092539</v>
       </c>
       <c r="C170">
-        <v>-80.942525</v>
+        <v>-85.745474</v>
       </c>
       <c r="D170">
-        <v>29.54146</v>
+        <v>30.133211</v>
       </c>
       <c r="E170">
-        <v>-81.164428</v>
+        <v>-85.687471</v>
       </c>
       <c r="F170">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="G170">
-        <v>3.8898</v>
+        <v>142.8999</v>
       </c>
       <c r="H170">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="I170">
-        <v>12.9495</v>
+        <v>102.3405</v>
       </c>
       <c r="J170">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="K170">
-        <v>4.732</v>
+        <v>116.3194</v>
       </c>
     </row>
     <row r="171">
@@ -6625,34 +6685,34 @@
         <v>180</v>
       </c>
       <c r="B171">
-        <v>17.957206</v>
+        <v>29.769416</v>
       </c>
       <c r="C171">
-        <v>-71.30278</v>
+        <v>-81.266143</v>
       </c>
       <c r="D171">
-        <v>27.59198</v>
+        <v>29.859566</v>
       </c>
       <c r="E171">
-        <v>-80.334731</v>
+        <v>-81.251453</v>
       </c>
       <c r="F171">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="G171">
-        <v>21.5703</v>
+        <v>175.2553</v>
       </c>
       <c r="H171">
-        <v>15</v>
+        <v>212</v>
       </c>
       <c r="I171">
-        <v>29.4891</v>
+        <v>165.5724</v>
       </c>
       <c r="J171">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="K171">
-        <v>16.891</v>
+        <v>145.6402</v>
       </c>
     </row>
     <row r="172">
@@ -6660,34 +6720,34 @@
         <v>181</v>
       </c>
       <c r="B172">
-        <v>23.350539</v>
+        <v>27.68323</v>
       </c>
       <c r="C172">
-        <v>-78.361414</v>
+        <v>-82.752128</v>
       </c>
       <c r="D172">
-        <v>26.600267</v>
+        <v>27.736243</v>
       </c>
       <c r="E172">
-        <v>-80.044399</v>
+        <v>-82.737859</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="G172">
-        <v>0.0</v>
+        <v>144.5573</v>
       </c>
       <c r="H172">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I172">
-        <v>10.4565</v>
+        <v>124.3633</v>
       </c>
       <c r="J172">
-        <v>5</v>
+        <v>167</v>
       </c>
       <c r="K172">
-        <v>3.6856</v>
+        <v>142.9416</v>
       </c>
     </row>
     <row r="173">
@@ -6695,34 +6755,34 @@
         <v>182</v>
       </c>
       <c r="B173">
-        <v>29.08107</v>
+        <v>26.421849</v>
       </c>
       <c r="C173">
-        <v>-83.447555</v>
+        <v>-82.080052</v>
       </c>
       <c r="D173">
-        <v>29.64978</v>
+        <v>26.454469</v>
       </c>
       <c r="E173">
-        <v>-84.88694</v>
+        <v>-82.013653</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G173">
-        <v>1.4505</v>
+        <v>22.0807</v>
       </c>
       <c r="H173">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="I173">
-        <v>2.9087</v>
+        <v>62.5996</v>
       </c>
       <c r="J173">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="K173">
-        <v>3.659</v>
+        <v>34.3922</v>
       </c>
     </row>
     <row r="174">
@@ -6730,34 +6790,34 @@
         <v>183</v>
       </c>
       <c r="B174">
-        <v>28.21825</v>
+        <v>26.421846</v>
       </c>
       <c r="C174">
-        <v>-82.90234</v>
+        <v>-82.182184</v>
       </c>
       <c r="D174">
-        <v>29.76714</v>
+        <v>26.482474</v>
       </c>
       <c r="E174">
-        <v>-84.69697</v>
+        <v>-82.080052</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G174">
-        <v>1.4173</v>
+        <v>11.4944</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="I174">
-        <v>0.4907</v>
+        <v>70.3847</v>
       </c>
       <c r="J174">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="K174">
-        <v>2.9102</v>
+        <v>23.2631</v>
       </c>
     </row>
     <row r="175">
@@ -6765,16 +6825,16 @@
         <v>184</v>
       </c>
       <c r="B175">
-        <v>17.755095</v>
+        <v>25.980405</v>
       </c>
       <c r="C175">
-        <v>-71.159622</v>
+        <v>-81.748101</v>
       </c>
       <c r="D175">
-        <v>29.893572</v>
+        <v>25.986845</v>
       </c>
       <c r="E175">
-        <v>-85.354722</v>
+        <v>-81.746003</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6783,16 +6843,16 @@
         <v>0.0</v>
       </c>
       <c r="H175">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I175">
-        <v>16.6986</v>
+        <v>0.0</v>
       </c>
       <c r="J175">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K175">
-        <v>3.3142</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -6800,34 +6860,34 @@
         <v>185</v>
       </c>
       <c r="B176">
-        <v>22.963135</v>
+        <v>27.861923</v>
       </c>
       <c r="C176">
-        <v>-76.419795</v>
+        <v>-80.454327</v>
       </c>
       <c r="D176">
-        <v>29.76124</v>
+        <v>27.874586</v>
       </c>
       <c r="E176">
-        <v>-85.394945</v>
+        <v>-80.446571</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G176">
-        <v>0.0</v>
+        <v>11.0225</v>
       </c>
       <c r="H176">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="I176">
-        <v>3.9995</v>
+        <v>40.5459</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K176">
-        <v>0.197</v>
+        <v>20.0993</v>
       </c>
     </row>
     <row r="177">
@@ -6835,34 +6895,34 @@
         <v>186</v>
       </c>
       <c r="B177">
-        <v>22.78235</v>
+        <v>27.833257</v>
       </c>
       <c r="C177">
-        <v>-78.2544</v>
+        <v>-80.446916</v>
       </c>
       <c r="D177">
-        <v>29.85604</v>
+        <v>27.859965</v>
       </c>
       <c r="E177">
-        <v>-85.409478</v>
+        <v>-80.43293</v>
       </c>
       <c r="F177">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G177">
-        <v>4.5085</v>
+        <v>54.3732</v>
       </c>
       <c r="H177">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="I177">
-        <v>3.659</v>
+        <v>72.9115</v>
       </c>
       <c r="J177">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="K177">
-        <v>2.7127</v>
+        <v>112.5712</v>
       </c>
     </row>
     <row r="178">
@@ -6870,34 +6930,34 @@
         <v>187</v>
       </c>
       <c r="B178">
-        <v>19.491134</v>
+        <v>27.246209</v>
       </c>
       <c r="C178">
-        <v>-73.481808</v>
+        <v>-82.569827</v>
       </c>
       <c r="D178">
-        <v>27.143848</v>
+        <v>27.27892</v>
       </c>
       <c r="E178">
-        <v>-80.160134</v>
+        <v>-82.535941</v>
       </c>
       <c r="F178">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="G178">
-        <v>23.5277</v>
+        <v>61.0304</v>
       </c>
       <c r="H178">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I178">
-        <v>55.5114</v>
+        <v>41.553</v>
       </c>
       <c r="J178">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="K178">
-        <v>47.2647</v>
+        <v>59.3907</v>
       </c>
     </row>
     <row r="179">
@@ -6905,34 +6965,34 @@
         <v>188</v>
       </c>
       <c r="B179">
-        <v>26.24879</v>
+        <v>27.208416</v>
       </c>
       <c r="C179">
-        <v>-81.08021</v>
+        <v>-82.526437</v>
       </c>
       <c r="D179">
-        <v>29.645888</v>
+        <v>27.235933</v>
       </c>
       <c r="E179">
-        <v>-85.157887</v>
+        <v>-82.512127</v>
       </c>
       <c r="F179">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="G179">
-        <v>4.5048</v>
+        <v>35.0821</v>
       </c>
       <c r="H179">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I179">
-        <v>9.1318</v>
+        <v>25.0288</v>
       </c>
       <c r="J179">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K179">
-        <v>6.9721</v>
+        <v>22.0285</v>
       </c>
     </row>
     <row r="180">
@@ -6940,16 +7000,16 @@
         <v>189</v>
       </c>
       <c r="B180">
-        <v>27.38521</v>
+        <v>26.794747</v>
       </c>
       <c r="C180">
-        <v>-82.81814</v>
+        <v>-80.035049</v>
       </c>
       <c r="D180">
-        <v>26.90248</v>
+        <v>26.812955</v>
       </c>
       <c r="E180">
-        <v>-82.34266</v>
+        <v>-80.031405</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -6958,16 +7018,16 @@
         <v>0.0</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="I180">
-        <v>0.48</v>
+        <v>27.4643</v>
       </c>
       <c r="J180">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K180">
-        <v>0.63</v>
+        <v>17.0465</v>
       </c>
     </row>
     <row r="181">
@@ -6975,34 +7035,34 @@
         <v>190</v>
       </c>
       <c r="B181">
-        <v>17.166991</v>
+        <v>26.781464</v>
       </c>
       <c r="C181">
-        <v>-69.718314</v>
+        <v>-80.032323</v>
       </c>
       <c r="D181">
-        <v>26.962682</v>
+        <v>26.792729</v>
       </c>
       <c r="E181">
-        <v>-80.082175</v>
+        <v>-80.031675</v>
       </c>
       <c r="F181">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G181">
-        <v>9.9314</v>
+        <v>1.5447</v>
       </c>
       <c r="H181">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I181">
-        <v>13.5047</v>
+        <v>46.6602</v>
       </c>
       <c r="J181">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K181">
-        <v>14.8608</v>
+        <v>14.8411</v>
       </c>
     </row>
     <row r="182">
@@ -7010,34 +7070,34 @@
         <v>191</v>
       </c>
       <c r="B182">
-        <v>26.343494</v>
+        <v>26.629405</v>
       </c>
       <c r="C182">
-        <v>-81.364698</v>
+        <v>-80.037423</v>
       </c>
       <c r="D182">
-        <v>30.36724</v>
+        <v>26.646752</v>
       </c>
       <c r="E182">
-        <v>-86.304364</v>
+        <v>-80.036958</v>
       </c>
       <c r="F182">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G182">
-        <v>1.2833</v>
+        <v>2.3452</v>
       </c>
       <c r="H182">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="I182">
-        <v>0.4669</v>
+        <v>88.5292</v>
       </c>
       <c r="J182">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K182">
-        <v>1.6055</v>
+        <v>22.2284</v>
       </c>
     </row>
     <row r="183">
@@ -7045,34 +7105,34 @@
         <v>192</v>
       </c>
       <c r="B183">
-        <v>23.810467</v>
+        <v>24.550383</v>
       </c>
       <c r="C183">
-        <v>-77.8384</v>
+        <v>-81.775512</v>
       </c>
       <c r="D183">
-        <v>26.707006</v>
+        <v>24.552462</v>
       </c>
       <c r="E183">
-        <v>-80.042219</v>
+        <v>-81.765568</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G183">
-        <v>0.0</v>
+        <v>96.9794</v>
       </c>
       <c r="H183">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="I183">
-        <v>10.0138</v>
+        <v>139.8677</v>
       </c>
       <c r="J183">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="K183">
-        <v>1.467</v>
+        <v>106.0918</v>
       </c>
     </row>
     <row r="184">
@@ -7080,34 +7140,34 @@
         <v>193</v>
       </c>
       <c r="B184">
-        <v>21.829614</v>
+        <v>24.690979</v>
       </c>
       <c r="C184">
-        <v>-75.961487</v>
+        <v>-81.086632</v>
       </c>
       <c r="D184">
-        <v>29.978081</v>
+        <v>24.692065</v>
       </c>
       <c r="E184">
-        <v>-85.506773</v>
+        <v>-81.082675</v>
       </c>
       <c r="F184">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G184">
-        <v>27.3779</v>
+        <v>1.03</v>
       </c>
       <c r="H184">
         <v>34</v>
       </c>
       <c r="I184">
-        <v>25.0513</v>
+        <v>43.3566</v>
       </c>
       <c r="J184">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K184">
-        <v>29.1954</v>
+        <v>4.6781</v>
       </c>
     </row>
     <row r="185">
@@ -7115,34 +7175,34 @@
         <v>194</v>
       </c>
       <c r="B185">
-        <v>24.62696</v>
+        <v>27.874586</v>
       </c>
       <c r="C185">
-        <v>-81.31822</v>
+        <v>-80.545315</v>
       </c>
       <c r="D185">
-        <v>24.90595</v>
+        <v>28.043353</v>
       </c>
       <c r="E185">
-        <v>-80.65045</v>
+        <v>-80.454327</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="G185">
-        <v>0.0584</v>
+        <v>243.2681</v>
       </c>
       <c r="H185">
-        <v>11</v>
+        <v>267</v>
       </c>
       <c r="I185">
-        <v>13.5777</v>
+        <v>245.9101</v>
       </c>
       <c r="J185">
-        <v>3</v>
+        <v>261</v>
       </c>
       <c r="K185">
-        <v>1.2766</v>
+        <v>202.5188</v>
       </c>
     </row>
     <row r="186">
@@ -7150,34 +7210,34 @@
         <v>195</v>
       </c>
       <c r="B186">
-        <v>26.8964</v>
+        <v>28.271967</v>
       </c>
       <c r="C186">
-        <v>-82.49111</v>
+        <v>-80.607271</v>
       </c>
       <c r="D186">
-        <v>27.11209</v>
+        <v>28.301428</v>
       </c>
       <c r="E186">
-        <v>-82.46819</v>
+        <v>-80.605359</v>
       </c>
       <c r="F186">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G186">
-        <v>1.0228</v>
+        <v>30.7729</v>
       </c>
       <c r="H186">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="I186">
-        <v>1.0223</v>
+        <v>35.8191</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="K186">
-        <v>2.8619</v>
+        <v>58.3308</v>
       </c>
     </row>
     <row r="187">
@@ -7185,34 +7245,34 @@
         <v>196</v>
       </c>
       <c r="B187">
-        <v>25.16946</v>
+        <v>29.50915</v>
       </c>
       <c r="C187">
-        <v>-79.05287</v>
+        <v>-81.176465</v>
       </c>
       <c r="D187">
-        <v>27.652153</v>
+        <v>29.584532</v>
       </c>
       <c r="E187">
-        <v>-80.352011</v>
+        <v>-81.140733</v>
       </c>
       <c r="F187">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="G187">
-        <v>5.9163</v>
+        <v>48.0654</v>
       </c>
       <c r="H187">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="I187">
-        <v>9.3275</v>
+        <v>107.9494</v>
       </c>
       <c r="J187">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K187">
-        <v>12.7511</v>
+        <v>57.6198</v>
       </c>
     </row>
     <row r="188">
@@ -7220,34 +7280,34 @@
         <v>197</v>
       </c>
       <c r="B188">
-        <v>27.933616</v>
+        <v>27.557286</v>
       </c>
       <c r="C188">
-        <v>-80.439736</v>
+        <v>-80.345901</v>
       </c>
       <c r="D188">
-        <v>29.938454</v>
+        <v>27.62041</v>
       </c>
       <c r="E188">
-        <v>-81.289738</v>
+        <v>-80.321571</v>
       </c>
       <c r="F188">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="G188">
-        <v>2.6663</v>
+        <v>127.2</v>
       </c>
       <c r="H188">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="I188">
-        <v>5.4768</v>
+        <v>133.043</v>
       </c>
       <c r="J188">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="K188">
-        <v>8.747</v>
+        <v>123.1669</v>
       </c>
     </row>
     <row r="189">
@@ -7255,34 +7315,34 @@
         <v>198</v>
       </c>
       <c r="B189">
-        <v>24.284085</v>
+        <v>26.585991</v>
       </c>
       <c r="C189">
-        <v>-79.078895</v>
+        <v>-80.037493</v>
       </c>
       <c r="D189">
-        <v>25.75454</v>
+        <v>26.611645</v>
       </c>
       <c r="E189">
-        <v>-80.158985</v>
+        <v>-80.0365</v>
       </c>
       <c r="F189">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G189">
-        <v>4.0488</v>
+        <v>2.0188</v>
       </c>
       <c r="H189">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="I189">
-        <v>9.2327</v>
+        <v>153.0815</v>
       </c>
       <c r="J189">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="K189">
-        <v>4.9443</v>
+        <v>65.8081</v>
       </c>
     </row>
     <row r="190">
@@ -7290,34 +7350,34 @@
         <v>199</v>
       </c>
       <c r="B190">
-        <v>27.575915</v>
+        <v>29.612897</v>
       </c>
       <c r="C190">
-        <v>-79.597581</v>
+        <v>-84.957805</v>
       </c>
       <c r="D190">
-        <v>29.28556</v>
+        <v>29.682643</v>
       </c>
       <c r="E190">
-        <v>-81.044222</v>
+        <v>-84.796757</v>
       </c>
       <c r="F190">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G190">
-        <v>23.6084</v>
+        <v>17.3701</v>
       </c>
       <c r="H190">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="I190">
-        <v>23.1043</v>
+        <v>58.6451</v>
       </c>
       <c r="J190">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K190">
-        <v>17.3146</v>
+        <v>37.9911</v>
       </c>
     </row>
     <row r="191">
@@ -7325,34 +7385,34 @@
         <v>200</v>
       </c>
       <c r="B191">
-        <v>28.723174</v>
+        <v>29.682643</v>
       </c>
       <c r="C191">
-        <v>-80.227876</v>
+        <v>-84.796757</v>
       </c>
       <c r="D191">
-        <v>29.138736</v>
+        <v>29.771091</v>
       </c>
       <c r="E191">
-        <v>-80.96311</v>
+        <v>-84.691455</v>
       </c>
       <c r="F191">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G191">
-        <v>12.0116</v>
+        <v>41.1051</v>
       </c>
       <c r="H191">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="I191">
-        <v>15.3642</v>
+        <v>100.6614</v>
       </c>
       <c r="J191">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="K191">
-        <v>11.1942</v>
+        <v>72.8167</v>
       </c>
     </row>
     <row r="192">
@@ -7360,34 +7420,34 @@
         <v>201</v>
       </c>
       <c r="B192">
-        <v>20.822479</v>
+        <v>29.850547</v>
       </c>
       <c r="C192">
-        <v>-73.195883</v>
+        <v>-85.389409</v>
       </c>
       <c r="D192">
-        <v>27.812588</v>
+        <v>29.924882</v>
       </c>
       <c r="E192">
-        <v>-80.425483</v>
+        <v>-85.337018</v>
       </c>
       <c r="F192">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G192">
-        <v>10.7523</v>
+        <v>36.5776</v>
       </c>
       <c r="H192">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="I192">
-        <v>6.6796</v>
+        <v>57.4633</v>
       </c>
       <c r="J192">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="K192">
-        <v>2.2517</v>
+        <v>35.2702</v>
       </c>
     </row>
     <row r="193">
@@ -7395,34 +7455,34 @@
         <v>202</v>
       </c>
       <c r="B193">
-        <v>20.880735</v>
+        <v>29.676535</v>
       </c>
       <c r="C193">
-        <v>-72.09143</v>
+        <v>-85.404724</v>
       </c>
       <c r="D193">
-        <v>27.759015</v>
+        <v>29.764176</v>
       </c>
       <c r="E193">
-        <v>-80.39342</v>
+        <v>-85.363114</v>
       </c>
       <c r="F193">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G193">
-        <v>1.1341</v>
+        <v>4.0869</v>
       </c>
       <c r="H193">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I193">
-        <v>0.6748</v>
+        <v>17.4114</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K193">
-        <v>0.6745</v>
+        <v>8.0445</v>
       </c>
     </row>
     <row r="194">
@@ -7430,34 +7490,34 @@
         <v>203</v>
       </c>
       <c r="B194">
-        <v>30.50255</v>
+        <v>29.764176</v>
       </c>
       <c r="C194">
-        <v>-81.27396</v>
+        <v>-85.417073</v>
       </c>
       <c r="D194">
-        <v>29.636305</v>
+        <v>29.878484</v>
       </c>
       <c r="E194">
-        <v>-81.196125</v>
+        <v>-85.384651</v>
       </c>
       <c r="F194">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="G194">
-        <v>0.6366</v>
+        <v>33.3267</v>
       </c>
       <c r="H194">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I194">
-        <v>1.5558</v>
+        <v>35.2979</v>
       </c>
       <c r="J194">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="K194">
-        <v>0.1934</v>
+        <v>42.274</v>
       </c>
     </row>
     <row r="195">
@@ -7465,34 +7525,34 @@
         <v>204</v>
       </c>
       <c r="B195">
-        <v>30.193665</v>
+        <v>27.130719</v>
       </c>
       <c r="C195">
-        <v>-86.605557</v>
+        <v>-80.157811</v>
       </c>
       <c r="D195">
-        <v>30.402293</v>
+        <v>27.163108</v>
       </c>
       <c r="E195">
-        <v>-86.603837</v>
+        <v>-80.145245</v>
       </c>
       <c r="F195">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="G195">
-        <v>1.4178</v>
+        <v>263.3122</v>
       </c>
       <c r="H195">
-        <v>8</v>
+        <v>343</v>
       </c>
       <c r="I195">
-        <v>4.9765</v>
+        <v>410.1992</v>
       </c>
       <c r="J195">
-        <v>3</v>
+        <v>335</v>
       </c>
       <c r="K195">
-        <v>1.0716</v>
+        <v>379.229</v>
       </c>
     </row>
     <row r="196">
@@ -7500,34 +7560,34 @@
         <v>205</v>
       </c>
       <c r="B196">
-        <v>27.006331</v>
+        <v>29.630006</v>
       </c>
       <c r="C196">
-        <v>-82.26449</v>
+        <v>-85.223564</v>
       </c>
       <c r="D196">
-        <v>30.35173</v>
+        <v>29.681156</v>
       </c>
       <c r="E196">
-        <v>-86.2149</v>
+        <v>-85.093881</v>
       </c>
       <c r="F196">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="G196">
-        <v>2.1549</v>
+        <v>93.974</v>
       </c>
       <c r="H196">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="I196">
-        <v>6.0958</v>
+        <v>176.8116</v>
       </c>
       <c r="J196">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="K196">
-        <v>2.7907</v>
+        <v>80.8805</v>
       </c>
     </row>
     <row r="197">
@@ -7535,33 +7595,733 @@
         <v>206</v>
       </c>
       <c r="B197">
-        <v>27.9995</v>
+        <v>26.897057</v>
       </c>
       <c r="C197">
-        <v>-82.93345</v>
+        <v>-82.353414</v>
       </c>
       <c r="D197">
-        <v>24.51813</v>
+        <v>26.910938</v>
       </c>
       <c r="E197">
-        <v>-81.9699</v>
+        <v>-82.340576</v>
       </c>
       <c r="F197">
+        <v>16</v>
+      </c>
+      <c r="G197">
+        <v>9.0105</v>
+      </c>
+      <c r="H197">
+        <v>16</v>
+      </c>
+      <c r="I197">
+        <v>10.7442</v>
+      </c>
+      <c r="J197">
+        <v>40</v>
+      </c>
+      <c r="K197">
+        <v>26.2298</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>207</v>
+      </c>
+      <c r="B198">
+        <v>25.850466</v>
+      </c>
+      <c r="C198">
+        <v>-81.636839</v>
+      </c>
+      <c r="D198">
+        <v>25.895294</v>
+      </c>
+      <c r="E198">
+        <v>-81.540138</v>
+      </c>
+      <c r="F198">
         <v>0</v>
       </c>
-      <c r="G197">
+      <c r="G198">
         <v>0.0</v>
       </c>
-      <c r="H197">
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0.0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>208</v>
+      </c>
+      <c r="B199">
+        <v>26.956523</v>
+      </c>
+      <c r="C199">
+        <v>-80.080544</v>
+      </c>
+      <c r="D199">
+        <v>26.970431</v>
+      </c>
+      <c r="E199">
+        <v>-80.076245</v>
+      </c>
+      <c r="F199">
+        <v>115</v>
+      </c>
+      <c r="G199">
+        <v>106.6605</v>
+      </c>
+      <c r="H199">
+        <v>144</v>
+      </c>
+      <c r="I199">
+        <v>162.4419</v>
+      </c>
+      <c r="J199">
+        <v>162</v>
+      </c>
+      <c r="K199">
+        <v>176.2842</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>209</v>
+      </c>
+      <c r="B200">
+        <v>30.355204</v>
+      </c>
+      <c r="C200">
+        <v>-86.317194</v>
+      </c>
+      <c r="D200">
+        <v>30.366741</v>
+      </c>
+      <c r="E200">
+        <v>-86.264535</v>
+      </c>
+      <c r="F200">
+        <v>35</v>
+      </c>
+      <c r="G200">
+        <v>18.3428</v>
+      </c>
+      <c r="H200">
+        <v>57</v>
+      </c>
+      <c r="I200">
+        <v>42.4978</v>
+      </c>
+      <c r="J200">
+        <v>39</v>
+      </c>
+      <c r="K200">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>210</v>
+      </c>
+      <c r="B201">
+        <v>26.692502</v>
+      </c>
+      <c r="C201">
+        <v>-80.034794</v>
+      </c>
+      <c r="D201">
+        <v>26.72723</v>
+      </c>
+      <c r="E201">
+        <v>-80.032824</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0.0</v>
+      </c>
+      <c r="H201">
+        <v>142</v>
+      </c>
+      <c r="I201">
+        <v>148.0439</v>
+      </c>
+      <c r="J201">
+        <v>44</v>
+      </c>
+      <c r="K201">
+        <v>44.3253</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>211</v>
+      </c>
+      <c r="B202">
+        <v>29.955533</v>
+      </c>
+      <c r="C202">
+        <v>-85.687471</v>
+      </c>
+      <c r="D202">
+        <v>30.092539</v>
+      </c>
+      <c r="E202">
+        <v>-85.448952</v>
+      </c>
+      <c r="F202">
+        <v>336</v>
+      </c>
+      <c r="G202">
+        <v>262.7304</v>
+      </c>
+      <c r="H202">
+        <v>283</v>
+      </c>
+      <c r="I202">
+        <v>212.193</v>
+      </c>
+      <c r="J202">
+        <v>264</v>
+      </c>
+      <c r="K202">
+        <v>204.9618</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>212</v>
+      </c>
+      <c r="B203">
+        <v>24.908004</v>
+      </c>
+      <c r="C203">
+        <v>-80.641833</v>
+      </c>
+      <c r="D203">
+        <v>24.914354</v>
+      </c>
+      <c r="E203">
+        <v>-80.633773</v>
+      </c>
+      <c r="F203">
         <v>1</v>
       </c>
-      <c r="I197">
-        <v>0.5511</v>
-      </c>
-      <c r="J197">
+      <c r="G203">
+        <v>0.0584</v>
+      </c>
+      <c r="H203">
+        <v>105</v>
+      </c>
+      <c r="I203">
+        <v>115.781</v>
+      </c>
+      <c r="J203">
+        <v>21</v>
+      </c>
+      <c r="K203">
+        <v>16.3477</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>213</v>
+      </c>
+      <c r="B204">
+        <v>26.219944</v>
+      </c>
+      <c r="C204">
+        <v>-81.827764</v>
+      </c>
+      <c r="D204">
+        <v>26.272275</v>
+      </c>
+      <c r="E204">
+        <v>-81.817562</v>
+      </c>
+      <c r="F204">
+        <v>40</v>
+      </c>
+      <c r="G204">
+        <v>19.0962</v>
+      </c>
+      <c r="H204">
+        <v>23</v>
+      </c>
+      <c r="I204">
+        <v>11.186</v>
+      </c>
+      <c r="J204">
+        <v>18</v>
+      </c>
+      <c r="K204">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>214</v>
+      </c>
+      <c r="B205">
+        <v>27.054913</v>
+      </c>
+      <c r="C205">
+        <v>-82.467849</v>
+      </c>
+      <c r="D205">
+        <v>27.112444</v>
+      </c>
+      <c r="E205">
+        <v>-82.441893</v>
+      </c>
+      <c r="F205">
+        <v>28</v>
+      </c>
+      <c r="G205">
+        <v>18.7865</v>
+      </c>
+      <c r="H205">
+        <v>54</v>
+      </c>
+      <c r="I205">
+        <v>47.6959</v>
+      </c>
+      <c r="J205">
+        <v>70</v>
+      </c>
+      <c r="K205">
+        <v>61.4991</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>215</v>
+      </c>
+      <c r="B206">
+        <v>27.62041</v>
+      </c>
+      <c r="C206">
+        <v>-80.361752</v>
+      </c>
+      <c r="D206">
+        <v>27.674945</v>
+      </c>
+      <c r="E206">
+        <v>-80.345899</v>
+      </c>
+      <c r="F206">
+        <v>68</v>
+      </c>
+      <c r="G206">
+        <v>59.8675</v>
+      </c>
+      <c r="H206">
+        <v>90</v>
+      </c>
+      <c r="I206">
+        <v>88.0487</v>
+      </c>
+      <c r="J206">
+        <v>97</v>
+      </c>
+      <c r="K206">
+        <v>95.9665</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>216</v>
+      </c>
+      <c r="B207">
+        <v>29.909626</v>
+      </c>
+      <c r="C207">
+        <v>-81.30392</v>
+      </c>
+      <c r="D207">
+        <v>29.952538</v>
+      </c>
+      <c r="E207">
+        <v>-81.288512</v>
+      </c>
+      <c r="F207">
+        <v>108</v>
+      </c>
+      <c r="G207">
+        <v>76.2471</v>
+      </c>
+      <c r="H207">
+        <v>83</v>
+      </c>
+      <c r="I207">
+        <v>59.905</v>
+      </c>
+      <c r="J207">
+        <v>131</v>
+      </c>
+      <c r="K207">
+        <v>94.428</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>217</v>
+      </c>
+      <c r="B208">
+        <v>25.732318</v>
+      </c>
+      <c r="C208">
+        <v>-80.160556</v>
+      </c>
+      <c r="D208">
+        <v>25.757794</v>
+      </c>
+      <c r="E208">
+        <v>-80.142299</v>
+      </c>
+      <c r="F208">
+        <v>88</v>
+      </c>
+      <c r="G208">
+        <v>106.8082</v>
+      </c>
+      <c r="H208">
+        <v>191</v>
+      </c>
+      <c r="I208">
+        <v>252.1226</v>
+      </c>
+      <c r="J208">
+        <v>85</v>
+      </c>
+      <c r="K208">
+        <v>114.8872</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>218</v>
+      </c>
+      <c r="B209">
+        <v>29.218528</v>
+      </c>
+      <c r="C209">
+        <v>-81.083844</v>
+      </c>
+      <c r="D209">
+        <v>29.387243</v>
+      </c>
+      <c r="E209">
+        <v>-81.002471</v>
+      </c>
+      <c r="F209">
+        <v>297</v>
+      </c>
+      <c r="G209">
+        <v>275.7561</v>
+      </c>
+      <c r="H209">
+        <v>365</v>
+      </c>
+      <c r="I209">
+        <v>315.7436</v>
+      </c>
+      <c r="J209">
+        <v>324</v>
+      </c>
+      <c r="K209">
+        <v>258.5303</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>219</v>
+      </c>
+      <c r="B210">
+        <v>29.078455</v>
+      </c>
+      <c r="C210">
+        <v>-81.002471</v>
+      </c>
+      <c r="D210">
+        <v>29.218528</v>
+      </c>
+      <c r="E210">
+        <v>-80.918108</v>
+      </c>
+      <c r="F210">
+        <v>290</v>
+      </c>
+      <c r="G210">
+        <v>271.4802</v>
+      </c>
+      <c r="H210">
+        <v>444</v>
+      </c>
+      <c r="I210">
+        <v>402.964</v>
+      </c>
+      <c r="J210">
+        <v>362</v>
+      </c>
+      <c r="K210">
+        <v>314.0852</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>220</v>
+      </c>
+      <c r="B211">
+        <v>27.767709</v>
+      </c>
+      <c r="C211">
+        <v>-80.43293</v>
+      </c>
+      <c r="D211">
+        <v>27.833257</v>
+      </c>
+      <c r="E211">
+        <v>-80.398712</v>
+      </c>
+      <c r="F211">
+        <v>57</v>
+      </c>
+      <c r="G211">
+        <v>48.4504</v>
+      </c>
+      <c r="H211">
+        <v>37</v>
+      </c>
+      <c r="I211">
+        <v>26.5816</v>
+      </c>
+      <c r="J211">
+        <v>45</v>
+      </c>
+      <c r="K211">
+        <v>37.8248</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>221</v>
+      </c>
+      <c r="B212">
+        <v>27.756911</v>
+      </c>
+      <c r="C212">
+        <v>-80.398794</v>
+      </c>
+      <c r="D212">
+        <v>27.767862</v>
+      </c>
+      <c r="E212">
+        <v>-80.392673</v>
+      </c>
+      <c r="F212">
+        <v>11</v>
+      </c>
+      <c r="G212">
+        <v>6.7566</v>
+      </c>
+      <c r="H212">
+        <v>12</v>
+      </c>
+      <c r="I212">
+        <v>13.1943</v>
+      </c>
+      <c r="J212">
+        <v>13</v>
+      </c>
+      <c r="K212">
+        <v>12.9589</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>222</v>
+      </c>
+      <c r="B213">
+        <v>29.63368</v>
+      </c>
+      <c r="C213">
+        <v>-81.201497</v>
+      </c>
+      <c r="D213">
+        <v>29.643187</v>
+      </c>
+      <c r="E213">
+        <v>-81.197575</v>
+      </c>
+      <c r="F213">
+        <v>12</v>
+      </c>
+      <c r="G213">
+        <v>8.9813</v>
+      </c>
+      <c r="H213">
+        <v>16</v>
+      </c>
+      <c r="I213">
+        <v>14.4304</v>
+      </c>
+      <c r="J213">
+        <v>17</v>
+      </c>
+      <c r="K213">
+        <v>15.643</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>223</v>
+      </c>
+      <c r="B214">
+        <v>30.392673</v>
+      </c>
+      <c r="C214">
+        <v>-86.633172</v>
+      </c>
+      <c r="D214">
+        <v>30.396527</v>
+      </c>
+      <c r="E214">
+        <v>-86.582795</v>
+      </c>
+      <c r="F214">
+        <v>83</v>
+      </c>
+      <c r="G214">
+        <v>85.8529</v>
+      </c>
+      <c r="H214">
+        <v>202</v>
+      </c>
+      <c r="I214">
+        <v>165.4068</v>
+      </c>
+      <c r="J214">
+        <v>115</v>
+      </c>
+      <c r="K214">
+        <v>95.2059</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>224</v>
+      </c>
+      <c r="B215">
+        <v>30.331686</v>
+      </c>
+      <c r="C215">
+        <v>-86.264535</v>
+      </c>
+      <c r="D215">
+        <v>30.355204</v>
+      </c>
+      <c r="E215">
+        <v>-86.179915</v>
+      </c>
+      <c r="F215">
+        <v>87</v>
+      </c>
+      <c r="G215">
+        <v>74.1129</v>
+      </c>
+      <c r="H215">
+        <v>236</v>
+      </c>
+      <c r="I215">
+        <v>154.1747</v>
+      </c>
+      <c r="J215">
+        <v>119</v>
+      </c>
+      <c r="K215">
+        <v>83.4237</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>225</v>
+      </c>
+      <c r="B216">
+        <v>26.272275</v>
+      </c>
+      <c r="C216">
+        <v>-81.831472</v>
+      </c>
+      <c r="D216">
+        <v>26.288585</v>
+      </c>
+      <c r="E216">
+        <v>-81.827764</v>
+      </c>
+      <c r="F216">
+        <v>8</v>
+      </c>
+      <c r="G216">
+        <v>3.3704</v>
+      </c>
+      <c r="H216">
+        <v>6</v>
+      </c>
+      <c r="I216">
+        <v>3.5009</v>
+      </c>
+      <c r="J216">
+        <v>4</v>
+      </c>
+      <c r="K216">
+        <v>1.5363</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>226</v>
+      </c>
+      <c r="B217">
+        <v>24.523184</v>
+      </c>
+      <c r="C217">
+        <v>-81.979396</v>
+      </c>
+      <c r="D217">
+        <v>24.524514</v>
+      </c>
+      <c r="E217">
+        <v>-81.967044</v>
+      </c>
+      <c r="F217">
         <v>0</v>
       </c>
-      <c r="K197">
+      <c r="G217">
+        <v>0.0</v>
+      </c>
+      <c r="H217">
+        <v>9</v>
+      </c>
+      <c r="I217">
+        <v>6.3468</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
         <v>0.0</v>
       </c>
     </row>

--- a/beaching_data_all.xlsx
+++ b/beaching_data_all.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
   <si>
     <t xml:space="preserve">beach</t>
   </si>
@@ -361,7 +361,16 @@
     <t xml:space="preserve">Hutchinson Island (South)</t>
   </si>
   <si>
-    <t xml:space="preserve">Indian River County Beaches</t>
+    <t xml:space="preserve">Indian River County Beaches (North)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian River County Beaches (South)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian River Shores (North)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian River Shores (South)</t>
   </si>
   <si>
     <t xml:space="preserve">J.D. MacArthur Beach State Park</t>
@@ -412,9 +421,6 @@
     <t xml:space="preserve">Little Crawl Key</t>
   </si>
   <si>
-    <t xml:space="preserve">Little Gasparilla Island</t>
-  </si>
-  <si>
     <t xml:space="preserve">Little Talbot Island State Park</t>
   </si>
   <si>
@@ -442,9 +448,6 @@
     <t xml:space="preserve">Manalapan (North)</t>
   </si>
   <si>
-    <t xml:space="preserve">Manasota Key (Casperson's Beach)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Manasota Key (Charlotte County)</t>
   </si>
   <si>
@@ -688,6 +691,9 @@
     <t xml:space="preserve">Venice Beaches</t>
   </si>
   <si>
+    <t xml:space="preserve">Vero Beach</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vilano Beach</t>
   </si>
   <si>
@@ -704,6 +710,9 @@
   </si>
   <si>
     <t xml:space="preserve">Wabasso Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wabasso Beach (South)</t>
   </si>
   <si>
     <t xml:space="preserve">Walton County Beaches (East)</t>
@@ -4510,16 +4519,16 @@
         <v>117</v>
       </c>
       <c r="B108">
-        <v>27.557281</v>
+        <v>27.674945</v>
       </c>
       <c r="C108">
-        <v>-80.39871</v>
+        <v>-80.374105</v>
       </c>
       <c r="D108">
-        <v>27.767704</v>
+        <v>27.71141</v>
       </c>
       <c r="E108">
-        <v>-80.321568</v>
+        <v>-80.361754</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -4545,16 +4554,16 @@
         <v>118</v>
       </c>
       <c r="B109">
-        <v>26.81295</v>
+        <v>27.557286</v>
       </c>
       <c r="C109">
-        <v>-80.041272</v>
+        <v>-80.345901</v>
       </c>
       <c r="D109">
-        <v>26.836195</v>
+        <v>27.62041</v>
       </c>
       <c r="E109">
-        <v>-80.035047</v>
+        <v>-80.321571</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -4580,16 +4589,16 @@
         <v>119</v>
       </c>
       <c r="B110">
-        <v>28.365521</v>
+        <v>27.750635</v>
       </c>
       <c r="C110">
-        <v>-80.602354</v>
+        <v>-80.392673</v>
       </c>
       <c r="D110">
-        <v>28.407948</v>
+        <v>27.756911</v>
       </c>
       <c r="E110">
-        <v>-80.588538</v>
+        <v>-80.389043</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -4615,16 +4624,16 @@
         <v>120</v>
       </c>
       <c r="B111">
-        <v>26.836195</v>
+        <v>27.71141</v>
       </c>
       <c r="C111">
-        <v>-80.065413</v>
+        <v>-80.389043</v>
       </c>
       <c r="D111">
-        <v>26.920492</v>
+        <v>27.750635</v>
       </c>
       <c r="E111">
-        <v>-80.041272</v>
+        <v>-80.374105</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -4650,16 +4659,16 @@
         <v>121</v>
       </c>
       <c r="B112">
-        <v>26.920492</v>
+        <v>26.81295</v>
       </c>
       <c r="C112">
-        <v>-80.071423</v>
+        <v>-80.041272</v>
       </c>
       <c r="D112">
-        <v>26.943583</v>
+        <v>26.836195</v>
       </c>
       <c r="E112">
-        <v>-80.065413</v>
+        <v>-80.035047</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -4685,16 +4694,16 @@
         <v>122</v>
       </c>
       <c r="B113">
-        <v>26.944526</v>
+        <v>28.365521</v>
       </c>
       <c r="C113">
-        <v>-80.076242</v>
+        <v>-80.602354</v>
       </c>
       <c r="D113">
-        <v>26.956518</v>
+        <v>28.407948</v>
       </c>
       <c r="E113">
-        <v>-80.071031</v>
+        <v>-80.588538</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -4720,16 +4729,16 @@
         <v>123</v>
       </c>
       <c r="B114">
-        <v>26.970426</v>
+        <v>26.836195</v>
       </c>
       <c r="C114">
-        <v>-80.124852</v>
+        <v>-80.065413</v>
       </c>
       <c r="D114">
-        <v>27.086364</v>
+        <v>26.920492</v>
       </c>
       <c r="E114">
-        <v>-80.080541</v>
+        <v>-80.041272</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -4755,16 +4764,16 @@
         <v>124</v>
       </c>
       <c r="B115">
-        <v>26.046946</v>
+        <v>26.920492</v>
       </c>
       <c r="C115">
-        <v>-81.801744</v>
+        <v>-80.071423</v>
       </c>
       <c r="D115">
-        <v>26.091792</v>
+        <v>26.943583</v>
       </c>
       <c r="E115">
-        <v>-81.78074</v>
+        <v>-80.065413</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -4790,16 +4799,16 @@
         <v>125</v>
       </c>
       <c r="B116">
-        <v>25.991496</v>
+        <v>26.944526</v>
       </c>
       <c r="C116">
-        <v>-81.78074</v>
+        <v>-80.076242</v>
       </c>
       <c r="D116">
-        <v>26.046946</v>
+        <v>26.956518</v>
       </c>
       <c r="E116">
-        <v>-81.750807</v>
+        <v>-80.071031</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -4825,16 +4834,16 @@
         <v>126</v>
       </c>
       <c r="B117">
-        <v>25.68302</v>
+        <v>26.970426</v>
       </c>
       <c r="C117">
-        <v>-80.15661</v>
+        <v>-80.124852</v>
       </c>
       <c r="D117">
-        <v>25.72638</v>
+        <v>27.086364</v>
       </c>
       <c r="E117">
-        <v>-80.147572</v>
+        <v>-80.080541</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4860,16 +4869,16 @@
         <v>127</v>
       </c>
       <c r="B118">
-        <v>25.728135</v>
+        <v>26.046946</v>
       </c>
       <c r="C118">
-        <v>-80.156137</v>
+        <v>-81.801744</v>
       </c>
       <c r="D118">
-        <v>25.728455</v>
+        <v>26.091792</v>
       </c>
       <c r="E118">
-        <v>-80.155067</v>
+        <v>-81.78074</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -4895,16 +4904,16 @@
         <v>128</v>
       </c>
       <c r="B119">
-        <v>25.725628</v>
+        <v>25.991496</v>
       </c>
       <c r="C119">
-        <v>-80.158074</v>
+        <v>-81.78074</v>
       </c>
       <c r="D119">
-        <v>25.72615</v>
+        <v>26.046946</v>
       </c>
       <c r="E119">
-        <v>-80.157499</v>
+        <v>-81.750807</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -4930,16 +4939,16 @@
         <v>129</v>
       </c>
       <c r="B120">
-        <v>24.716403</v>
+        <v>25.68302</v>
       </c>
       <c r="C120">
-        <v>-81.023778</v>
+        <v>-80.15661</v>
       </c>
       <c r="D120">
-        <v>24.72179</v>
+        <v>25.72638</v>
       </c>
       <c r="E120">
-        <v>-81.011948</v>
+        <v>-80.147572</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -4965,16 +4974,16 @@
         <v>130</v>
       </c>
       <c r="B121">
-        <v>26.61164</v>
+        <v>25.728135</v>
       </c>
       <c r="C121">
-        <v>-80.036588</v>
+        <v>-80.156137</v>
       </c>
       <c r="D121">
-        <v>26.615223</v>
+        <v>25.728455</v>
       </c>
       <c r="E121">
-        <v>-80.036497</v>
+        <v>-80.155067</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -5000,16 +5009,16 @@
         <v>131</v>
       </c>
       <c r="B122">
-        <v>26.583946</v>
+        <v>25.725628</v>
       </c>
       <c r="C122">
-        <v>-80.037563</v>
+        <v>-80.158074</v>
       </c>
       <c r="D122">
-        <v>26.585986</v>
+        <v>25.72615</v>
       </c>
       <c r="E122">
-        <v>-80.037486</v>
+        <v>-80.157499</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -5035,16 +5044,16 @@
         <v>132</v>
       </c>
       <c r="B123">
-        <v>27.296716</v>
+        <v>24.716403</v>
       </c>
       <c r="C123">
-        <v>-82.588606</v>
+        <v>-81.023778</v>
       </c>
       <c r="D123">
-        <v>27.326699</v>
+        <v>24.72179</v>
       </c>
       <c r="E123">
-        <v>-82.564269</v>
+        <v>-81.011948</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -5070,16 +5079,16 @@
         <v>133</v>
       </c>
       <c r="B124">
-        <v>24.73987</v>
+        <v>26.61164</v>
       </c>
       <c r="C124">
-        <v>-80.98347</v>
+        <v>-80.036588</v>
       </c>
       <c r="D124">
-        <v>24.741482</v>
+        <v>26.615223</v>
       </c>
       <c r="E124">
-        <v>-80.979963</v>
+        <v>-80.036497</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -5105,16 +5114,16 @@
         <v>134</v>
       </c>
       <c r="B125">
-        <v>26.81584</v>
+        <v>26.583946</v>
       </c>
       <c r="C125">
-        <v>-82.299085</v>
+        <v>-80.037563</v>
       </c>
       <c r="D125">
-        <v>26.839613</v>
+        <v>26.585986</v>
       </c>
       <c r="E125">
-        <v>-82.28129</v>
+        <v>-80.037486</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -5140,16 +5149,16 @@
         <v>135</v>
       </c>
       <c r="B126">
-        <v>30.426477</v>
+        <v>27.296716</v>
       </c>
       <c r="C126">
-        <v>-81.42591</v>
+        <v>-82.588606</v>
       </c>
       <c r="D126">
-        <v>30.48997</v>
+        <v>27.326699</v>
       </c>
       <c r="E126">
-        <v>-81.406087</v>
+        <v>-82.564269</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -5175,16 +5184,16 @@
         <v>136</v>
       </c>
       <c r="B127">
-        <v>24.802978</v>
+        <v>24.73987</v>
       </c>
       <c r="C127">
-        <v>-80.848833</v>
+        <v>-80.98347</v>
       </c>
       <c r="D127">
-        <v>24.805638</v>
+        <v>24.741482</v>
       </c>
       <c r="E127">
-        <v>-80.841912</v>
+        <v>-80.979963</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -5210,16 +5219,16 @@
         <v>137</v>
       </c>
       <c r="B128">
-        <v>24.805638</v>
+        <v>30.426477</v>
       </c>
       <c r="C128">
-        <v>-80.841912</v>
+        <v>-81.42591</v>
       </c>
       <c r="D128">
-        <v>24.81259</v>
+        <v>30.48997</v>
       </c>
       <c r="E128">
-        <v>-80.817545</v>
+        <v>-81.406087</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -5245,16 +5254,16 @@
         <v>138</v>
       </c>
       <c r="B129">
-        <v>24.811465</v>
+        <v>24.802978</v>
       </c>
       <c r="C129">
-        <v>-80.798569</v>
+        <v>-80.848833</v>
       </c>
       <c r="D129">
-        <v>24.821441</v>
+        <v>24.805638</v>
       </c>
       <c r="E129">
-        <v>-80.787588</v>
+        <v>-80.841912</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -5280,16 +5289,16 @@
         <v>139</v>
       </c>
       <c r="B130">
-        <v>27.389659</v>
+        <v>24.805638</v>
       </c>
       <c r="C130">
-        <v>-82.688671</v>
+        <v>-80.841912</v>
       </c>
       <c r="D130">
-        <v>27.435221</v>
+        <v>24.81259</v>
       </c>
       <c r="E130">
-        <v>-82.642832</v>
+        <v>-80.817545</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -5315,16 +5324,16 @@
         <v>140</v>
       </c>
       <c r="B131">
-        <v>27.328393</v>
+        <v>24.811465</v>
       </c>
       <c r="C131">
-        <v>-82.642832</v>
+        <v>-80.798569</v>
       </c>
       <c r="D131">
-        <v>27.389659</v>
+        <v>24.821441</v>
       </c>
       <c r="E131">
-        <v>-82.586293</v>
+        <v>-80.787588</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -5350,16 +5359,16 @@
         <v>141</v>
       </c>
       <c r="B132">
-        <v>26.379221</v>
+        <v>27.389659</v>
       </c>
       <c r="C132">
-        <v>-81.886154</v>
+        <v>-82.688671</v>
       </c>
       <c r="D132">
-        <v>26.40367</v>
+        <v>27.435221</v>
       </c>
       <c r="E132">
-        <v>-81.868648</v>
+        <v>-82.642832</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -5385,16 +5394,16 @@
         <v>142</v>
       </c>
       <c r="B133">
-        <v>24.84841</v>
+        <v>27.328393</v>
       </c>
       <c r="C133">
-        <v>-80.734713</v>
+        <v>-82.642832</v>
       </c>
       <c r="D133">
-        <v>24.860572</v>
+        <v>27.389659</v>
       </c>
       <c r="E133">
-        <v>-80.719734</v>
+        <v>-82.586293</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -5420,16 +5429,16 @@
         <v>143</v>
       </c>
       <c r="B134">
-        <v>26.549394</v>
+        <v>26.379221</v>
       </c>
       <c r="C134">
-        <v>-80.041771</v>
+        <v>-81.886154</v>
       </c>
       <c r="D134">
-        <v>26.583932</v>
+        <v>26.40367</v>
       </c>
       <c r="E134">
-        <v>-80.037567</v>
+        <v>-81.868648</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -5455,16 +5464,16 @@
         <v>144</v>
       </c>
       <c r="B135">
-        <v>27.03676</v>
+        <v>24.84841</v>
       </c>
       <c r="C135">
-        <v>-82.44189</v>
+        <v>-80.734713</v>
       </c>
       <c r="D135">
-        <v>27.054908</v>
+        <v>24.860572</v>
       </c>
       <c r="E135">
-        <v>-82.42928</v>
+        <v>-80.719734</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -5490,16 +5499,16 @@
         <v>145</v>
       </c>
       <c r="B136">
-        <v>26.910933</v>
+        <v>26.549394</v>
       </c>
       <c r="C136">
-        <v>-82.37429</v>
+        <v>-80.041771</v>
       </c>
       <c r="D136">
-        <v>26.945964</v>
+        <v>26.583932</v>
       </c>
       <c r="E136">
-        <v>-82.35341</v>
+        <v>-80.037567</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -5525,16 +5534,16 @@
         <v>146</v>
       </c>
       <c r="B137">
+        <v>26.910933</v>
+      </c>
+      <c r="C137">
+        <v>-82.37429</v>
+      </c>
+      <c r="D137">
         <v>26.945964</v>
       </c>
-      <c r="C137">
-        <v>-82.42928</v>
-      </c>
-      <c r="D137">
-        <v>27.03676</v>
-      </c>
       <c r="E137">
-        <v>-82.37429</v>
+        <v>-82.35341</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -5560,16 +5569,16 @@
         <v>147</v>
       </c>
       <c r="B138">
-        <v>25.909404</v>
+        <v>26.945964</v>
       </c>
       <c r="C138">
-        <v>-81.752636</v>
+        <v>-82.42928</v>
       </c>
       <c r="D138">
-        <v>25.964073</v>
+        <v>27.03676</v>
       </c>
       <c r="E138">
-        <v>-81.729021</v>
+        <v>-82.37429</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -5595,16 +5604,16 @@
         <v>148</v>
       </c>
       <c r="B139">
-        <v>29.643182</v>
+        <v>25.909404</v>
       </c>
       <c r="C139">
-        <v>-81.21312</v>
+        <v>-81.752636</v>
       </c>
       <c r="D139">
-        <v>29.67085</v>
+        <v>25.964073</v>
       </c>
       <c r="E139">
-        <v>-81.201494</v>
+        <v>-81.729021</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -5630,16 +5639,16 @@
         <v>149</v>
       </c>
       <c r="B140">
-        <v>30.381821</v>
+        <v>29.643182</v>
       </c>
       <c r="C140">
-        <v>-81.396393</v>
+        <v>-81.21312</v>
       </c>
       <c r="D140">
-        <v>30.397033</v>
+        <v>29.67085</v>
       </c>
       <c r="E140">
-        <v>-81.39212</v>
+        <v>-81.201494</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -5665,16 +5674,16 @@
         <v>150</v>
       </c>
       <c r="B141">
-        <v>28.568612</v>
+        <v>30.381821</v>
       </c>
       <c r="C141">
-        <v>-80.624022</v>
+        <v>-81.396393</v>
       </c>
       <c r="D141">
-        <v>28.644191</v>
+        <v>30.397033</v>
       </c>
       <c r="E141">
-        <v>-80.569098</v>
+        <v>-81.39212</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -5700,16 +5709,16 @@
         <v>151</v>
       </c>
       <c r="B142">
-        <v>29.92489</v>
+        <v>28.568612</v>
       </c>
       <c r="C142">
-        <v>-85.449027</v>
+        <v>-80.624022</v>
       </c>
       <c r="D142">
-        <v>29.955296</v>
+        <v>28.644191</v>
       </c>
       <c r="E142">
-        <v>-85.38928</v>
+        <v>-80.569098</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -5735,16 +5744,16 @@
         <v>152</v>
       </c>
       <c r="B143">
-        <v>25.764274</v>
+        <v>29.92489</v>
       </c>
       <c r="C143">
-        <v>-80.130755</v>
+        <v>-85.449027</v>
       </c>
       <c r="D143">
-        <v>25.957118</v>
+        <v>29.955296</v>
       </c>
       <c r="E143">
-        <v>-80.118494</v>
+        <v>-85.38928</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -5770,16 +5779,16 @@
         <v>153</v>
       </c>
       <c r="B144">
-        <v>28.105808</v>
+        <v>25.764274</v>
       </c>
       <c r="C144">
-        <v>-80.596746</v>
+        <v>-80.130755</v>
       </c>
       <c r="D144">
-        <v>28.212675</v>
+        <v>25.957118</v>
       </c>
       <c r="E144">
-        <v>-80.570181</v>
+        <v>-80.118494</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -5805,16 +5814,16 @@
         <v>154</v>
       </c>
       <c r="B145">
-        <v>30.366735</v>
+        <v>28.105808</v>
       </c>
       <c r="C145">
-        <v>-86.39736</v>
+        <v>-80.596746</v>
       </c>
       <c r="D145">
-        <v>30.378833</v>
+        <v>28.212675</v>
       </c>
       <c r="E145">
-        <v>-86.317189</v>
+        <v>-80.570181</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -5840,16 +5849,16 @@
         <v>155</v>
       </c>
       <c r="B146">
-        <v>26.06043</v>
+        <v>30.366735</v>
       </c>
       <c r="C146">
-        <v>-80.11138</v>
+        <v>-86.39736</v>
       </c>
       <c r="D146">
-        <v>26.092238</v>
+        <v>30.378833</v>
       </c>
       <c r="E146">
-        <v>-80.108145</v>
+        <v>-86.317189</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -5875,16 +5884,16 @@
         <v>156</v>
       </c>
       <c r="B147">
-        <v>26.093527</v>
+        <v>26.06043</v>
       </c>
       <c r="C147">
-        <v>-81.814249</v>
+        <v>-80.11138</v>
       </c>
       <c r="D147">
-        <v>26.173663</v>
+        <v>26.092238</v>
       </c>
       <c r="E147">
-        <v>-81.800885</v>
+        <v>-80.108145</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -5910,16 +5919,16 @@
         <v>157</v>
       </c>
       <c r="B148">
-        <v>24.549702</v>
+        <v>26.093527</v>
       </c>
       <c r="C148">
-        <v>-81.779688</v>
+        <v>-81.814249</v>
       </c>
       <c r="D148">
-        <v>24.55039</v>
+        <v>26.173663</v>
       </c>
       <c r="E148">
-        <v>-81.776581</v>
+        <v>-81.800885</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -5945,16 +5954,16 @@
         <v>158</v>
       </c>
       <c r="B149">
-        <v>30.37101</v>
+        <v>24.549702</v>
       </c>
       <c r="C149">
-        <v>-86.918744</v>
+        <v>-81.779688</v>
       </c>
       <c r="D149">
-        <v>30.381512</v>
+        <v>24.55039</v>
       </c>
       <c r="E149">
-        <v>-86.849454</v>
+        <v>-81.776581</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -5980,16 +5989,16 @@
         <v>159</v>
       </c>
       <c r="B150">
-        <v>28.938628</v>
+        <v>30.37101</v>
       </c>
       <c r="C150">
-        <v>-80.91776</v>
+        <v>-86.918744</v>
       </c>
       <c r="D150">
-        <v>29.074478</v>
+        <v>30.381512</v>
       </c>
       <c r="E150">
-        <v>-80.830145</v>
+        <v>-86.849454</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -6015,16 +6024,16 @@
         <v>160</v>
       </c>
       <c r="B151">
-        <v>26.593234</v>
+        <v>28.938628</v>
       </c>
       <c r="C151">
-        <v>-82.224353</v>
+        <v>-80.91776</v>
       </c>
       <c r="D151">
-        <v>26.607012</v>
+        <v>29.074478</v>
       </c>
       <c r="E151">
-        <v>-82.220238</v>
+        <v>-80.830145</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -6050,16 +6059,16 @@
         <v>161</v>
       </c>
       <c r="B152">
-        <v>26.555672</v>
+        <v>26.593234</v>
       </c>
       <c r="C152">
-        <v>-82.202057</v>
+        <v>-82.224353</v>
       </c>
       <c r="D152">
-        <v>26.560105</v>
+        <v>26.607012</v>
       </c>
       <c r="E152">
-        <v>-82.200216</v>
+        <v>-82.220238</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -6085,16 +6094,16 @@
         <v>162</v>
       </c>
       <c r="B153">
+        <v>26.555672</v>
+      </c>
+      <c r="C153">
+        <v>-82.202057</v>
+      </c>
+      <c r="D153">
         <v>26.560105</v>
       </c>
-      <c r="C153">
-        <v>-82.223694</v>
-      </c>
-      <c r="D153">
-        <v>26.593234</v>
-      </c>
       <c r="E153">
-        <v>-82.202057</v>
+        <v>-82.200216</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -6120,16 +6129,16 @@
         <v>163</v>
       </c>
       <c r="B154">
-        <v>29.387237</v>
+        <v>26.560105</v>
       </c>
       <c r="C154">
-        <v>-81.102129</v>
+        <v>-82.223694</v>
       </c>
       <c r="D154">
-        <v>29.427169</v>
+        <v>26.593234</v>
       </c>
       <c r="E154">
-        <v>-81.083841</v>
+        <v>-82.202057</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -6155,16 +6164,16 @@
         <v>164</v>
       </c>
       <c r="B155">
-        <v>26.792724</v>
+        <v>29.387237</v>
       </c>
       <c r="C155">
-        <v>-80.032082</v>
+        <v>-81.102129</v>
       </c>
       <c r="D155">
-        <v>26.794655</v>
+        <v>29.427169</v>
       </c>
       <c r="E155">
-        <v>-80.031974</v>
+        <v>-81.083841</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -6190,16 +6199,16 @@
         <v>165</v>
       </c>
       <c r="B156">
-        <v>26.507464</v>
+        <v>26.792724</v>
       </c>
       <c r="C156">
-        <v>-80.050737</v>
+        <v>-80.032082</v>
       </c>
       <c r="D156">
-        <v>26.516226</v>
+        <v>26.794655</v>
       </c>
       <c r="E156">
-        <v>-80.048968</v>
+        <v>-80.031974</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -6225,16 +6234,16 @@
         <v>166</v>
       </c>
       <c r="B157">
-        <v>30.378833</v>
+        <v>26.507464</v>
       </c>
       <c r="C157">
-        <v>-86.507078</v>
+        <v>-80.050737</v>
       </c>
       <c r="D157">
-        <v>30.383991</v>
+        <v>26.516226</v>
       </c>
       <c r="E157">
-        <v>-86.397361</v>
+        <v>-80.048968</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6260,16 +6269,16 @@
         <v>167</v>
       </c>
       <c r="B158">
-        <v>30.392784</v>
+        <v>30.378833</v>
       </c>
       <c r="C158">
-        <v>-86.633156</v>
+        <v>-86.507078</v>
       </c>
       <c r="D158">
-        <v>30.396836</v>
+        <v>30.383991</v>
       </c>
       <c r="E158">
-        <v>-86.582791</v>
+        <v>-86.397361</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6295,16 +6304,16 @@
         <v>168</v>
       </c>
       <c r="B159">
-        <v>24.557144</v>
+        <v>30.392784</v>
       </c>
       <c r="C159">
-        <v>-81.718797</v>
+        <v>-86.633156</v>
       </c>
       <c r="D159">
-        <v>24.558689</v>
+        <v>30.396836</v>
       </c>
       <c r="E159">
-        <v>-81.717075</v>
+        <v>-86.582791</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -6330,16 +6339,16 @@
         <v>169</v>
       </c>
       <c r="B160">
-        <v>30.127149</v>
+        <v>24.557144</v>
       </c>
       <c r="C160">
-        <v>-81.350422</v>
+        <v>-81.718797</v>
       </c>
       <c r="D160">
-        <v>30.1411</v>
+        <v>24.558689</v>
       </c>
       <c r="E160">
-        <v>-81.347137</v>
+        <v>-81.717075</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -6365,16 +6374,16 @@
         <v>170</v>
       </c>
       <c r="B161">
-        <v>27.650138</v>
+        <v>30.127149</v>
       </c>
       <c r="C161">
-        <v>-82.755057</v>
+        <v>-81.350422</v>
       </c>
       <c r="D161">
-        <v>27.652936</v>
+        <v>30.1411</v>
       </c>
       <c r="E161">
-        <v>-82.753384</v>
+        <v>-81.347137</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -6400,16 +6409,16 @@
         <v>171</v>
       </c>
       <c r="B162">
-        <v>26.516225</v>
+        <v>27.650138</v>
       </c>
       <c r="C162">
-        <v>-80.048969</v>
+        <v>-82.755057</v>
       </c>
       <c r="D162">
-        <v>26.549394</v>
+        <v>27.652936</v>
       </c>
       <c r="E162">
-        <v>-80.041771</v>
+        <v>-82.753384</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -6435,16 +6444,16 @@
         <v>172</v>
       </c>
       <c r="B163">
-        <v>26.615223</v>
+        <v>26.516225</v>
       </c>
       <c r="C163">
-        <v>-80.037321</v>
+        <v>-80.048969</v>
       </c>
       <c r="D163">
-        <v>26.771248</v>
+        <v>26.549394</v>
       </c>
       <c r="E163">
-        <v>-80.032863</v>
+        <v>-80.041771</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -6470,16 +6479,16 @@
         <v>173</v>
       </c>
       <c r="B164">
-        <v>26.77371</v>
+        <v>26.615223</v>
       </c>
       <c r="C164">
-        <v>-80.031754</v>
+        <v>-80.037321</v>
       </c>
       <c r="D164">
-        <v>26.781459</v>
+        <v>26.771248</v>
       </c>
       <c r="E164">
-        <v>-80.031443</v>
+        <v>-80.032863</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -6505,16 +6514,16 @@
         <v>174</v>
       </c>
       <c r="B165">
-        <v>30.133206</v>
+        <v>26.77371</v>
       </c>
       <c r="C165">
-        <v>-85.990849</v>
+        <v>-80.031754</v>
       </c>
       <c r="D165">
-        <v>30.267047</v>
+        <v>26.781459</v>
       </c>
       <c r="E165">
-        <v>-85.745469</v>
+        <v>-80.031443</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -6540,16 +6549,16 @@
         <v>175</v>
       </c>
       <c r="B166">
-        <v>26.174467</v>
+        <v>30.133206</v>
       </c>
       <c r="C166">
-        <v>-81.816997</v>
+        <v>-85.990849</v>
       </c>
       <c r="D166">
-        <v>26.210929</v>
+        <v>30.267047</v>
       </c>
       <c r="E166">
-        <v>-81.814722</v>
+        <v>-85.745469</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -6575,16 +6584,16 @@
         <v>176</v>
       </c>
       <c r="B167">
-        <v>24.545009</v>
+        <v>26.174467</v>
       </c>
       <c r="C167">
-        <v>-81.808257</v>
+        <v>-81.816997</v>
       </c>
       <c r="D167">
-        <v>24.545347</v>
+        <v>26.210929</v>
       </c>
       <c r="E167">
-        <v>-81.805488</v>
+        <v>-81.814722</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -6610,16 +6619,16 @@
         <v>177</v>
       </c>
       <c r="B168">
-        <v>28.212675</v>
+        <v>24.545009</v>
       </c>
       <c r="C168">
-        <v>-80.605356</v>
+        <v>-81.808257</v>
       </c>
       <c r="D168">
-        <v>28.271962</v>
+        <v>24.545347</v>
       </c>
       <c r="E168">
-        <v>-80.596746</v>
+        <v>-81.805488</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -6645,16 +6654,16 @@
         <v>178</v>
       </c>
       <c r="B169">
-        <v>30.325107</v>
+        <v>28.212675</v>
       </c>
       <c r="C169">
-        <v>-87.18109</v>
+        <v>-80.605356</v>
       </c>
       <c r="D169">
-        <v>30.34766</v>
+        <v>28.271962</v>
       </c>
       <c r="E169">
-        <v>-87.05355</v>
+        <v>-80.596746</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -6680,16 +6689,16 @@
         <v>179</v>
       </c>
       <c r="B170">
-        <v>30.279929</v>
+        <v>30.325107</v>
       </c>
       <c r="C170">
-        <v>-87.518465</v>
+        <v>-87.18109</v>
       </c>
       <c r="D170">
-        <v>30.297771</v>
+        <v>30.34766</v>
       </c>
       <c r="E170">
-        <v>-87.419652</v>
+        <v>-87.05355</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -6715,16 +6724,16 @@
         <v>180</v>
       </c>
       <c r="B171">
-        <v>30.287811</v>
+        <v>30.279929</v>
       </c>
       <c r="C171">
-        <v>-87.479907</v>
+        <v>-87.518465</v>
       </c>
       <c r="D171">
-        <v>30.292608</v>
+        <v>30.297771</v>
       </c>
       <c r="E171">
-        <v>-87.453058</v>
+        <v>-87.419652</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -6750,16 +6759,16 @@
         <v>181</v>
       </c>
       <c r="B172">
-        <v>29.9043</v>
+        <v>30.287811</v>
       </c>
       <c r="C172">
-        <v>-84.441415</v>
+        <v>-87.479907</v>
       </c>
       <c r="D172">
-        <v>29.918918</v>
+        <v>30.292608</v>
       </c>
       <c r="E172">
-        <v>-84.42392</v>
+        <v>-87.453058</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -6785,16 +6794,16 @@
         <v>182</v>
       </c>
       <c r="B173">
-        <v>27.738636</v>
+        <v>29.9043</v>
       </c>
       <c r="C173">
-        <v>-82.837894</v>
+        <v>-84.441415</v>
       </c>
       <c r="D173">
-        <v>27.836403</v>
+        <v>29.918918</v>
       </c>
       <c r="E173">
-        <v>-82.756574</v>
+        <v>-84.42392</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -6820,16 +6829,16 @@
         <v>183</v>
       </c>
       <c r="B174">
+        <v>27.738636</v>
+      </c>
+      <c r="C174">
+        <v>-82.837894</v>
+      </c>
+      <c r="D174">
         <v>27.836403</v>
       </c>
-      <c r="C174">
-        <v>-82.851822</v>
-      </c>
-      <c r="D174">
-        <v>28.019414</v>
-      </c>
       <c r="E174">
-        <v>-82.826804</v>
+        <v>-82.756574</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -6855,16 +6864,16 @@
         <v>184</v>
       </c>
       <c r="B175">
-        <v>26.18948</v>
+        <v>27.836403</v>
       </c>
       <c r="C175">
-        <v>-80.094825</v>
+        <v>-82.851822</v>
       </c>
       <c r="D175">
-        <v>26.257875</v>
+        <v>28.019414</v>
       </c>
       <c r="E175">
-        <v>-80.081883</v>
+        <v>-82.826804</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6890,16 +6899,16 @@
         <v>185</v>
       </c>
       <c r="B176">
-        <v>30.217084</v>
+        <v>26.18948</v>
       </c>
       <c r="C176">
-        <v>-81.380382</v>
+        <v>-80.094825</v>
       </c>
       <c r="D176">
-        <v>30.252987</v>
+        <v>26.257875</v>
       </c>
       <c r="E176">
-        <v>-81.370731</v>
+        <v>-80.081883</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -6925,16 +6934,16 @@
         <v>186</v>
       </c>
       <c r="B177">
-        <v>29.952532</v>
+        <v>30.217084</v>
       </c>
       <c r="C177">
-        <v>-81.322751</v>
+        <v>-81.380382</v>
       </c>
       <c r="D177">
-        <v>30.022624</v>
+        <v>30.252987</v>
       </c>
       <c r="E177">
-        <v>-81.303917</v>
+        <v>-81.370731</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -6960,16 +6969,16 @@
         <v>187</v>
       </c>
       <c r="B178">
-        <v>24.546884</v>
+        <v>29.952532</v>
       </c>
       <c r="C178">
-        <v>-81.79405</v>
+        <v>-81.322751</v>
       </c>
       <c r="D178">
-        <v>24.54709</v>
+        <v>30.022624</v>
       </c>
       <c r="E178">
-        <v>-81.793173</v>
+        <v>-81.303917</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -6995,16 +7004,16 @@
         <v>188</v>
       </c>
       <c r="B179">
-        <v>24.545796</v>
+        <v>24.546884</v>
       </c>
       <c r="C179">
-        <v>-81.801988</v>
+        <v>-81.79405</v>
       </c>
       <c r="D179">
-        <v>24.546515</v>
+        <v>24.54709</v>
       </c>
       <c r="E179">
-        <v>-81.799134</v>
+        <v>-81.793173</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -7030,16 +7039,16 @@
         <v>189</v>
       </c>
       <c r="B180">
-        <v>30.122317</v>
+        <v>24.545796</v>
       </c>
       <c r="C180">
-        <v>-85.745469</v>
+        <v>-81.801988</v>
       </c>
       <c r="D180">
-        <v>30.133206</v>
+        <v>24.546515</v>
       </c>
       <c r="E180">
-        <v>-85.733198</v>
+        <v>-81.799134</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -7065,16 +7074,16 @@
         <v>190</v>
       </c>
       <c r="B181">
-        <v>30.093054</v>
+        <v>30.122317</v>
       </c>
       <c r="C181">
-        <v>-85.7294</v>
+        <v>-85.745469</v>
       </c>
       <c r="D181">
-        <v>30.1187</v>
+        <v>30.133206</v>
       </c>
       <c r="E181">
-        <v>-85.687693</v>
+        <v>-85.733198</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -7100,16 +7109,16 @@
         <v>191</v>
       </c>
       <c r="B182">
-        <v>29.76941</v>
+        <v>30.093054</v>
       </c>
       <c r="C182">
-        <v>-81.26532</v>
+        <v>-85.7294</v>
       </c>
       <c r="D182">
-        <v>29.859518</v>
+        <v>30.1187</v>
       </c>
       <c r="E182">
-        <v>-81.25145</v>
+        <v>-85.687693</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -7135,16 +7144,16 @@
         <v>192</v>
       </c>
       <c r="B183">
-        <v>29.613264</v>
+        <v>29.76941</v>
       </c>
       <c r="C183">
-        <v>-84.958006</v>
+        <v>-81.26532</v>
       </c>
       <c r="D183">
-        <v>29.682908</v>
+        <v>29.859518</v>
       </c>
       <c r="E183">
-        <v>-84.796875</v>
+        <v>-81.25145</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -7170,16 +7179,16 @@
         <v>193</v>
       </c>
       <c r="B184">
+        <v>29.613264</v>
+      </c>
+      <c r="C184">
+        <v>-84.958006</v>
+      </c>
+      <c r="D184">
         <v>29.682908</v>
       </c>
-      <c r="C184">
+      <c r="E184">
         <v>-84.796875</v>
-      </c>
-      <c r="D184">
-        <v>29.772265</v>
-      </c>
-      <c r="E184">
-        <v>-84.691495</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -7205,16 +7214,16 @@
         <v>194</v>
       </c>
       <c r="B185">
-        <v>29.850541</v>
+        <v>29.682908</v>
       </c>
       <c r="C185">
-        <v>-85.38928</v>
+        <v>-84.796875</v>
       </c>
       <c r="D185">
-        <v>29.92489</v>
+        <v>29.772265</v>
       </c>
       <c r="E185">
-        <v>-85.337013</v>
+        <v>-84.691495</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -7240,16 +7249,16 @@
         <v>195</v>
       </c>
       <c r="B186">
-        <v>29.680601</v>
+        <v>29.850541</v>
       </c>
       <c r="C186">
-        <v>-85.403139</v>
+        <v>-85.38928</v>
       </c>
       <c r="D186">
-        <v>29.759268</v>
+        <v>29.92489</v>
       </c>
       <c r="E186">
-        <v>-85.36631</v>
+        <v>-85.337013</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -7275,16 +7284,16 @@
         <v>196</v>
       </c>
       <c r="B187">
+        <v>29.680601</v>
+      </c>
+      <c r="C187">
+        <v>-85.403139</v>
+      </c>
+      <c r="D187">
         <v>29.759268</v>
       </c>
-      <c r="C187">
-        <v>-85.416856</v>
-      </c>
-      <c r="D187">
-        <v>29.879239</v>
-      </c>
       <c r="E187">
-        <v>-85.384372</v>
+        <v>-85.36631</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -7310,16 +7319,16 @@
         <v>197</v>
       </c>
       <c r="B188">
-        <v>27.479232</v>
+        <v>29.759268</v>
       </c>
       <c r="C188">
-        <v>-80.313916</v>
+        <v>-85.416856</v>
       </c>
       <c r="D188">
-        <v>27.532586</v>
+        <v>29.879239</v>
       </c>
       <c r="E188">
-        <v>-80.293157</v>
+        <v>-85.384372</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -7345,16 +7354,16 @@
         <v>198</v>
       </c>
       <c r="B189">
-        <v>27.130714</v>
+        <v>27.479232</v>
       </c>
       <c r="C189">
-        <v>-80.157694</v>
+        <v>-80.313916</v>
       </c>
       <c r="D189">
-        <v>27.163102</v>
+        <v>27.532586</v>
       </c>
       <c r="E189">
-        <v>-80.145242</v>
+        <v>-80.293157</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -7380,16 +7389,16 @@
         <v>199</v>
       </c>
       <c r="B190">
-        <v>27.683225</v>
+        <v>27.130714</v>
       </c>
       <c r="C190">
-        <v>-82.754256</v>
+        <v>-80.157694</v>
       </c>
       <c r="D190">
-        <v>27.73721</v>
+        <v>27.163102</v>
       </c>
       <c r="E190">
-        <v>-82.737883</v>
+        <v>-80.145242</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -7415,16 +7424,16 @@
         <v>200</v>
       </c>
       <c r="B191">
-        <v>29.630233</v>
+        <v>27.683225</v>
       </c>
       <c r="C191">
-        <v>-85.222506</v>
+        <v>-82.754256</v>
       </c>
       <c r="D191">
-        <v>29.68115</v>
+        <v>27.73721</v>
       </c>
       <c r="E191">
-        <v>-85.094442</v>
+        <v>-82.737883</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -7450,16 +7459,16 @@
         <v>201</v>
       </c>
       <c r="B192">
-        <v>26.421856</v>
+        <v>29.630233</v>
       </c>
       <c r="C192">
-        <v>-82.080049</v>
+        <v>-85.222506</v>
       </c>
       <c r="D192">
-        <v>26.454364</v>
+        <v>29.68115</v>
       </c>
       <c r="E192">
-        <v>-82.013847</v>
+        <v>-85.094442</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -7488,13 +7497,13 @@
         <v>26.421856</v>
       </c>
       <c r="C193">
-        <v>-82.182181</v>
+        <v>-82.080049</v>
       </c>
       <c r="D193">
-        <v>26.482469</v>
+        <v>26.454364</v>
       </c>
       <c r="E193">
-        <v>-82.080049</v>
+        <v>-82.013847</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -7520,16 +7529,16 @@
         <v>203</v>
       </c>
       <c r="B194">
-        <v>25.978749</v>
+        <v>26.421856</v>
       </c>
       <c r="C194">
-        <v>-81.744747</v>
+        <v>-82.182181</v>
       </c>
       <c r="D194">
-        <v>25.982905</v>
+        <v>26.482469</v>
       </c>
       <c r="E194">
-        <v>-81.739302</v>
+        <v>-82.080049</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -7555,16 +7564,16 @@
         <v>204</v>
       </c>
       <c r="B195">
-        <v>27.861918</v>
+        <v>25.978749</v>
       </c>
       <c r="C195">
-        <v>-80.454324</v>
+        <v>-81.744747</v>
       </c>
       <c r="D195">
-        <v>27.874581</v>
+        <v>25.982905</v>
       </c>
       <c r="E195">
-        <v>-80.446568</v>
+        <v>-81.739302</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -7590,16 +7599,16 @@
         <v>205</v>
       </c>
       <c r="B196">
-        <v>27.833252</v>
+        <v>27.861918</v>
       </c>
       <c r="C196">
-        <v>-80.446913</v>
+        <v>-80.454324</v>
       </c>
       <c r="D196">
-        <v>27.859959</v>
+        <v>27.874581</v>
       </c>
       <c r="E196">
-        <v>-80.432927</v>
+        <v>-80.446568</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -7625,16 +7634,16 @@
         <v>206</v>
       </c>
       <c r="B197">
-        <v>27.208442</v>
+        <v>27.833252</v>
       </c>
       <c r="C197">
-        <v>-82.512082</v>
+        <v>-80.446913</v>
       </c>
       <c r="D197">
-        <v>27.209766</v>
+        <v>27.859959</v>
       </c>
       <c r="E197">
-        <v>-82.511546</v>
+        <v>-80.432927</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -7660,16 +7669,16 @@
         <v>207</v>
       </c>
       <c r="B198">
-        <v>27.246199</v>
+        <v>27.208442</v>
       </c>
       <c r="C198">
-        <v>-82.56982</v>
+        <v>-82.512082</v>
       </c>
       <c r="D198">
-        <v>27.27891</v>
+        <v>27.209766</v>
       </c>
       <c r="E198">
-        <v>-82.535934</v>
+        <v>-82.511546</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -7695,16 +7704,16 @@
         <v>208</v>
       </c>
       <c r="B199">
-        <v>27.208411</v>
+        <v>27.246199</v>
       </c>
       <c r="C199">
-        <v>-82.526429</v>
+        <v>-82.56982</v>
       </c>
       <c r="D199">
-        <v>27.235931</v>
+        <v>27.27891</v>
       </c>
       <c r="E199">
-        <v>-82.512124</v>
+        <v>-82.535934</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -7730,16 +7739,16 @@
         <v>209</v>
       </c>
       <c r="B200">
-        <v>26.795541</v>
+        <v>27.208411</v>
       </c>
       <c r="C200">
-        <v>-80.035047</v>
+        <v>-82.526429</v>
       </c>
       <c r="D200">
-        <v>26.81295</v>
+        <v>27.235931</v>
       </c>
       <c r="E200">
-        <v>-80.031469</v>
+        <v>-82.512124</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -7765,16 +7774,16 @@
         <v>210</v>
       </c>
       <c r="B201">
-        <v>26.794655</v>
+        <v>26.795541</v>
       </c>
       <c r="C201">
-        <v>-80.031975</v>
+        <v>-80.035047</v>
       </c>
       <c r="D201">
-        <v>26.795541</v>
+        <v>26.81295</v>
       </c>
       <c r="E201">
-        <v>-80.031727</v>
+        <v>-80.031469</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -7800,16 +7809,16 @@
         <v>211</v>
       </c>
       <c r="B202">
-        <v>26.781459</v>
+        <v>26.794655</v>
       </c>
       <c r="C202">
-        <v>-80.032317</v>
+        <v>-80.031975</v>
       </c>
       <c r="D202">
-        <v>26.792724</v>
+        <v>26.795541</v>
       </c>
       <c r="E202">
-        <v>-80.031673</v>
+        <v>-80.031727</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -7835,16 +7844,16 @@
         <v>212</v>
       </c>
       <c r="B203">
-        <v>24.550378</v>
+        <v>26.781459</v>
       </c>
       <c r="C203">
-        <v>-81.775509</v>
+        <v>-80.032317</v>
       </c>
       <c r="D203">
-        <v>24.552461</v>
+        <v>26.792724</v>
       </c>
       <c r="E203">
-        <v>-81.765565</v>
+        <v>-80.031673</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -7870,16 +7879,16 @@
         <v>213</v>
       </c>
       <c r="B204">
-        <v>24.690974</v>
+        <v>24.550378</v>
       </c>
       <c r="C204">
-        <v>-81.086629</v>
+        <v>-81.775509</v>
       </c>
       <c r="D204">
-        <v>24.69216</v>
+        <v>24.552461</v>
       </c>
       <c r="E204">
-        <v>-81.082672</v>
+        <v>-81.765565</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -7905,16 +7914,16 @@
         <v>214</v>
       </c>
       <c r="B205">
-        <v>26.585986</v>
+        <v>24.690974</v>
       </c>
       <c r="C205">
-        <v>-80.037486</v>
+        <v>-81.086629</v>
       </c>
       <c r="D205">
-        <v>26.61164</v>
+        <v>24.69216</v>
       </c>
       <c r="E205">
-        <v>-80.036497</v>
+        <v>-81.082672</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -7940,16 +7949,16 @@
         <v>215</v>
       </c>
       <c r="B206">
-        <v>28.043348</v>
+        <v>26.585986</v>
       </c>
       <c r="C206">
-        <v>-80.570181</v>
+        <v>-80.037486</v>
       </c>
       <c r="D206">
-        <v>28.105808</v>
+        <v>26.61164</v>
       </c>
       <c r="E206">
-        <v>-80.545313</v>
+        <v>-80.036497</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -7975,16 +7984,16 @@
         <v>216</v>
       </c>
       <c r="B207">
-        <v>26.897711</v>
+        <v>28.043348</v>
       </c>
       <c r="C207">
-        <v>-82.35341</v>
+        <v>-80.570181</v>
       </c>
       <c r="D207">
-        <v>26.910933</v>
+        <v>28.105808</v>
       </c>
       <c r="E207">
-        <v>-82.340709</v>
+        <v>-80.545313</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -8010,16 +8019,16 @@
         <v>217</v>
       </c>
       <c r="B208">
-        <v>24.606795</v>
+        <v>26.897711</v>
       </c>
       <c r="C208">
-        <v>-81.561901</v>
+        <v>-82.35341</v>
       </c>
       <c r="D208">
-        <v>24.6122</v>
+        <v>26.910933</v>
       </c>
       <c r="E208">
-        <v>-81.550435</v>
+        <v>-82.340709</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -8045,16 +8054,16 @@
         <v>218</v>
       </c>
       <c r="B209">
-        <v>24.563343</v>
+        <v>24.606795</v>
       </c>
       <c r="C209">
-        <v>-81.81424</v>
+        <v>-81.561901</v>
       </c>
       <c r="D209">
-        <v>24.563746</v>
+        <v>24.6122</v>
       </c>
       <c r="E209">
-        <v>-81.812689</v>
+        <v>-81.550435</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -8080,16 +8089,16 @@
         <v>219</v>
       </c>
       <c r="B210">
-        <v>25.850722</v>
+        <v>24.563343</v>
       </c>
       <c r="C210">
-        <v>-81.63693</v>
+        <v>-81.81424</v>
       </c>
       <c r="D210">
-        <v>25.895289</v>
+        <v>24.563746</v>
       </c>
       <c r="E210">
-        <v>-81.540135</v>
+        <v>-81.812689</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -8115,16 +8124,16 @@
         <v>220</v>
       </c>
       <c r="B211">
-        <v>26.956518</v>
+        <v>25.850722</v>
       </c>
       <c r="C211">
-        <v>-80.080541</v>
+        <v>-81.63693</v>
       </c>
       <c r="D211">
-        <v>26.970426</v>
+        <v>25.895289</v>
       </c>
       <c r="E211">
-        <v>-80.076242</v>
+        <v>-81.540135</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -8150,16 +8159,16 @@
         <v>221</v>
       </c>
       <c r="B212">
-        <v>30.355198</v>
+        <v>26.956518</v>
       </c>
       <c r="C212">
-        <v>-86.317189</v>
+        <v>-80.080541</v>
       </c>
       <c r="D212">
-        <v>30.366735</v>
+        <v>26.970426</v>
       </c>
       <c r="E212">
-        <v>-86.26453</v>
+        <v>-80.076242</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -8185,16 +8194,16 @@
         <v>222</v>
       </c>
       <c r="B213">
-        <v>29.955296</v>
+        <v>30.355198</v>
       </c>
       <c r="C213">
-        <v>-85.687693</v>
+        <v>-86.317189</v>
       </c>
       <c r="D213">
-        <v>30.093054</v>
+        <v>30.366735</v>
       </c>
       <c r="E213">
-        <v>-85.449027</v>
+        <v>-86.26453</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -8220,16 +8229,16 @@
         <v>223</v>
       </c>
       <c r="B214">
-        <v>30.34766</v>
+        <v>29.955296</v>
       </c>
       <c r="C214">
-        <v>-87.05355</v>
+        <v>-85.687693</v>
       </c>
       <c r="D214">
-        <v>30.351441</v>
+        <v>30.093054</v>
       </c>
       <c r="E214">
-        <v>-87.032988</v>
+        <v>-85.449027</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -8255,16 +8264,16 @@
         <v>224</v>
       </c>
       <c r="B215">
-        <v>26.219939</v>
+        <v>30.34766</v>
       </c>
       <c r="C215">
-        <v>-81.82776</v>
+        <v>-87.05355</v>
       </c>
       <c r="D215">
-        <v>26.272271</v>
+        <v>30.351441</v>
       </c>
       <c r="E215">
-        <v>-81.817559</v>
+        <v>-87.032988</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -8290,16 +8299,16 @@
         <v>225</v>
       </c>
       <c r="B216">
-        <v>27.054908</v>
+        <v>26.219939</v>
       </c>
       <c r="C216">
-        <v>-82.467846</v>
+        <v>-81.82776</v>
       </c>
       <c r="D216">
-        <v>27.112439</v>
+        <v>26.272271</v>
       </c>
       <c r="E216">
-        <v>-82.44189</v>
+        <v>-81.817559</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -8325,16 +8334,16 @@
         <v>226</v>
       </c>
       <c r="B217">
-        <v>29.910518</v>
+        <v>27.054908</v>
       </c>
       <c r="C217">
-        <v>-81.303917</v>
+        <v>-82.467846</v>
       </c>
       <c r="D217">
-        <v>29.952532</v>
+        <v>27.112439</v>
       </c>
       <c r="E217">
-        <v>-81.288765</v>
+        <v>-82.44189</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -8360,16 +8369,16 @@
         <v>227</v>
       </c>
       <c r="B218">
-        <v>25.732313</v>
+        <v>27.62041</v>
       </c>
       <c r="C218">
-        <v>-80.160553</v>
+        <v>-80.361752</v>
       </c>
       <c r="D218">
-        <v>25.757787</v>
+        <v>27.674945</v>
       </c>
       <c r="E218">
-        <v>-80.142618</v>
+        <v>-80.345899</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -8395,16 +8404,16 @@
         <v>228</v>
       </c>
       <c r="B219">
-        <v>25.731705</v>
+        <v>29.910518</v>
       </c>
       <c r="C219">
-        <v>-80.162087</v>
+        <v>-81.303917</v>
       </c>
       <c r="D219">
-        <v>25.732159</v>
+        <v>29.952532</v>
       </c>
       <c r="E219">
-        <v>-80.160814</v>
+        <v>-81.288765</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -8430,16 +8439,16 @@
         <v>229</v>
       </c>
       <c r="B220">
-        <v>29.218522</v>
+        <v>25.732313</v>
       </c>
       <c r="C220">
-        <v>-81.083841</v>
+        <v>-80.160553</v>
       </c>
       <c r="D220">
-        <v>29.387237</v>
+        <v>25.757787</v>
       </c>
       <c r="E220">
-        <v>-81.002468</v>
+        <v>-80.142618</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -8465,16 +8474,16 @@
         <v>230</v>
       </c>
       <c r="B221">
-        <v>29.07845</v>
+        <v>25.731705</v>
       </c>
       <c r="C221">
-        <v>-81.002468</v>
+        <v>-80.162087</v>
       </c>
       <c r="D221">
-        <v>29.218522</v>
+        <v>25.732159</v>
       </c>
       <c r="E221">
-        <v>-80.918105</v>
+        <v>-80.160814</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -8500,16 +8509,16 @@
         <v>231</v>
       </c>
       <c r="B222">
-        <v>27.767704</v>
+        <v>29.218522</v>
       </c>
       <c r="C222">
-        <v>-80.432927</v>
+        <v>-81.083841</v>
       </c>
       <c r="D222">
-        <v>27.833252</v>
+        <v>29.387237</v>
       </c>
       <c r="E222">
-        <v>-80.39871</v>
+        <v>-81.002468</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -8535,16 +8544,16 @@
         <v>232</v>
       </c>
       <c r="B223">
-        <v>30.269277</v>
+        <v>29.07845</v>
       </c>
       <c r="C223">
-        <v>-86.077346</v>
+        <v>-81.002468</v>
       </c>
       <c r="D223">
-        <v>30.299108</v>
+        <v>29.218522</v>
       </c>
       <c r="E223">
-        <v>-85.996024</v>
+        <v>-80.918105</v>
       </c>
       <c r="F223">
         <v>0</v>
@@ -8570,16 +8579,16 @@
         <v>233</v>
       </c>
       <c r="B224">
-        <v>30.302</v>
+        <v>27.767709</v>
       </c>
       <c r="C224">
-        <v>-86.14618</v>
+        <v>-80.43293</v>
       </c>
       <c r="D224">
-        <v>30.321211</v>
+        <v>27.833257</v>
       </c>
       <c r="E224">
-        <v>-86.084846</v>
+        <v>-80.398712</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -8605,16 +8614,16 @@
         <v>234</v>
       </c>
       <c r="B225">
-        <v>30.33168</v>
+        <v>27.756911</v>
       </c>
       <c r="C225">
-        <v>-86.26453</v>
+        <v>-80.398712</v>
       </c>
       <c r="D225">
-        <v>30.355198</v>
+        <v>27.767709</v>
       </c>
       <c r="E225">
-        <v>-86.17991</v>
+        <v>-80.392673</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -8640,16 +8649,16 @@
         <v>235</v>
       </c>
       <c r="B226">
-        <v>29.633674</v>
+        <v>30.269277</v>
       </c>
       <c r="C226">
-        <v>-81.201494</v>
+        <v>-86.077346</v>
       </c>
       <c r="D226">
-        <v>29.643182</v>
+        <v>30.299108</v>
       </c>
       <c r="E226">
-        <v>-81.197572</v>
+        <v>-85.996024</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -8675,33 +8684,138 @@
         <v>236</v>
       </c>
       <c r="B227">
+        <v>30.302</v>
+      </c>
+      <c r="C227">
+        <v>-86.14618</v>
+      </c>
+      <c r="D227">
+        <v>30.321211</v>
+      </c>
+      <c r="E227">
+        <v>-86.084846</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>0.0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>0.0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>237</v>
+      </c>
+      <c r="B228">
+        <v>30.33168</v>
+      </c>
+      <c r="C228">
+        <v>-86.26453</v>
+      </c>
+      <c r="D228">
+        <v>30.355198</v>
+      </c>
+      <c r="E228">
+        <v>-86.17991</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>0.0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0.0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>238</v>
+      </c>
+      <c r="B229">
+        <v>29.633674</v>
+      </c>
+      <c r="C229">
+        <v>-81.201494</v>
+      </c>
+      <c r="D229">
+        <v>29.643182</v>
+      </c>
+      <c r="E229">
+        <v>-81.197572</v>
+      </c>
+      <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>0.0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0.0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230">
         <v>26.272271</v>
       </c>
-      <c r="C227">
+      <c r="C230">
         <v>-81.831469</v>
       </c>
-      <c r="D227">
+      <c r="D230">
         <v>26.28858</v>
       </c>
-      <c r="E227">
+      <c r="E230">
         <v>-81.82776</v>
       </c>
-      <c r="F227">
-        <v>0</v>
-      </c>
-      <c r="G227">
-        <v>0.0</v>
-      </c>
-      <c r="H227">
-        <v>0</v>
-      </c>
-      <c r="I227">
-        <v>0.0</v>
-      </c>
-      <c r="J227">
-        <v>0</v>
-      </c>
-      <c r="K227">
+      <c r="F230">
+        <v>0</v>
+      </c>
+      <c r="G230">
+        <v>0.0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0.0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
         <v>0.0</v>
       </c>
     </row>
